--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
@@ -3646,7 +3646,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 3</t>
+          <t>Supplementary Figure 2</t>
         </is>
       </c>
     </row>
@@ -3836,7 +3836,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5</t>
+          <t>Supplementary Figure 4</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 6b</t>
+          <t>Supplementary Figure 5b</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 7</t>
+          <t>Supplementary Figure 6</t>
         </is>
       </c>
     </row>
@@ -11852,7 +11852,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9a,b</t>
+          <t>Supplementary Figure 8a,b</t>
         </is>
       </c>
     </row>
@@ -15888,7 +15888,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9c,d</t>
+          <t>Supplementary Figure 8c,d</t>
         </is>
       </c>
     </row>
@@ -16173,7 +16173,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh (21.25 million elements).</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh.</t>
         </is>
       </c>
     </row>
@@ -16200,117 +16200,115 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>L1 (Very Low)</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
+      <c r="B5" t="n">
         <v>182768</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>1.439</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>1465.8</v>
+      <c r="C5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-87.2</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>L2 (Low)</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0.4977</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>441.6</v>
+      <c r="C6" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-26.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>L3 (Medium)</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
+      <c r="B7" t="n">
         <v>3454723</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0.1633</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>77.7</v>
+      <c r="C7" t="n">
+        <v>0.1794</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-4.6</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>L4 (High)</t>
         </is>
       </c>
-      <c r="B8" s="9" t="n">
+      <c r="B8" t="n">
         <v>4990080</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0.1208</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>31.4</v>
+      <c r="C8" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>L5 (Very High)</t>
         </is>
       </c>
-      <c r="B9" s="9" t="n">
+      <c r="B9" t="n">
         <v>11958220</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0.1002</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>9</v>
+      <c r="C9" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>L6 (Ultra High)</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n">
+      <c r="B10" t="n">
         <v>18864900</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0.0927</v>
-      </c>
-      <c r="D10" s="4" t="n">
+      <c r="C10" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D10" t="n">
         <v>0.87</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" t="n">
         <v>21245850</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="C11" t="n">
+        <v>0.1897</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>
@@ -16344,7 +16342,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison between adaptive and uniform meshes at approximately 800,000 elements.</t>
+          <t>Comparison between an adaptive mesh and a uniform mesh (approximately 800,000 elements).</t>
         </is>
       </c>
     </row>
@@ -16376,63 +16374,63 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Uniform Mesh</t>
         </is>
       </c>
-      <c r="B5" s="9" t="n">
-        <v>799520</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>2.8561</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>3007.8</v>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="B5" t="n">
+        <v>799000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-77.90000000000001</v>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Adaptive Mesh</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B6" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0.4977</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>441.6</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.8532</v>
+      <c r="C6" t="n">
+        <v>0.1387</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-26.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.663</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Reference Mesh</t>
         </is>
       </c>
-      <c r="B7" s="9" t="n">
-        <v>21245850</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+      <c r="B7" t="n">
+        <v>18864900</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" t="n">
         <v>1</v>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -16209,10 +16209,10 @@
         <v>182768</v>
       </c>
       <c r="C5" t="n">
-        <v>0.024</v>
+        <v>0.3009</v>
       </c>
       <c r="D5" t="n">
-        <v>-87.2</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6">
@@ -16225,10 +16225,10 @@
         <v>802365</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1387</v>
+        <v>0.2029</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.2</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="7">
@@ -16241,10 +16241,10 @@
         <v>3454723</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1794</v>
+        <v>0.1682</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -16257,10 +16257,10 @@
         <v>4990080</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1846</v>
+        <v>0.1637</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -16273,7 +16273,7 @@
         <v>11958220</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1871</v>
+        <v>0.1616</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
@@ -16289,7 +16289,7 @@
         <v>18864900</v>
       </c>
       <c r="C10" t="n">
-        <v>0.188</v>
+        <v>0.1622</v>
       </c>
       <c r="D10" t="n">
         <v>0.87</v>
@@ -16305,10 +16305,12 @@
         <v>21245850</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1897</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9</v>
+        <v>0.1608</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -16383,10 +16385,10 @@
         <v>799000</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0415</v>
+        <v>0.286</v>
       </c>
       <c r="D5" t="n">
-        <v>-77.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -16404,10 +16406,10 @@
         <v>802365</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1387</v>
+        <v>0.2029</v>
       </c>
       <c r="D6" t="n">
-        <v>-26.2</v>
+        <v>26.2</v>
       </c>
       <c r="E6" t="n">
         <v>0.663</v>
@@ -16420,10 +16422,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18864900</v>
+        <v>21245850</v>
       </c>
       <c r="C7" t="n">
-        <v>0.188</v>
+        <v>0.1608</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -16289,10 +16289,10 @@
         <v>18864900</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1622</v>
+        <v>0.1611</v>
       </c>
       <c r="D10" t="n">
-        <v>0.87</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11">

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -2968,6 +2968,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3018,7 +3019,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3041,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3073,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3095,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3117,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3139,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>[48]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
@@ -3170,7 +3171,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3191,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[35]</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3211,7 @@
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[36]</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3233,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3265,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>[51]</t>
+          <t>[37]</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3313,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[52]</t>
+          <t>[38]</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3335,7 @@
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>[29]</t>
+          <t>[21]</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3355,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>[53]</t>
+          <t>[39]</t>
         </is>
       </c>
     </row>
@@ -16062,7 +16063,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched literature mass-loss measurements and was adopted in the final model.</t>
+          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) gave the lowest RMSE, which was used as a consistency check but was not the main selection criterion, and was adopted on physical grounds (RMSE values may differ from those of the calibrated model, as these validation cases were evaluated prior to model calibration).</t>
         </is>
       </c>
     </row>
@@ -17214,10 +17215,11 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameters included in the Morris sensitivity analysis.</t>
-        </is>
-      </c>
-    </row>
+          <t>Parameters included in the Morris sensitivity analysis (the ranges might differ from calibration space as this was done prior to calibration of the model).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17280,7 +17282,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>mm^6 g^-2 h^-1</t>
+          <t>L^2 mol^-2 h^-1</t>
         </is>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -2964,7 +2964,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model parameters used in the Zn biodegradation simulation.</t>
+          <t>Model parameters used in the Zn biodegradation simulation. The simulations used diffusivities 15-26% above the tabulated values (mm^2 h^-1: Zn2+ 3.38, Cl- 9.7, OH- 25.45, O2 10.8) and a film tortuosity of 120.</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>5.606 g cm^-3</t>
+          <t>3.998 g cm^-3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>120</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -3248,26 +3248,10 @@
       <c r="D18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ sat. concentration</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>[Zn]_sat</t>
-        </is>
-      </c>
-      <c r="C19" s="1" t="inlineStr">
-        <is>
-          <t>10 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>[37]</t>
-        </is>
-      </c>
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="1" t="n"/>
+      <c r="C19" s="1" t="n"/>
+      <c r="D19" s="1" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3308,7 +3292,7 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>142.3 mmol L^-1</t>
+          <t>142.3 mmol L^-1 (5.04e-6 g mm^-3)</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
@@ -3330,7 +3314,7 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>3.5 mg L^-1</t>
+          <t>3.5 mg L^-1 (3.5e-9 g mm^-3)</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
@@ -3393,6 +3377,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3428,11 +3413,13 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>[1, 100]</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>35.91</v>
+          <t>[1, 1e5]</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3448,11 +3435,13 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[5, 100]</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>27.17</v>
+          <t>[0.01, 1e3]</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3468,11 +3457,13 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.05, 5.0]</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.51</v>
+          <t>[0.5, 50]</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>[v4 optimum]</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -16471,6 +16462,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -16719,7 +16711,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>802,365</t>
+          <t>37,399</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -16741,7 +16733,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>121,120</t>
+          <t>[to update]</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -16763,7 +16755,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>0.1 mm</t>
+          <t>0.5 mm</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -16839,7 +16831,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>0.25 h</t>
+          <t>4 h</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -16914,7 +16906,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>50</v>
@@ -16931,7 +16923,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>2,592</t>
+          <t>[to update]</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -17041,7 +17033,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>2 h</t>
+          <t>~20 min</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -17149,7 +17141,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Dirichlet</t>
+          <t>Dirichlet (C_O2 = 3.5 mg L^-1)</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -17219,7 +17211,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -2968,7 +2968,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3430,12 +3429,12 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>L^2 mol^-2 h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[0.01, 1e3]</t>
+          <t>[8.0e6, 8.0e11]</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -16462,7 +16461,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17211,6 +17209,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -17273,7 +17272,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>L^2 mol^-2 h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
@@ -3376,7 +3376,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3637,7 +3636,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 2</t>
+          <t>Supplementary Figure 1</t>
         </is>
       </c>
     </row>
@@ -3648,6 +3647,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3827,7 +3827,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 4</t>
+          <t>Supplementary Figure 3</t>
         </is>
       </c>
     </row>
@@ -3838,6 +3838,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5120,7 +5121,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5b</t>
+          <t>Supplementary Figure 4b</t>
         </is>
       </c>
     </row>
@@ -5138,6 +5139,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -5928,7 +5930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 6</t>
+          <t>Supplementary Figure 5</t>
         </is>
       </c>
     </row>
@@ -5939,6 +5941,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -10058,6 +10061,7 @@
       </c>
       <c r="H174" s="1" t="n"/>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -11843,7 +11847,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 8a,b</t>
+          <t>Supplementary Figure 7a,b</t>
         </is>
       </c>
     </row>
@@ -11854,6 +11858,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -15785,6 +15790,7 @@
         <v>3.411422</v>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -15879,7 +15885,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 8c,d</t>
+          <t>Supplementary Figure 7c,d</t>
         </is>
       </c>
     </row>
@@ -15890,6 +15896,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -16035,7 +16042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16044,94 +16051,85 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Table S1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) gave the lowest RMSE, which was used as a consistency check but was not the main selection criterion, and was adopted on physical grounds (RMSE values may differ from those of the calibrated model, as these validation cases were evaluated prior to model calibration).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Limiting regimes of the interfacial oxygen flux.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>RMSE (%)</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regime</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Condition</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Interfacial flux J_O2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Hard minimum</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.0568</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Reaction-controlled</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Da &lt;&lt; 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>k_ORR C_b</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Mixed control</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0.077</v>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Transition</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Da ~ 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>C_b/(1/k_ORR + delta/D_O2,eff)</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Hybrid cathodic</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.0766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Coupled ORR (no O2 cap)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.2983</v>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Diffusion-controlled</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Da &gt;&gt; 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>D_O2,eff C_b/delta</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -17209,7 +17207,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-1185" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure 3a" sheetId="1" state="visible" r:id="rId1"/>
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 1" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
@@ -75,7 +75,12 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
+      <family val="2"/>
       <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -109,9 +114,14 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2964,7 +2974,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Model parameters used in the Zn biodegradation simulation. The simulations used diffusivities 15-26% above the tabulated values (mm^2 h^-1: Zn2+ 3.38, Cl- 9.7, OH- 25.45, O2 10.8) and a film tortuosity of 120.</t>
+          <t>Model parameters used in the Zn biodegradation simulation.</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3028,7 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[46]</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3050,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[46]</t>
         </is>
       </c>
     </row>
@@ -3072,7 +3082,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[47]</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3104,7 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[47]</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3126,7 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[47]</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3148,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>[34]</t>
+          <t>[48]</t>
         </is>
       </c>
     </row>
@@ -3165,12 +3175,12 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>3.998 g cm^-3</t>
+          <t>5.606 g cm^-3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[47]</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3200,7 @@
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[35]</t>
+          <t>[49]</t>
         </is>
       </c>
     </row>
@@ -3206,11 +3216,11 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[36]</t>
+          <t>[50]</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3242,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>[33]</t>
+          <t>[46]</t>
         </is>
       </c>
     </row>
@@ -3247,10 +3257,26 @@
       <c r="D18" s="1" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="1" t="n"/>
-      <c r="C19" s="1" t="n"/>
-      <c r="D19" s="1" t="n"/>
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Zn2+ sat. concentration</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="inlineStr">
+        <is>
+          <t>[Zn]_sat</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="inlineStr">
+        <is>
+          <t>10 mg L^-1</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>[51]</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -3291,12 +3317,12 @@
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>142.3 mmol L^-1 (5.04e-6 g mm^-3)</t>
+          <t>142.3 mmol L^-1</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[38]</t>
+          <t>[52]</t>
         </is>
       </c>
     </row>
@@ -3313,12 +3339,12 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>3.5 mg L^-1 (3.5e-9 g mm^-3)</t>
+          <t>3.5 mg L^-1</t>
         </is>
       </c>
       <c r="D23" s="1" t="inlineStr">
         <is>
-          <t>[21]</t>
+          <t>[29]</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3364,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>[39]</t>
+          <t>[53]</t>
         </is>
       </c>
     </row>
@@ -3411,13 +3437,11 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>[1, 1e5]</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>[v4 optimum]</t>
-        </is>
+          <t>[1, 100]</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>35.91</v>
       </c>
     </row>
     <row r="6">
@@ -3428,18 +3452,16 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>mm^6 g^-2 h^-1</t>
+          <t>L^2 mol^-2 h^-1</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[8.0e6, 8.0e11]</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>[v4 optimum]</t>
-        </is>
+          <t>[5, 100]</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>27.17</v>
       </c>
     </row>
     <row r="7">
@@ -3455,13 +3477,11 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.5, 50]</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>[v4 optimum]</t>
-        </is>
+          <t>[0.05, 5.0]</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.51</v>
       </c>
     </row>
     <row r="8">
@@ -3636,7 +3656,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 1</t>
+          <t>Supplementary Figure 3</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3667,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -3827,7 +3846,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 3</t>
+          <t>Supplementary Figure 5</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -5121,7 +5139,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 4b</t>
+          <t>Supplementary Figure 6b</t>
         </is>
       </c>
     </row>
@@ -5139,7 +5157,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -5930,7 +5947,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5</t>
+          <t>Supplementary Figure 7</t>
         </is>
       </c>
     </row>
@@ -5941,7 +5958,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -10061,7 +10077,6 @@
       </c>
       <c r="H174" s="1" t="n"/>
     </row>
-    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -10957,14 +10972,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="4" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
@@ -10986,13 +11000,6 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Kinetic parameters: k_f = 35.91 h^-1, k_d = 27.17 L^2 mol^-2 h^-1, k_ORR = 0.51 mm h^-1 (calibrated optimum, Table 2).</t>
-        </is>
-      </c>
-    </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -11029,6 +11036,12 @@
           <t>Stage</t>
         </is>
       </c>
+      <c r="I4" s="10" t="n"/>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -11037,14 +11050,18 @@
       <c r="B5" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>35.90583</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>27.16962</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>0.50747</v>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>3.0×10⁵</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>1.0×10⁸</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>80</v>
       </c>
       <c r="F5" s="1" t="n">
         <v>0.042402</v>
@@ -11054,6 +11071,12 @@
           <t>dip</t>
         </is>
       </c>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -11062,14 +11085,18 @@
       <c r="B6" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>11.869081</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>36.881722</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>0.2513</v>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>9.9×10⁴</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>1.4×10⁸</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>40</v>
       </c>
       <c r="F6" s="1" t="n">
         <v>0.04609</v>
@@ -11079,6 +11106,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -11087,14 +11120,18 @@
       <c r="B7" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>30.214196</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>61.694967</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>0.394269</v>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>2.5×10⁵</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>2.3×10⁸</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>62</v>
       </c>
       <c r="F7" s="1" t="n">
         <v>0.046374</v>
@@ -11104,6 +11141,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -11112,14 +11155,18 @@
       <c r="B8" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>48.4118</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>29.5251</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>0.5962</v>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>4.0×10⁵</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>1.1×10⁸</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>94</v>
       </c>
       <c r="F8" s="1" t="n">
         <v>0.046388</v>
@@ -11129,6 +11176,12 @@
           <t>dip</t>
         </is>
       </c>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -11137,14 +11190,18 @@
       <c r="B9" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>57.872716</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>21.341167</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>0.656898</v>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>4.8×10⁵</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>7.9×10⁷</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>100</v>
       </c>
       <c r="F9" s="1" t="n">
         <v>0.046866</v>
@@ -11154,6 +11211,12 @@
           <t>dip</t>
         </is>
       </c>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -11162,14 +11225,18 @@
       <c r="B10" s="1" t="n">
         <v>25</v>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>36.548579</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>14.595382</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>0.427188</v>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>3.1×10⁵</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>5.4×10⁷</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>67</v>
       </c>
       <c r="F10" s="1" t="n">
         <v>0.04719</v>
@@ -11179,6 +11246,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -11187,14 +11260,18 @@
       <c r="B11" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>51.43335</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>37.009824</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0.704924</v>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>4.3×10⁵</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>1.4×10⁸</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>110</v>
       </c>
       <c r="F11" s="1" t="n">
         <v>0.048462</v>
@@ -11204,6 +11281,12 @@
           <t>dip</t>
         </is>
       </c>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -11212,14 +11295,18 @@
       <c r="B12" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>4.364803</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>5.5078</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0.15547</v>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>3.6×10⁴</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>2.0×10⁷</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="n">
         <v>0.052771</v>
@@ -11229,6 +11316,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="11" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -11237,14 +11330,18 @@
       <c r="B13" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>57.141068</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>42.489062</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0.437817</v>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>4.8×10⁵</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>1.6×10⁸</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>69</v>
       </c>
       <c r="F13" s="1" t="n">
         <v>0.055936</v>
@@ -11254,6 +11351,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="11" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -11262,14 +11365,18 @@
       <c r="B14" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>57.480181</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>18.053204</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>0.434372</v>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>4.8×10⁵</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>6.6×10⁷</t>
+        </is>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>68</v>
       </c>
       <c r="F14" s="1" t="n">
         <v>0.056486</v>
@@ -11279,6 +11386,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="11" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -11287,14 +11400,18 @@
       <c r="B15" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>66.021243</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>11.767734</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>0.452399</v>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>5.5×10⁵</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>4.3×10⁷</t>
+        </is>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>71</v>
       </c>
       <c r="F15" s="1" t="n">
         <v>0.05756</v>
@@ -11304,6 +11421,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="11" t="n"/>
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="11" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -11312,14 +11435,18 @@
       <c r="B16" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>58.226265</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>0.430407</v>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>4.9×10⁵</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>3.7×10⁸</t>
+        </is>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>68</v>
       </c>
       <c r="F16" s="1" t="n">
         <v>0.057868</v>
@@ -11329,6 +11456,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="11" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -11337,14 +11470,18 @@
       <c r="B17" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>60.640234</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>0.433336</v>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>5.1×10⁵</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>1.8×10⁷</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>68</v>
       </c>
       <c r="F17" s="1" t="n">
         <v>0.058507</v>
@@ -11354,6 +11491,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="11" t="n"/>
+      <c r="M17" s="11" t="n"/>
+      <c r="N17" s="11" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -11362,14 +11505,18 @@
       <c r="B18" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>66.116321</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>27.695915</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>0.445382</v>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>5.5×10⁵</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>1.0×10⁸</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="n">
         <v>0.058528</v>
@@ -11379,6 +11526,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="11" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -11387,14 +11540,18 @@
       <c r="B19" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>60.154809</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>7.670637</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0.431341</v>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>5.0×10⁵</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>2.8×10⁷</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>68</v>
       </c>
       <c r="F19" s="1" t="n">
         <v>0.059043</v>
@@ -11404,6 +11561,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -11412,14 +11575,18 @@
       <c r="B20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>55.129743</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>65.183634</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>0.418043</v>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>4.6×10⁵</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>2.4×10⁸</t>
+        </is>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>66</v>
       </c>
       <c r="F20" s="1" t="n">
         <v>0.059716</v>
@@ -11429,6 +11596,12 @@
           <t>phase2</t>
         </is>
       </c>
+      <c r="I20" s="11" t="n"/>
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="11" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -11437,14 +11610,18 @@
       <c r="B21" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>6.248831</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>12.592237</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>0.165976</v>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>5.2×10⁴</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>4.6×10⁷</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="n">
         <v>0.060445</v>
@@ -11454,6 +11631,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -11462,14 +11645,18 @@
       <c r="B22" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>14.726772</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>47.756723</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>0.526387</v>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>1.2×10⁵</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>1.8×10⁸</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>83</v>
       </c>
       <c r="F22" s="1" t="n">
         <v>0.070782</v>
@@ -11479,6 +11666,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="11" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="11" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -11487,14 +11680,18 @@
       <c r="B23" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>25.55777</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>28.358274</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>0.705943</v>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>2.1×10⁵</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>1.0×10⁸</t>
+        </is>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>110</v>
       </c>
       <c r="F23" s="1" t="n">
         <v>0.07711800000000001</v>
@@ -11504,6 +11701,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="11" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -11512,14 +11715,18 @@
       <c r="B24" s="1" t="n">
         <v>26</v>
       </c>
-      <c r="C24" s="1" t="n">
-        <v>62.647707</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>13.264881</v>
-      </c>
-      <c r="E24" s="1" t="n">
-        <v>0.301923</v>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>5.2×10⁵</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>4.9×10⁷</t>
+        </is>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>48</v>
       </c>
       <c r="F24" s="1" t="n">
         <v>0.088184</v>
@@ -11529,6 +11736,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="11" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -11537,14 +11750,18 @@
       <c r="B25" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>1.694926</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>48.516168</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>0.079988</v>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>1.4×10⁴</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>1.8×10⁸</t>
+        </is>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="n">
         <v>0.100601</v>
@@ -11554,6 +11771,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -11562,14 +11785,18 @@
       <c r="B26" s="1" t="n">
         <v>28</v>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>50.313013</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>39.610909</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>1.082887</v>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>4.2×10⁵</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>1.5×10⁸</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>170</v>
       </c>
       <c r="F26" s="1" t="n">
         <v>0.100613</v>
@@ -11579,6 +11806,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="11" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -11587,14 +11820,18 @@
       <c r="B27" s="1" t="n">
         <v>27</v>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>21.406276</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>20.22353</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>0.820634</v>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>1.8×10⁵</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>7.4×10⁷</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="n">
+        <v>130</v>
       </c>
       <c r="F27" s="1" t="n">
         <v>0.112077</v>
@@ -11604,6 +11841,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -11612,14 +11855,18 @@
       <c r="B28" s="1" t="n">
         <v>29</v>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>75.720311</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>22.601489</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>0.222116</v>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>6.3×10⁵</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>8.3×10⁷</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="n">
+        <v>35</v>
       </c>
       <c r="F28" s="1" t="n">
         <v>0.112735</v>
@@ -11629,6 +11876,12 @@
           <t>phase3</t>
         </is>
       </c>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="11" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -11637,14 +11890,18 @@
       <c r="B29" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>19.536874</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>20.009222</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>0.887589</v>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>1.6×10⁵</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>7.4×10⁷</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>140</v>
       </c>
       <c r="F29" s="1" t="n">
         <v>0.126677</v>
@@ -11654,6 +11911,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I29" s="11" t="n"/>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -11662,14 +11925,18 @@
       <c r="B30" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="1" t="n">
-        <v>32.64415</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>24.529234</v>
-      </c>
-      <c r="E30" s="1" t="n">
-        <v>0.060249</v>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>2.7×10⁵</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>9.0×10⁷</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="n">
+        <v>9.5</v>
       </c>
       <c r="F30" s="1" t="n">
         <v>0.154122</v>
@@ -11679,6 +11946,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -11687,14 +11960,18 @@
       <c r="B31" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="C31" s="1" t="n">
-        <v>2.937196</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>65.546769</v>
-      </c>
-      <c r="E31" s="1" t="n">
-        <v>0.462952</v>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>2.5×10⁴</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>2.4×10⁸</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="n">
+        <v>73</v>
       </c>
       <c r="F31" s="1" t="n">
         <v>0.160994</v>
@@ -11704,6 +11981,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -11712,14 +11995,18 @@
       <c r="B32" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C32" s="1" t="n">
-        <v>67.991682</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>8.613716999999999</v>
-      </c>
-      <c r="E32" s="1" t="n">
-        <v>2.508756</v>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>5.7×10⁵</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>3.2×10⁷</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="n">
+        <v>400</v>
       </c>
       <c r="F32" s="1" t="n">
         <v>0.206768</v>
@@ -11729,6 +12016,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="11" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -11737,14 +12030,18 @@
       <c r="B33" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C33" s="1" t="n">
-        <v>24.90597</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>78.122794</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>2.136741</v>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>2.1×10⁵</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>2.9×10⁸</t>
+        </is>
+      </c>
+      <c r="E33" s="12" t="n">
+        <v>340</v>
       </c>
       <c r="F33" s="1" t="n">
         <v>0.260444</v>
@@ -11754,6 +12051,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I33" s="11" t="n"/>
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="11" t="n"/>
+      <c r="L33" s="11" t="n"/>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -11762,14 +12065,18 @@
       <c r="B34" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C34" s="1" t="n">
-        <v>9.864005000000001</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>15.319409</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>1.322114</v>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>8.2×10⁴</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>5.6×10⁷</t>
+        </is>
+      </c>
+      <c r="E34" s="12" t="n">
+        <v>210</v>
       </c>
       <c r="F34" s="1" t="n">
         <v>0.276129</v>
@@ -11779,6 +12086,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I34" s="11" t="n"/>
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="11" t="n"/>
+      <c r="N34" s="11" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -11787,14 +12100,18 @@
       <c r="B35" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C35" s="1" t="n">
-        <v>83.562388</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>34.156142</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>4.493303</v>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>7.0×10⁵</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>1.3×10⁸</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="n">
+        <v>710</v>
       </c>
       <c r="F35" s="1" t="n">
         <v>0.307616</v>
@@ -11804,6 +12121,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="11" t="n"/>
+      <c r="L35" s="11" t="n"/>
+      <c r="M35" s="11" t="n"/>
+      <c r="N35" s="11" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -11812,14 +12135,18 @@
       <c r="B36" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="C36" s="1" t="n">
-        <v>1.212982</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>7.744136</v>
-      </c>
-      <c r="E36" s="1" t="n">
-        <v>0.730585</v>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>1.0×10⁴</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>2.9×10⁷</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="n">
+        <v>120</v>
       </c>
       <c r="F36" s="1" t="n">
         <v>0.320861</v>
@@ -11829,6 +12156,12 @@
           <t>global</t>
         </is>
       </c>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11847,7 +12180,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 7a,b</t>
+          <t>Supplementary Figure 9a,b</t>
         </is>
       </c>
     </row>
@@ -11858,7 +12191,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -15790,7 +16122,6 @@
         <v>3.411422</v>
       </c>
     </row>
-    <row r="175"/>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
@@ -15885,7 +16216,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 7c,d</t>
+          <t>Supplementary Figure 9c,d</t>
         </is>
       </c>
     </row>
@@ -15896,7 +16227,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -16042,7 +16372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -16051,85 +16381,94 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Table S1</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Limiting regimes of the interfacial oxygen flux.</t>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched literature mass-loss measurements and was adopted in the final model.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regime</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Condition</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Interfacial flux J_O2</t>
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>RMSE (%)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Reaction-controlled</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Da &lt;&lt; 1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>k_ORR C_b</t>
-        </is>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Hard minimum</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.0568</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Transition</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Da ~ 1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>C_b/(1/k_ORR + delta/D_O2,eff)</t>
-        </is>
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Mixed control</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0.077</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Diffusion-controlled</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Da &gt;&gt; 1</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>D_O2,eff C_b/delta</t>
-        </is>
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Hybrid cathodic</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>0.0766</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Coupled ORR (no O2 cap)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>0.2983</v>
       </c>
     </row>
   </sheetData>
@@ -16162,7 +16501,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh.</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh (21.25 million elements).</t>
         </is>
       </c>
     </row>
@@ -16189,114 +16528,114 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>L1 (Very Low)</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="9" t="n">
         <v>182768</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.3009</v>
-      </c>
-      <c r="D5" t="n">
-        <v>87.2</v>
+      <c r="C5" s="7" t="n">
+        <v>1.439</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>1465.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>L2 (Low)</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.2029</v>
-      </c>
-      <c r="D6" t="n">
-        <v>26.2</v>
+      <c r="C6" s="6" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>441.6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>L3 (Medium)</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="9" t="n">
         <v>3454723</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.1682</v>
-      </c>
-      <c r="D7" t="n">
-        <v>4.6</v>
+      <c r="C7" s="6" t="n">
+        <v>0.1633</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>77.7</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>L4 (High)</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="9" t="n">
         <v>4990080</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.1637</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.8</v>
+      <c r="C8" s="6" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>31.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>L5 (Very High)</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="9" t="n">
         <v>11958220</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.1616</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5</v>
+      <c r="C9" s="6" t="n">
+        <v>0.1002</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>L6 (Ultra High)</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="9" t="n">
         <v>18864900</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.1611</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.19</v>
+      <c r="C10" s="6" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>0.87</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="9" t="n">
         <v>21245850</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.1608</v>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C11" s="6" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="D11" s="1" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -16333,7 +16672,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison between an adaptive mesh and a uniform mesh (approximately 800,000 elements).</t>
+          <t>Comparison between adaptive and uniform meshes at approximately 800,000 elements.</t>
         </is>
       </c>
     </row>
@@ -16365,63 +16704,63 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Uniform Mesh</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>799000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="D5" t="n">
-        <v>77.90000000000001</v>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="B5" s="9" t="n">
+        <v>799520</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>2.8561</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3007.8</v>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Adaptive Mesh</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.2029</v>
-      </c>
-      <c r="D6" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.663</v>
+      <c r="C6" s="6" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>441.6</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>0.8532</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Reference Mesh</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="9" t="n">
         <v>21245850</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.1608</v>
-      </c>
-      <c r="D7" t="inlineStr">
+      <c r="C7" s="6" t="n">
+        <v>0.0919</v>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -16440,9 +16779,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="2" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16707,7 +17044,7 @@
       </c>
       <c r="B16" s="1" t="inlineStr">
         <is>
-          <t>37,399</t>
+          <t>802,365</t>
         </is>
       </c>
       <c r="C16" s="1" t="inlineStr">
@@ -16729,7 +17066,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[to update]</t>
+          <t>121,120</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -16751,7 +17088,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>0.5 mm</t>
+          <t>0.1 mm</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -16827,7 +17164,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>4 h</t>
+          <t>0.25 h</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -16902,7 +17239,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>50</v>
@@ -16919,7 +17256,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>[to update]</t>
+          <t>2,592</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -17029,7 +17366,7 @@
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>~20 min</t>
+          <t>2 h</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -17137,7 +17474,7 @@
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>Dirichlet (C_O2 = 3.5 mg L^-1)</t>
+          <t>Dirichlet</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -17203,7 +17540,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameters included in the Morris sensitivity analysis (the ranges might differ from calibration space as this was done prior to calibration of the model).</t>
+          <t>Parameters included in the Morris sensitivity analysis.</t>
         </is>
       </c>
     </row>
@@ -17805,7 +18142,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
+          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 3.0×10⁵ h⁻¹, k_d = 1.0×10⁸ mm⁶ g⁻² h⁻¹, k_ORR = 80 mm h⁻¹ (middle curves); low/high = 0.13×/3.3× (k_f), 0.2×/4× (k_d), 0.2×/5× (k_ORR).</t>
         </is>
       </c>
     </row>
@@ -17824,17 +18161,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 5</t>
+          <t>kf 4.0×10⁴</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 35</t>
+          <t>kf 3.0×10⁵</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 150</t>
+          <t>kf 1.0×10⁶</t>
         </is>
       </c>
     </row>
@@ -18448,17 +18785,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 2.0×10⁷</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 27</t>
+          <t>kd 1.0×10⁸</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 120</t>
+          <t>kd 4.0×10⁸</t>
         </is>
       </c>
     </row>
@@ -19072,17 +19409,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 16</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.5</t>
+          <t>kORR 80</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 2.5</t>
+          <t>kORR 400</t>
         </is>
       </c>
     </row>
@@ -20046,8 +20383,7 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -20598,7 +20934,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
+          <t>Corrosion-product saturation, F/Fmax (%), in one-at-a-time parameter sweeps of k_f (panel d), k_d (panel e), and k_ORR (panel f). Baseline: k_f = 3.0×10⁵ h⁻¹, k_d = 1.0×10⁸ mm⁶ g⁻² h⁻¹, k_ORR = 80 mm h⁻¹ (middle curves); low/high = 0.13×/3.3× (k_f), 0.2×/4× (k_d), 0.2×/5× (k_ORR).</t>
         </is>
       </c>
     </row>
@@ -20617,17 +20953,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 5</t>
+          <t>kf 4.0×10⁴</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 35</t>
+          <t>kf 3.0×10⁵</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 150</t>
+          <t>kf 1.0×10⁶</t>
         </is>
       </c>
     </row>
@@ -21241,17 +21577,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 2.0×10⁷</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 27</t>
+          <t>kd 1.0×10⁸</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 120</t>
+          <t>kd 4.0×10⁸</t>
         </is>
       </c>
     </row>
@@ -21865,17 +22201,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 16</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.5</t>
+          <t>kORR 80</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 2.5</t>
+          <t>kORR 400</t>
         </is>
       </c>
     </row>
@@ -22505,7 +22841,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 35, k_d = 27, k_ORR = 0.5 (middle curves).</t>
+          <t>Interfacial dissolved oxygen concentration response (mg/L) to one-at-a-time parameter sweeps of k_f (panel g), k_d (panel h), and k_ORR (panel i). Baseline: k_f = 3.0×10⁵ h⁻¹, k_d = 1.0×10⁸ mm⁶ g⁻² h⁻¹, k_ORR = 80 mm h⁻¹ (middle curves); low/high = 0.13×/3.3× (k_f), 0.2×/4× (k_d), 0.2×/5× (k_ORR).</t>
         </is>
       </c>
     </row>
@@ -22524,17 +22860,17 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>kf 5</t>
+          <t>kf 4.0×10⁴</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>kf 35</t>
+          <t>kf 3.0×10⁵</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>kf 150</t>
+          <t>kf 1.0×10⁶</t>
         </is>
       </c>
     </row>
@@ -23148,17 +23484,17 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>kd 5</t>
+          <t>kd 2.0×10⁷</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
         <is>
-          <t>kd 27</t>
+          <t>kd 1.0×10⁸</t>
         </is>
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>kd 120</t>
+          <t>kd 4.0×10⁸</t>
         </is>
       </c>
     </row>
@@ -23772,17 +24108,17 @@
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.1</t>
+          <t>kORR 16</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
         <is>
-          <t>kORR 0.5</t>
+          <t>kORR 80</t>
         </is>
       </c>
       <c r="D96" s="1" t="inlineStr">
         <is>
-          <t>kORR 2.5</t>
+          <t>kORR 400</t>
         </is>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -27,18 +27,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9a,b" sheetId="20" state="visible" r:id="rId20"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9c,d" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S4" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S5" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S6" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S7" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S8" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S9" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S10" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S11" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S12" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 10a" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 10b" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S2" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S3" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S4" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S5" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S6" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S7" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S8" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S9" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S10" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S11" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S12" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16372,6 +16374,5363 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E173"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Figure 10a</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Predicted mass loss (%) of the disc over 672 h for different oxygen-replenishing boundaries: no replenishing boundary (None), top and bottom faces, side faces, and all faces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Top &amp; Bottom</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Sides</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.00739838</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00739838</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.00739838</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.00739838</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.014748</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0165542</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.0161191</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.0166576</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.0208485</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.0251473</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.024112</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0.0251702</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.026298</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.0337245</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.0325258</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.0338126</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.0301527</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.0404147</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0.0386458</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0.0405878</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0330137</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0.0467903</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.0441267</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0.0470415</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.0349797</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.0525307</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0.0492566</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0.0527313</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.0376152</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.0598082</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.0564412</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0.0599843</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.0395924</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.06680270000000001</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0.0635019</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.0670861</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.0414083</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.0739945</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.0700518</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>0.0741213</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.0432497</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.0805698</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0.0757828</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>0.0806838</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.0446178</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.0870015</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.08188819999999999</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.087545</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.0457829</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.09423819999999999</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0.088931</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.0946496</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.0470602</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0.100317</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0.0955652</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>0.100848</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.0476692</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0.106748</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0.101344</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>0.107302</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.0484642</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.113703</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0.106782</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>0.114331</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.0491334</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>0.120221</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.113142</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>0.120739</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>0.0496934</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0.125903</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0.119572</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>0.126467</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>0.0502848</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0.132828</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0.126362</v>
+      </c>
+      <c r="E24" s="1" t="n">
+        <v>0.133576</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>0.0506912</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>0.138844</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>0.13182</v>
+      </c>
+      <c r="E25" s="1" t="n">
+        <v>0.139751</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>0.0511351</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>0.145284</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0.137778</v>
+      </c>
+      <c r="E26" s="1" t="n">
+        <v>0.146322</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.0513635</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0.151123</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0.143454</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>0.152185</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.0514806</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>0.157224</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="E28" s="1" t="n">
+        <v>0.158055</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>0.0517267</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>0.163975</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0.154928</v>
+      </c>
+      <c r="E29" s="1" t="n">
+        <v>0.164697</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>0.0519545</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>0.1695</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0.159679</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0.170498</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>0.0521936</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>0.17559</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0.1649</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0.176638</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>0.0522735</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>0.181495</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>0.17026</v>
+      </c>
+      <c r="E32" s="1" t="n">
+        <v>0.182491</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.0523843</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>0.187095</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>0.175268</v>
+      </c>
+      <c r="E33" s="1" t="n">
+        <v>0.188128</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.0524561</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>0.192592</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0.18008</v>
+      </c>
+      <c r="E34" s="1" t="n">
+        <v>0.193784</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>0.0525776</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>0.198208</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.185342</v>
+      </c>
+      <c r="E35" s="1" t="n">
+        <v>0.199358</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.0527631</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>0.203363</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.190358</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>0.204684</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.0528216</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>0.208264</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.194506</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0.209672</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.0528644</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>0.213002</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.199417</v>
+      </c>
+      <c r="E38" s="1" t="n">
+        <v>0.214507</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>0.0529001</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>0.217901</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0.203762</v>
+      </c>
+      <c r="E39" s="1" t="n">
+        <v>0.219212</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>0.0529504</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>0.222492</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>0.208432</v>
+      </c>
+      <c r="E40" s="1" t="n">
+        <v>0.223733</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>0.0530092</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>0.226768</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0.212835</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>0.228024</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>0.053076</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>0.231038</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0.217319</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>0.232616</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0.0531126</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>0.235281</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>0.221577</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>0.237247</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>0.0531681</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>0.239667</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>0.225151</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>0.241403</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>0.0531681</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>0.244086</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0.228293</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>0.24608</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>0.0532255</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>0.248381</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0.231695</v>
+      </c>
+      <c r="E46" s="1" t="n">
+        <v>0.250087</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.0532501</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>0.252126</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0.235416</v>
+      </c>
+      <c r="E47" s="1" t="n">
+        <v>0.253914</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>0.0533107</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>0.256199</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>0.239554</v>
+      </c>
+      <c r="E48" s="1" t="n">
+        <v>0.257725</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.0533361</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>0.2598</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0.242531</v>
+      </c>
+      <c r="E49" s="1" t="n">
+        <v>0.261473</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>0.0533361</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>0.263328</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>0.245636</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>0.264846</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>0.0533361</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>0.267015</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>0.248665</v>
+      </c>
+      <c r="E51" s="1" t="n">
+        <v>0.268375</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>0.0533604</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>0.270189</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>0.251775</v>
+      </c>
+      <c r="E52" s="1" t="n">
+        <v>0.271521</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>0.0533604</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>0.27339</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>0.255139</v>
+      </c>
+      <c r="E53" s="1" t="n">
+        <v>0.274718</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>0.0534456</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>0.258149</v>
+      </c>
+      <c r="E54" s="1" t="n">
+        <v>0.277895</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>0.0534456</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>0.260711</v>
+      </c>
+      <c r="E55" s="1" t="n">
+        <v>0.280743</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>0.0534456</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>0.282258</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>0.263429</v>
+      </c>
+      <c r="E56" s="1" t="n">
+        <v>0.283353</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>0.0534456</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>0.284916</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0.265809</v>
+      </c>
+      <c r="E57" s="1" t="n">
+        <v>0.285885</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>0.0534606</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>0.287383</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>0.268206</v>
+      </c>
+      <c r="E58" s="1" t="n">
+        <v>0.288346</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>0.0534606</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>0.290377</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>0.270314</v>
+      </c>
+      <c r="E59" s="1" t="n">
+        <v>0.291289</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>0.292638</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>0.272483</v>
+      </c>
+      <c r="E60" s="1" t="n">
+        <v>0.293686</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>0.294851</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>0.274591</v>
+      </c>
+      <c r="E61" s="1" t="n">
+        <v>0.29618</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>0.297883</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>0.276619</v>
+      </c>
+      <c r="E62" s="1" t="n">
+        <v>0.298828</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>0.278803</v>
+      </c>
+      <c r="E63" s="1" t="n">
+        <v>0.301005</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>0.302559</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>0.280612</v>
+      </c>
+      <c r="E64" s="1" t="n">
+        <v>0.303304</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0.0535543</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>0.304429</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0.282914</v>
+      </c>
+      <c r="E65" s="1" t="n">
+        <v>0.305397</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>0.0536411</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="E66" s="1" t="n">
+        <v>0.307611</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>0.0536726</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0.287555</v>
+      </c>
+      <c r="E67" s="1" t="n">
+        <v>0.309744</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>0.0536793</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>0.310694</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0.289046</v>
+      </c>
+      <c r="E68" s="1" t="n">
+        <v>0.311898</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>0.0536877</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>0.312622</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0.290918</v>
+      </c>
+      <c r="E69" s="1" t="n">
+        <v>0.313771</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>0.0537024</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>0.292657</v>
+      </c>
+      <c r="E70" s="1" t="n">
+        <v>0.315738</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>0.0537024</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>0.316404</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>0.293996</v>
+      </c>
+      <c r="E71" s="1" t="n">
+        <v>0.31754</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>0.318324</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0.295643</v>
+      </c>
+      <c r="E72" s="1" t="n">
+        <v>0.319105</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>0.319915</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0.297412</v>
+      </c>
+      <c r="E73" s="1" t="n">
+        <v>0.320855</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>0.321786</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0.299133</v>
+      </c>
+      <c r="E74" s="1" t="n">
+        <v>0.32257</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>0.323675</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>0.300811</v>
+      </c>
+      <c r="E75" s="1" t="n">
+        <v>0.324446</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>0.325059</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0.302306</v>
+      </c>
+      <c r="E76" s="1" t="n">
+        <v>0.326004</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>0.0537641</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>0.326796</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0.303863</v>
+      </c>
+      <c r="E77" s="1" t="n">
+        <v>0.327825</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>0.328481</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0.305691</v>
+      </c>
+      <c r="E78" s="1" t="n">
+        <v>0.329591</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>0.330522</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0.307426</v>
+      </c>
+      <c r="E79" s="1" t="n">
+        <v>0.331513</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>0.331865</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0.309051</v>
+      </c>
+      <c r="E80" s="1" t="n">
+        <v>0.333212</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>0.333823</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0.310642</v>
+      </c>
+      <c r="E81" s="1" t="n">
+        <v>0.334924</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>0.335366</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0.312358</v>
+      </c>
+      <c r="E82" s="1" t="n">
+        <v>0.33639</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>0.053828</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>0.336924</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0.313905</v>
+      </c>
+      <c r="E83" s="1" t="n">
+        <v>0.337993</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>0.338649</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0.315644</v>
+      </c>
+      <c r="E84" s="1" t="n">
+        <v>0.339622</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>0.339894</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>0.317214</v>
+      </c>
+      <c r="E85" s="1" t="n">
+        <v>0.340915</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>0.318357</v>
+      </c>
+      <c r="E86" s="1" t="n">
+        <v>0.342347</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>328</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>0.342933</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>0.319919</v>
+      </c>
+      <c r="E87" s="1" t="n">
+        <v>0.344037</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>0.344704</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0.321349</v>
+      </c>
+      <c r="E88" s="1" t="n">
+        <v>0.345652</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>0.0538916</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>0.346151</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="E89" s="1" t="n">
+        <v>0.347151</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>0.347564</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0.323856</v>
+      </c>
+      <c r="E90" s="1" t="n">
+        <v>0.348458</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>344</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>0.348884</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0.325193</v>
+      </c>
+      <c r="E91" s="1" t="n">
+        <v>0.350032</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>348</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>0.350069</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0.326685</v>
+      </c>
+      <c r="E92" s="1" t="n">
+        <v>0.351242</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>352</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>0.351593</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>0.327835</v>
+      </c>
+      <c r="E93" s="1" t="n">
+        <v>0.352692</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>356</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>0.353015</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="E94" s="1" t="n">
+        <v>0.35421</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>0.0539837</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>0.354346</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>0.330137</v>
+      </c>
+      <c r="E95" s="1" t="n">
+        <v>0.355563</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>364</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>0.355786</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>0.331171</v>
+      </c>
+      <c r="E96" s="1" t="n">
+        <v>0.356694</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>368</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>0.357217</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>0.332592</v>
+      </c>
+      <c r="E97" s="1" t="n">
+        <v>0.358069</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>372</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>0.358485</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>0.333789</v>
+      </c>
+      <c r="E98" s="1" t="n">
+        <v>0.359322</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>0.359556</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="E99" s="1" t="n">
+        <v>0.36046</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>0.360953</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>0.336106</v>
+      </c>
+      <c r="E100" s="1" t="n">
+        <v>0.361659</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>0.0540601</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>0.362024</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>0.337338</v>
+      </c>
+      <c r="E101" s="1" t="n">
+        <v>0.362674</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>0.3631</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>0.338508</v>
+      </c>
+      <c r="E102" s="1" t="n">
+        <v>0.363965</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>0.364446</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>0.339496</v>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>0.365151</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>396</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>0.340436</v>
+      </c>
+      <c r="E104" s="1" t="n">
+        <v>0.366228</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>0.366657</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>0.341504</v>
+      </c>
+      <c r="E105" s="1" t="n">
+        <v>0.367254</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>0.367974</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>0.342369</v>
+      </c>
+      <c r="E106" s="1" t="n">
+        <v>0.368585</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>0.0541538</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>0.369168</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>0.343515</v>
+      </c>
+      <c r="E107" s="1" t="n">
+        <v>0.369807</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>0.370304</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>0.344623</v>
+      </c>
+      <c r="E108" s="1" t="n">
+        <v>0.370963</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>0.371482</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>0.345732</v>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>0.372119</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>0.372314</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>0.346782</v>
+      </c>
+      <c r="E110" s="1" t="n">
+        <v>0.373046</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>0.373482</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>0.347649</v>
+      </c>
+      <c r="E111" s="1" t="n">
+        <v>0.37412</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>428</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>0.374478</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>0.348726</v>
+      </c>
+      <c r="E112" s="1" t="n">
+        <v>0.375181</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>432</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>0.0542335</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>0.375468</v>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>0.349841</v>
+      </c>
+      <c r="E113" s="1" t="n">
+        <v>0.376322</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>436</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>0.376392</v>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>0.350782</v>
+      </c>
+      <c r="E114" s="1" t="n">
+        <v>0.377353</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>0.351697</v>
+      </c>
+      <c r="E115" s="1" t="n">
+        <v>0.378669</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>0.378423</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>0.352711</v>
+      </c>
+      <c r="E116" s="1" t="n">
+        <v>0.379435</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>448</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>0.37948</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>0.353494</v>
+      </c>
+      <c r="E117" s="1" t="n">
+        <v>0.380591</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>452</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>0.380504</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>0.354286</v>
+      </c>
+      <c r="E118" s="1" t="n">
+        <v>0.38156</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>456</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>0.0542809</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>0.381452</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>0.355093</v>
+      </c>
+      <c r="E119" s="1" t="n">
+        <v>0.382526</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>0.382533</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>0.355921</v>
+      </c>
+      <c r="E120" s="1" t="n">
+        <v>0.38359</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>464</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>0.383339</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>0.356779</v>
+      </c>
+      <c r="E121" s="1" t="n">
+        <v>0.38431</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>468</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>0.384079</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>0.357626</v>
+      </c>
+      <c r="E122" s="1" t="n">
+        <v>0.38519</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>472</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>0.384927</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0.358621</v>
+      </c>
+      <c r="E123" s="1" t="n">
+        <v>0.386143</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>476</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>0.38598</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>0.359741</v>
+      </c>
+      <c r="E124" s="1" t="n">
+        <v>0.387167</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>0.0543135</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>0.386747</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>0.360588</v>
+      </c>
+      <c r="E125" s="1" t="n">
+        <v>0.388065</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>484</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>0.387723</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0.361292</v>
+      </c>
+      <c r="E126" s="1" t="n">
+        <v>0.389029</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>488</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>0.388555</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="E127" s="1" t="n">
+        <v>0.390196</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>492</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>0.389722</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>0.363357</v>
+      </c>
+      <c r="E128" s="1" t="n">
+        <v>0.390967</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>496</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>0.390494</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0.364178</v>
+      </c>
+      <c r="E129" s="1" t="n">
+        <v>0.391742</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>0.391302</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>0.365076</v>
+      </c>
+      <c r="E130" s="1" t="n">
+        <v>0.39269</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>0.0543835</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>0.391995</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>0.365919</v>
+      </c>
+      <c r="E131" s="1" t="n">
+        <v>0.393298</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>508</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>0.392737</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>0.367029</v>
+      </c>
+      <c r="E132" s="1" t="n">
+        <v>0.393898</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>0.393374</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>0.367667</v>
+      </c>
+      <c r="E133" s="1" t="n">
+        <v>0.394658</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>516</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>0.394277</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0.368394</v>
+      </c>
+      <c r="E134" s="1" t="n">
+        <v>0.395408</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>520</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>0.395096</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>0.369122</v>
+      </c>
+      <c r="E135" s="1" t="n">
+        <v>0.396181</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>524</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>0.395714</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>0.369643</v>
+      </c>
+      <c r="E136" s="1" t="n">
+        <v>0.396985</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>528</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>0.0545111</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>0.396442</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>0.37042</v>
+      </c>
+      <c r="E137" s="1" t="n">
+        <v>0.397903</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>532</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>0.397352</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>0.371378</v>
+      </c>
+      <c r="E138" s="1" t="n">
+        <v>0.398691</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>536</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>0.398227</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0.371993</v>
+      </c>
+      <c r="E139" s="1" t="n">
+        <v>0.39947</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>540</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>0.398902</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>0.372742</v>
+      </c>
+      <c r="E140" s="1" t="n">
+        <v>0.400433</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>544</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>0.399638</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>0.373662</v>
+      </c>
+      <c r="E141" s="1" t="n">
+        <v>0.401422</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>548</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>0.400744</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>0.374241</v>
+      </c>
+      <c r="E142" s="1" t="n">
+        <v>0.402328</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>552</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>0.0545843</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>0.401545</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>0.375049</v>
+      </c>
+      <c r="E143" s="1" t="n">
+        <v>0.402831</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>556</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>0.402227</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>0.375676</v>
+      </c>
+      <c r="E144" s="1" t="n">
+        <v>0.403662</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>560</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>0.403075</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>0.376687</v>
+      </c>
+      <c r="E145" s="1" t="n">
+        <v>0.404412</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>564</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>0.403762</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>0.37734</v>
+      </c>
+      <c r="E146" s="1" t="n">
+        <v>0.405186</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>568</v>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>0.404578</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>0.378342</v>
+      </c>
+      <c r="E147" s="1" t="n">
+        <v>0.406188</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>572</v>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>0.405403</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>0.379194</v>
+      </c>
+      <c r="E148" s="1" t="n">
+        <v>0.407026</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>576</v>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>0.0547533</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>0.406244</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>0.379911</v>
+      </c>
+      <c r="E149" s="1" t="n">
+        <v>0.407851</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>0.407027</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>0.380462</v>
+      </c>
+      <c r="E150" s="1" t="n">
+        <v>0.408395</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>584</v>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>0.408248</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>0.381162</v>
+      </c>
+      <c r="E151" s="1" t="n">
+        <v>0.40913</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>588</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>0.408913</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>0.38189</v>
+      </c>
+      <c r="E152" s="1" t="n">
+        <v>0.40975</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>592</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>0.409535</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>0.382612</v>
+      </c>
+      <c r="E153" s="1" t="n">
+        <v>0.410579</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>596</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>0.383522</v>
+      </c>
+      <c r="E154" s="1" t="n">
+        <v>0.411375</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>0.0548521</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>0.411167</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>0.384191</v>
+      </c>
+      <c r="E155" s="1" t="n">
+        <v>0.412259</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>604</v>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>0.41182</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>0.384939</v>
+      </c>
+      <c r="E156" s="1" t="n">
+        <v>0.41305</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>608</v>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>0.412694</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>0.385667</v>
+      </c>
+      <c r="E157" s="1" t="n">
+        <v>0.413836</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>612</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>0.413555</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>0.386286</v>
+      </c>
+      <c r="E158" s="1" t="n">
+        <v>0.414556</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>616</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>0.414393</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>0.386781</v>
+      </c>
+      <c r="E159" s="1" t="n">
+        <v>0.415441</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>620</v>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>0.415049</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>0.387644</v>
+      </c>
+      <c r="E160" s="1" t="n">
+        <v>0.416026</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>624</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>0.0549281</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>0.415693</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>0.388371</v>
+      </c>
+      <c r="E161" s="1" t="n">
+        <v>0.416894</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>628</v>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>0.416488</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>0.389023</v>
+      </c>
+      <c r="E162" s="1" t="n">
+        <v>0.417617</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>632</v>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>0.417153</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>0.389744</v>
+      </c>
+      <c r="E163" s="1" t="n">
+        <v>0.418447</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>636</v>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>0.418027</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>0.39054</v>
+      </c>
+      <c r="E164" s="1" t="n">
+        <v>0.419414</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>640</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>0.418974</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>0.39131</v>
+      </c>
+      <c r="E165" s="1" t="n">
+        <v>0.42018</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>644</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>0.419781</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>0.391828</v>
+      </c>
+      <c r="E166" s="1" t="n">
+        <v>0.420745</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>648</v>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>0.0550231</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>0.420448</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>0.392357</v>
+      </c>
+      <c r="E167" s="1" t="n">
+        <v>0.421707</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>652</v>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>0.42124</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>0.393322</v>
+      </c>
+      <c r="E168" s="1" t="n">
+        <v>0.422742</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>656</v>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>0.421935</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>0.394003</v>
+      </c>
+      <c r="E169" s="1" t="n">
+        <v>0.423322</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>660</v>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>0.422686</v>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>0.394675</v>
+      </c>
+      <c r="E170" s="1" t="n">
+        <v>0.423963</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>0.423411</v>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>0.395337</v>
+      </c>
+      <c r="E171" s="1" t="n">
+        <v>0.424391</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>668</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>0.42393</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>0.396082</v>
+      </c>
+      <c r="E172" s="1" t="n">
+        <v>0.425191</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>672</v>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>0.055154</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>0.424432</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>0.396889</v>
+      </c>
+      <c r="E173" s="1" t="n">
+        <v>0.425725</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D173"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Supplementary Figure 10b</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Predicted mass loss (%) of the disc over 672 h for initial dissolved-oxygen concentrations of 1.5, 5.5 and 7.5 mg/L (1.5, 5.5 and 7.5 × 10⁻⁹ g mm⁻³).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Time (h)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>O2 initial = 1.5×10⁻⁹ g mm⁻³</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>O2 initial = 5.5×10⁻⁹ g mm⁻³</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>O2 initial = 7.5×10⁻⁹ g mm⁻³</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.00383607</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.0140649</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.019179</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.00749848</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0275049</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.0375142</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.0111991</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.041089</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.0560477</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.0148394</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.054463</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.0743026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.0181371</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.0665873</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0.0908583</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.0210151</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0.0771367</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.105242</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.0237618</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.0871939</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0.118947</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.0264419</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.0970036</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.132312</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.0290693</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.106619</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0.145412</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.0316466</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.11605</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.158261</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.0341743</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.1253</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0.170861</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.0366519</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.134366</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.183213</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.039079</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.143249</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0.195315</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.0414553</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0.151946</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0.207165</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.0437803</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0.160457</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0.218762</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.0460537</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.16878</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0.230106</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.0482751</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>0.176915</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.241194</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>0.0504441</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0.184861</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0.252026</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>0.0525606</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0.192617</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0.262602</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>0.0546242</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>0.200183</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>0.27292</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>0.0566348</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>0.207557</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0.28298</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.0585922</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0.21474</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0.292782</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.0604963</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>0.221732</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.302326</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>0.0623472</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>0.228532</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0.311613</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>0.0641448</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>0.235142</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0.320643</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>0.0658894</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>0.241561</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0.329416</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>0.067581</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>0.247792</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>0.337935</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.06922010000000001</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>0.253833</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>0.346201</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.07080690000000001</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>0.259689</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0.354216</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>0.07234210000000001</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>0.265359</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.361983</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.073826</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>0.270847</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.369504</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.07525949999999999</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>0.276154</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.376783</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.0766433</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>0.281284</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.383824</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>0.0779782</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>0.286239</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0.39063</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>0.0792653</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>0.291024</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>0.397206</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>0.0805056</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>0.295641</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0.403557</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>0.08170040000000001</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>0.300096</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0.409689</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0.0828507</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>0.304391</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>0.415608</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>0.083958</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>0.308532</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>0.421319</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>0.08502369999999999</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>0.312524</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0.426829</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>0.0860493</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>0.316372</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0.432145</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.08703619999999999</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>0.320081</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0.437274</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>0.08798599999999999</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>0.323657</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>0.442223</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.08890049999999999</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>0.327106</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0.447</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B50" s="1" t="n">
+        <v>0.08978129999999999</v>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>0.330432</v>
+      </c>
+      <c r="D50" s="1" t="n">
+        <v>0.451612</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B51" s="1" t="n">
+        <v>0.09063</v>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>0.333643</v>
+      </c>
+      <c r="D51" s="1" t="n">
+        <v>0.456067</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>0.0914483</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>0.336743</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>0.460373</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>0.092238</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>0.33974</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>0.464538</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>0.09300079999999999</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>0.342639</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>0.46857</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>0.0937383</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>0.345446</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>0.472477</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>204</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>0.0944522</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>0.348166</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>0.476266</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>208</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>0.0951443</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>0.350806</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0.479946</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>212</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>0.095816</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>0.353371</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>0.483523</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>0.0964689</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>0.355868</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>0.487006</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>0.0971046</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>0.490402</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>224</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>0.09772450000000001</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>0.360674</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>0.493717</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>228</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>0.09833</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>0.362994</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>0.496959</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>232</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>0.0989225</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>0.365266</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>0.500133</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>236</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>0.0995032</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>0.367494</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>0.503247</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>240</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0.100073</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>0.369681</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0.506305</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>244</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>0.100634</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>0.371833</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>0.509314</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>248</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>0.101186</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>0.373953</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0.512278</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>252</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>0.101731</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>0.376045</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0.515202</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>256</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>0.10227</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>0.378112</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0.518092</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>260</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>0.102803</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>0.380157</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>0.5209510000000001</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>0.103331</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>0.382183</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>0.523783</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>0.103855</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>0.384192</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0.5265919999999999</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>272</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>0.104375</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>0.386188</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0.52938</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>276</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>0.104893</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>0.388172</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0.532152</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>280</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>0.105409</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>0.390146</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>0.534909</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>0.105923</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>0.392113</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0.537655</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>288</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>0.106435</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>0.394074</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0.540392</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>292</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>0.106947</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>0.396029</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0.543121</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>296</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>0.107458</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>0.397982</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0.545844</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>300</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>0.107969</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>0.399933</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0.5485640000000001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>304</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>0.108481</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>0.401882</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0.551281</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>308</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>0.108993</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>0.403832</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0.553997</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>312</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>0.109505</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>0.405783</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0.556713</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>316</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>0.110018</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>0.407735</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0.55943</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>320</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>0.110533</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>0.409689</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>0.56215</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>324</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>0.111048</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>0.411647</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>0.564871</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>328</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>0.111565</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>0.413607</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>0.567597</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>332</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>0.112083</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>0.415572</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0.570327</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>336</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>0.112603</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.57306</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>340</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>0.113125</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>0.419513</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0.5757989999999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>344</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>0.113648</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>0.421491</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0.5785439999999999</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>348</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>0.114173</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>0.423474</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0.5812929999999999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>352</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>0.1147</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>0.425462</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>0.584049</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>356</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>0.115228</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>0.427455</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>0.5868100000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>360</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>0.115759</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>0.429453</v>
+      </c>
+      <c r="D95" s="1" t="n">
+        <v>0.589578</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>364</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>0.116291</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>0.431457</v>
+      </c>
+      <c r="D96" s="1" t="n">
+        <v>0.592351</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>368</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>0.116825</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>0.433466</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>0.595132</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>372</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>0.117362</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>0.43548</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>0.5979179999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>376</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>0.1179</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>0.60071</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>380</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>0.118439</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>0.439525</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>0.603509</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>384</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>0.118981</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>0.441555</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>0.606314</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>388</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>0.119525</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>0.44359</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>0.609124</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>392</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>0.12007</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>0.445631</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>0.611941</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>396</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>0.120617</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>0.447677</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>0.6147629999999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>0.121166</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>0.449727</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>0.617591</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>404</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>0.121716</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>0.451783</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>0.620425</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>0.122269</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>0.453842</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>0.623264</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>412</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>0.122822</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>0.455907</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>0.626108</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>416</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>0.123378</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>0.457976</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>0.628957</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>420</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>0.123935</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>0.460049</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>0.631811</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>424</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>0.124493</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>0.462126</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>0.63467</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>428</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>0.125053</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>0.464208</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>0.637533</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>432</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>0.125614</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>0.466293</v>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>0.640401</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>436</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>0.126177</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>0.468382</v>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>0.643272</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>440</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>0.126741</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>0.470474</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>0.646147</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>444</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>0.127306</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>0.47257</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>0.649027</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>448</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>0.127873</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>0.474669</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>0.651909</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>452</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>0.12844</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>0.476771</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>0.654795</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>456</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>0.129009</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>0.478875</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>0.657683</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>460</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>0.129579</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>0.480983</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>0.660575</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>464</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>0.13015</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>0.483093</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>0.663469</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>468</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>0.130721</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>0.485206</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>0.666366</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>472</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>0.131294</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>0.487321</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0.669265</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>476</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>0.131868</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>0.489438</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>0.672166</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>480</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>0.132442</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>0.491557</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>0.675069</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>484</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>0.133017</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>0.493677</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0.677973</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>488</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>0.133594</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>0.680879</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>492</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>0.13417</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>0.497924</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>0.683787</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>496</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>0.134748</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>0.500049</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0.6866950000000001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>500</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>0.135326</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>0.502176</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>0.689604</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>504</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>0.135904</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>0.5043029999999999</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>0.692514</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>508</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>0.136484</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>0.506432</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>0.695425</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>512</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>0.137063</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>0.508561</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>0.698336</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>516</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>0.137643</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>0.510691</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0.701247</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>520</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>0.138224</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>0.512822</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>0.704158</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>524</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>0.138805</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>0.514953</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>0.7070689999999999</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>528</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>0.139386</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>0.517084</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>0.7099800000000001</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>532</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>0.139967</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>0.519215</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>0.71289</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>536</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>0.140549</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>0.521347</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0.7158</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>540</v>
+      </c>
+      <c r="B140" s="1" t="n">
+        <v>0.141131</v>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>0.523478</v>
+      </c>
+      <c r="D140" s="1" t="n">
+        <v>0.718709</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>544</v>
+      </c>
+      <c r="B141" s="1" t="n">
+        <v>0.141713</v>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>0.525609</v>
+      </c>
+      <c r="D141" s="1" t="n">
+        <v>0.721617</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>548</v>
+      </c>
+      <c r="B142" s="1" t="n">
+        <v>0.142296</v>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>0.52774</v>
+      </c>
+      <c r="D142" s="1" t="n">
+        <v>0.7245239999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>552</v>
+      </c>
+      <c r="B143" s="1" t="n">
+        <v>0.142878</v>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>0.52987</v>
+      </c>
+      <c r="D143" s="1" t="n">
+        <v>0.727429</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>556</v>
+      </c>
+      <c r="B144" s="1" t="n">
+        <v>0.143461</v>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="D144" s="1" t="n">
+        <v>0.730334</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>560</v>
+      </c>
+      <c r="B145" s="1" t="n">
+        <v>0.144043</v>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>0.534129</v>
+      </c>
+      <c r="D145" s="1" t="n">
+        <v>0.733237</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>564</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>0.144626</v>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>0.536258</v>
+      </c>
+      <c r="D146" s="1" t="n">
+        <v>0.736138</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>568</v>
+      </c>
+      <c r="B147" s="1" t="n">
+        <v>0.145208</v>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>0.538385</v>
+      </c>
+      <c r="D147" s="1" t="n">
+        <v>0.7390370000000001</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>572</v>
+      </c>
+      <c r="B148" s="1" t="n">
+        <v>0.145791</v>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>0.540512</v>
+      </c>
+      <c r="D148" s="1" t="n">
+        <v>0.741934</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>576</v>
+      </c>
+      <c r="B149" s="1" t="n">
+        <v>0.146373</v>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>0.542637</v>
+      </c>
+      <c r="D149" s="1" t="n">
+        <v>0.74483</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>580</v>
+      </c>
+      <c r="B150" s="1" t="n">
+        <v>0.146956</v>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>0.5447610000000001</v>
+      </c>
+      <c r="D150" s="1" t="n">
+        <v>0.747723</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>584</v>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>0.147538</v>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>0.546884</v>
+      </c>
+      <c r="D151" s="1" t="n">
+        <v>0.750614</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>588</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>0.549006</v>
+      </c>
+      <c r="D152" s="1" t="n">
+        <v>0.753503</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>592</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>0.148702</v>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>0.551126</v>
+      </c>
+      <c r="D153" s="1" t="n">
+        <v>0.756389</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>596</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>0.149283</v>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>0.553244</v>
+      </c>
+      <c r="D154" s="1" t="n">
+        <v>0.759273</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>600</v>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>0.149865</v>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>0.555361</v>
+      </c>
+      <c r="D155" s="1" t="n">
+        <v>0.762153</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>604</v>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>0.150446</v>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>0.557476</v>
+      </c>
+      <c r="D156" s="1" t="n">
+        <v>0.765031</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>608</v>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>0.151026</v>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>0.55959</v>
+      </c>
+      <c r="D157" s="1" t="n">
+        <v>0.767906</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>612</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>0.151607</v>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>0.561701</v>
+      </c>
+      <c r="D158" s="1" t="n">
+        <v>0.770778</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>616</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>0.152187</v>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>0.563811</v>
+      </c>
+      <c r="D159" s="1" t="n">
+        <v>0.773647</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>620</v>
+      </c>
+      <c r="B160" s="1" t="n">
+        <v>0.152766</v>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>0.565918</v>
+      </c>
+      <c r="D160" s="1" t="n">
+        <v>0.776512</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>624</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>0.153346</v>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>0.568024</v>
+      </c>
+      <c r="D161" s="1" t="n">
+        <v>0.779375</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>628</v>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>0.153924</v>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>0.5701270000000001</v>
+      </c>
+      <c r="D162" s="1" t="n">
+        <v>0.782234</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>632</v>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>0.154503</v>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>0.572227</v>
+      </c>
+      <c r="D163" s="1" t="n">
+        <v>0.785089</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>636</v>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>0.155081</v>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>0.574326</v>
+      </c>
+      <c r="D164" s="1" t="n">
+        <v>0.78794</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>640</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>0.155658</v>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>0.576422</v>
+      </c>
+      <c r="D165" s="1" t="n">
+        <v>0.790788</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>644</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>0.156235</v>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>0.578516</v>
+      </c>
+      <c r="D166" s="1" t="n">
+        <v>0.793633</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>648</v>
+      </c>
+      <c r="B167" s="1" t="n">
+        <v>0.156811</v>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>0.580607</v>
+      </c>
+      <c r="D167" s="1" t="n">
+        <v>0.796473</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>652</v>
+      </c>
+      <c r="B168" s="1" t="n">
+        <v>0.157387</v>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>0.582695</v>
+      </c>
+      <c r="D168" s="1" t="n">
+        <v>0.799309</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>656</v>
+      </c>
+      <c r="B169" s="1" t="n">
+        <v>0.157962</v>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>0.584781</v>
+      </c>
+      <c r="D169" s="1" t="n">
+        <v>0.802142</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>660</v>
+      </c>
+      <c r="B170" s="1" t="n">
+        <v>0.158537</v>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>0.5868640000000001</v>
+      </c>
+      <c r="D170" s="1" t="n">
+        <v>0.80497</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>664</v>
+      </c>
+      <c r="B171" s="1" t="n">
+        <v>0.159111</v>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>0.588944</v>
+      </c>
+      <c r="D171" s="1" t="n">
+        <v>0.807794</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>668</v>
+      </c>
+      <c r="B172" s="1" t="n">
+        <v>0.159684</v>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>0.591022</v>
+      </c>
+      <c r="D172" s="1" t="n">
+        <v>0.8106139999999999</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>672</v>
+      </c>
+      <c r="B173" s="1" t="n">
+        <v>0.160257</v>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>0.593096</v>
+      </c>
+      <c r="D173" s="1" t="n">
+        <v>0.81343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -16476,7 +21835,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16646,7 +22005,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16769,7 +22128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17515,7 +22874,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17747,7 +23106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17867,7 +23226,1914 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D139"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Figure 4a-c</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 3.0×10⁵ h⁻¹, k_d = 1.0×10⁸ mm⁶ g⁻² h⁻¹, k_ORR = 80 mm h⁻¹ (middle curves); low/high = 0.13×/3.3× (k_f), 0.2×/4× (k_d), 0.2×/5× (k_ORR).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Predicted mass loss with kinetic parameter sweep</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Time (hrs)</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>kf 4.0×10⁴</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>kf 3.0×10⁵</t>
+        </is>
+      </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>kf 1.0×10⁶</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.024554562</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>0.020944463</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.016104173</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.037217756</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.03174587</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>0.024409362</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.047468438</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>0.04048946</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0.031132298</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.056411569</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>0.048117741</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>0.036997674</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.06449323899999999</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.055011215</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>0.042298058</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.07194869800000001</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>0.061370546</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>0.047187739</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.078920715</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.067317512</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>0.051760355</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.08550395</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.072932857</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>0.056077987</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.091765132</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.078273497</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>0.060184399</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.09775347099999999</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.08338141</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>0.064111867</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.103506541</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.088288644</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>0.067885033</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.109053833</v>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>0.093020353</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>0.071523238</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.114419013</v>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>0.097596725</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>0.07504200599999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.119621435</v>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>0.102034269</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>0.078454028</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.124677172</v>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>0.106346693</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>0.08176984599999999</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>0.129599754</v>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>0.11054554</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>0.08499833399999999</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>0.134400703</v>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>0.114640636</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>0.08814704900000001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>0.13908993</v>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>0.118640437</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>0.091222491</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B26" s="1" t="n">
+        <v>0.143676039</v>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>0.12255228</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>0.094230302</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B27" s="1" t="n">
+        <v>0.148166555</v>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>0.126382584</v>
+      </c>
+      <c r="D27" s="1" t="n">
+        <v>0.097175419</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B28" s="1" t="n">
+        <v>0.152568109</v>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>0.130137006</v>
+      </c>
+      <c r="D28" s="1" t="n">
+        <v>0.100062189</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>0.15688658</v>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>0.13382056</v>
+      </c>
+      <c r="D29" s="1" t="n">
+        <v>0.102894469</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B30" s="1" t="n">
+        <v>0.16112721</v>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>0.137437718</v>
+      </c>
+      <c r="D30" s="1" t="n">
+        <v>0.105675698</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B31" s="1" t="n">
+        <v>0.165294701</v>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>0.14099249</v>
+      </c>
+      <c r="D31" s="1" t="n">
+        <v>0.108408957</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B32" s="1" t="n">
+        <v>0.169393285</v>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>0.144488486</v>
+      </c>
+      <c r="D32" s="1" t="n">
+        <v>0.111097025</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B33" s="1" t="n">
+        <v>0.173426794</v>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>0.147928973</v>
+      </c>
+      <c r="D33" s="1" t="n">
+        <v>0.113742411</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B34" s="1" t="n">
+        <v>0.177398705</v>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>0.15131692</v>
+      </c>
+      <c r="D34" s="1" t="n">
+        <v>0.1163474</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B35" s="1" t="n">
+        <v>0.181312191</v>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>0.154655031</v>
+      </c>
+      <c r="D35" s="1" t="n">
+        <v>0.118914069</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B36" s="1" t="n">
+        <v>0.185170153</v>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>0.157945782</v>
+      </c>
+      <c r="D36" s="1" t="n">
+        <v>0.121444324</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B37" s="1" t="n">
+        <v>0.188975255</v>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>0.161191444</v>
+      </c>
+      <c r="D37" s="1" t="n">
+        <v>0.12393991</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B38" s="1" t="n">
+        <v>0.192729947</v>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>0.164394109</v>
+      </c>
+      <c r="D38" s="1" t="n">
+        <v>0.126402435</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B39" s="1" t="n">
+        <v>0.196436494</v>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>0.167555706</v>
+      </c>
+      <c r="D39" s="1" t="n">
+        <v>0.128833383</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B40" s="1" t="n">
+        <v>0.200096987</v>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>0.170678021</v>
+      </c>
+      <c r="D40" s="1" t="n">
+        <v>0.131234127</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B41" s="1" t="n">
+        <v>0.203713372</v>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>0.173762711</v>
+      </c>
+      <c r="D41" s="1" t="n">
+        <v>0.133605942</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B42" s="1" t="n">
+        <v>0.207287452</v>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>0.176811318</v>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>0.135950012</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B43" s="1" t="n">
+        <v>0.210820912</v>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>0.179825276</v>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>0.13826744</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B44" s="1" t="n">
+        <v>0.214315322</v>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>0.182805925</v>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>0.140559258</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B45" s="1" t="n">
+        <v>0.217772153</v>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>0.185754521</v>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>0.14282643</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B46" s="1" t="n">
+        <v>0.221192782</v>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>0.188672237</v>
+      </c>
+      <c r="D46" s="1" t="n">
+        <v>0.145069858</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B47" s="1" t="n">
+        <v>0.224578502</v>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>0.191560177</v>
+      </c>
+      <c r="D47" s="1" t="n">
+        <v>0.147290392</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B48" s="1" t="n">
+        <v>0.22793053</v>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>0.194419377</v>
+      </c>
+      <c r="D48" s="1" t="n">
+        <v>0.149488828</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B49" s="1" t="n">
+        <v>0.23125001</v>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>0.197250816</v>
+      </c>
+      <c r="D49" s="1" t="n">
+        <v>0.151665918</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>Time (hrs)</t>
+        </is>
+      </c>
+      <c r="B51" s="1" t="inlineStr">
+        <is>
+          <t>kd 2.0×10⁷</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>kd 1.0×10⁸</t>
+        </is>
+      </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>kd 4.0×10⁸</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="n">
+        <v>0.017904039</v>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>0.020944463</v>
+      </c>
+      <c r="D53" s="1" t="n">
+        <v>0.024554562</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1" t="n">
+        <v>0.027137449</v>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>0.03174587</v>
+      </c>
+      <c r="D54" s="1" t="n">
+        <v>0.037217756</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>0.034611767</v>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>0.04048946</v>
+      </c>
+      <c r="D55" s="1" t="n">
+        <v>0.047468438</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>0.041132681</v>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>0.048117741</v>
+      </c>
+      <c r="D56" s="1" t="n">
+        <v>0.056411569</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>0.047025457</v>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>0.055011215</v>
+      </c>
+      <c r="D57" s="1" t="n">
+        <v>0.06449323899999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>0.052461629</v>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>0.061370546</v>
+      </c>
+      <c r="D58" s="1" t="n">
+        <v>0.07194869800000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>0.057545298</v>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>0.067317512</v>
+      </c>
+      <c r="D59" s="1" t="n">
+        <v>0.078920715</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>0.062345486</v>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>0.072932857</v>
+      </c>
+      <c r="D60" s="1" t="n">
+        <v>0.08550395</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>0.066910847</v>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>0.078273497</v>
+      </c>
+      <c r="D61" s="1" t="n">
+        <v>0.091765132</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B62" s="1" t="n">
+        <v>0.07127726400000001</v>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>0.08338141</v>
+      </c>
+      <c r="D62" s="1" t="n">
+        <v>0.09775347099999999</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B63" s="1" t="n">
+        <v>0.075472135</v>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>0.088288644</v>
+      </c>
+      <c r="D63" s="1" t="n">
+        <v>0.103506541</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B64" s="1" t="n">
+        <v>0.07951696</v>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>0.093020353</v>
+      </c>
+      <c r="D64" s="1" t="n">
+        <v>0.109053833</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B65" s="1" t="n">
+        <v>0.083428999</v>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>0.097596725</v>
+      </c>
+      <c r="D65" s="1" t="n">
+        <v>0.114419013</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B66" s="1" t="n">
+        <v>0.087222362</v>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>0.102034269</v>
+      </c>
+      <c r="D66" s="1" t="n">
+        <v>0.119621435</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="1" t="n">
+        <v>0.090908769</v>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>0.106346693</v>
+      </c>
+      <c r="D67" s="1" t="n">
+        <v>0.124677172</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="1" t="n">
+        <v>0.094498086</v>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>0.11054554</v>
+      </c>
+      <c r="D68" s="1" t="n">
+        <v>0.129599754</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1" t="n">
+        <v>0.097998714</v>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>0.114640636</v>
+      </c>
+      <c r="D69" s="1" t="n">
+        <v>0.134400703</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B70" s="1" t="n">
+        <v>0.101417879</v>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>0.118640437</v>
+      </c>
+      <c r="D70" s="1" t="n">
+        <v>0.13908993</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B71" s="1" t="n">
+        <v>0.104761856</v>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>0.12255228</v>
+      </c>
+      <c r="D71" s="1" t="n">
+        <v>0.143676039</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="n">
+        <v>0.10803613</v>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>0.126382584</v>
+      </c>
+      <c r="D72" s="1" t="n">
+        <v>0.148166555</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B73" s="1" t="n">
+        <v>0.111245538</v>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>0.130137006</v>
+      </c>
+      <c r="D73" s="1" t="n">
+        <v>0.152568109</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B74" s="1" t="n">
+        <v>0.114394365</v>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>0.13382056</v>
+      </c>
+      <c r="D74" s="1" t="n">
+        <v>0.15688658</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B75" s="1" t="n">
+        <v>0.117486434</v>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>0.137437718</v>
+      </c>
+      <c r="D75" s="1" t="n">
+        <v>0.16112721</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B76" s="1" t="n">
+        <v>0.120525174</v>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>0.14099249</v>
+      </c>
+      <c r="D76" s="1" t="n">
+        <v>0.165294701</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B77" s="1" t="n">
+        <v>0.12351367</v>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>0.144488486</v>
+      </c>
+      <c r="D77" s="1" t="n">
+        <v>0.169393285</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B78" s="1" t="n">
+        <v>0.126454716</v>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>0.147928973</v>
+      </c>
+      <c r="D78" s="1" t="n">
+        <v>0.173426794</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B79" s="1" t="n">
+        <v>0.129350848</v>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>0.15131692</v>
+      </c>
+      <c r="D79" s="1" t="n">
+        <v>0.177398705</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B80" s="1" t="n">
+        <v>0.132204379</v>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>0.154655031</v>
+      </c>
+      <c r="D80" s="1" t="n">
+        <v>0.181312191</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B81" s="1" t="n">
+        <v>0.135017425</v>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>0.157945782</v>
+      </c>
+      <c r="D81" s="1" t="n">
+        <v>0.185170153</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B82" s="1" t="n">
+        <v>0.137791927</v>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>0.161191444</v>
+      </c>
+      <c r="D82" s="1" t="n">
+        <v>0.188975255</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B83" s="1" t="n">
+        <v>0.140529674</v>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>0.164394109</v>
+      </c>
+      <c r="D83" s="1" t="n">
+        <v>0.192729947</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B84" s="1" t="n">
+        <v>0.143232314</v>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>0.167555706</v>
+      </c>
+      <c r="D84" s="1" t="n">
+        <v>0.196436494</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B85" s="1" t="n">
+        <v>0.145901375</v>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>0.170678021</v>
+      </c>
+      <c r="D85" s="1" t="n">
+        <v>0.200096987</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B86" s="1" t="n">
+        <v>0.148538274</v>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>0.173762711</v>
+      </c>
+      <c r="D86" s="1" t="n">
+        <v>0.203713372</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B87" s="1" t="n">
+        <v>0.151144326</v>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>0.176811318</v>
+      </c>
+      <c r="D87" s="1" t="n">
+        <v>0.207287452</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B88" s="1" t="n">
+        <v>0.15372076</v>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>0.179825276</v>
+      </c>
+      <c r="D88" s="1" t="n">
+        <v>0.210820912</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B89" s="1" t="n">
+        <v>0.156268721</v>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>0.182805925</v>
+      </c>
+      <c r="D89" s="1" t="n">
+        <v>0.214315322</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B90" s="1" t="n">
+        <v>0.15878928</v>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>0.185754521</v>
+      </c>
+      <c r="D90" s="1" t="n">
+        <v>0.217772153</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B91" s="1" t="n">
+        <v>0.161283443</v>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>0.188672237</v>
+      </c>
+      <c r="D91" s="1" t="n">
+        <v>0.221192782</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B92" s="1" t="n">
+        <v>0.163752152</v>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>0.191560177</v>
+      </c>
+      <c r="D92" s="1" t="n">
+        <v>0.224578502</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B93" s="1" t="n">
+        <v>0.166196294</v>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>0.194419377</v>
+      </c>
+      <c r="D93" s="1" t="n">
+        <v>0.22793053</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>0.168616704</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>0.197250816</v>
+      </c>
+      <c r="D94" s="1" t="n">
+        <v>0.23125001</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>Time (hrs)</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="inlineStr">
+        <is>
+          <t>kORR 16</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="inlineStr">
+        <is>
+          <t>kORR 80</t>
+        </is>
+      </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>kORR 400</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>0.002584384</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>0.025248274</v>
+      </c>
+      <c r="D98" s="1" t="n">
+        <v>0.14042038</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>0.004346399</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>0.036965637</v>
+      </c>
+      <c r="D99" s="1" t="n">
+        <v>0.185285802</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>0.005891123</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>0.046200682</v>
+      </c>
+      <c r="D100" s="1" t="n">
+        <v>0.217910745</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>0.007309743</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>0.054120861</v>
+      </c>
+      <c r="D101" s="1" t="n">
+        <v>0.244486082</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>0.00864141</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>0.061187851</v>
+      </c>
+      <c r="D102" s="1" t="n">
+        <v>0.26731181</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>0.009907648</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>0.067641758</v>
+      </c>
+      <c r="D103" s="1" t="n">
+        <v>0.287534952</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>0.011121943</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>0.07362674800000001</v>
+      </c>
+      <c r="D104" s="1" t="n">
+        <v>0.305822448</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>0.012293473</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>0.079237578</v>
+      </c>
+      <c r="D105" s="1" t="n">
+        <v>0.322601319</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>0.013428855</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>0.084540552</v>
+      </c>
+      <c r="D106" s="1" t="n">
+        <v>0.338163826</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>0.014533062</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>0.089584258</v>
+      </c>
+      <c r="D107" s="1" t="n">
+        <v>0.352720048</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>0.015609954</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>0.094405582</v>
+      </c>
+      <c r="D108" s="1" t="n">
+        <v>0.36642679</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>0.016662611</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>0.09903333</v>
+      </c>
+      <c r="D109" s="1" t="n">
+        <v>0.379404644</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>0.017693536</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>0.103490514</v>
+      </c>
+      <c r="D110" s="1" t="n">
+        <v>0.391748629</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>0.018704803</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>0.107795869</v>
+      </c>
+      <c r="D111" s="1" t="n">
+        <v>0.403535139</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>0.019698155</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>0.111964899</v>
+      </c>
+      <c r="D112" s="1" t="n">
+        <v>0.414826649</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>0.020675075</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>0.116010604</v>
+      </c>
+      <c r="D113" s="1" t="n">
+        <v>0.425674993</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>0.021636839</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>0.119944021</v>
+      </c>
+      <c r="D114" s="1" t="n">
+        <v>0.436123725</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>0.022584553</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>0.123774613</v>
+      </c>
+      <c r="D115" s="1" t="n">
+        <v>0.446209843</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>0.023519188</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>0.127510568</v>
+      </c>
+      <c r="D116" s="1" t="n">
+        <v>0.455965081</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>80</v>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>0.024441599</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>0.13115903</v>
+      </c>
+      <c r="D117" s="1" t="n">
+        <v>0.465416893</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>84</v>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>0.025352546</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>0.134726278</v>
+      </c>
+      <c r="D118" s="1" t="n">
+        <v>0.474589212</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>88</v>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>0.026252709</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>0.138217863</v>
+      </c>
+      <c r="D119" s="1" t="n">
+        <v>0.483503049</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>0.027142697</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>0.141638725</v>
+      </c>
+      <c r="D120" s="1" t="n">
+        <v>0.492176959</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>96</v>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>0.028023059</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>0.144993282</v>
+      </c>
+      <c r="D121" s="1" t="n">
+        <v>0.50062743</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>100</v>
+      </c>
+      <c r="B122" s="1" t="n">
+        <v>0.028894296</v>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>0.148285506</v>
+      </c>
+      <c r="D122" s="1" t="n">
+        <v>0.5088691789999999</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>104</v>
+      </c>
+      <c r="B123" s="1" t="n">
+        <v>0.029756862</v>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>0.151518981</v>
+      </c>
+      <c r="D123" s="1" t="n">
+        <v>0.516915415</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>108</v>
+      </c>
+      <c r="B124" s="1" t="n">
+        <v>0.030611171</v>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>0.154696956</v>
+      </c>
+      <c r="D124" s="1" t="n">
+        <v>0.5247780359999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>112</v>
+      </c>
+      <c r="B125" s="1" t="n">
+        <v>0.031457604</v>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>0.15782239</v>
+      </c>
+      <c r="D125" s="1" t="n">
+        <v>0.532467809</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B126" s="1" t="n">
+        <v>0.032296511</v>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>0.160897982</v>
+      </c>
+      <c r="D126" s="1" t="n">
+        <v>0.539994509</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B127" s="1" t="n">
+        <v>0.033128217</v>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>0.163926206</v>
+      </c>
+      <c r="D127" s="1" t="n">
+        <v>0.547367045</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B128" s="1" t="n">
+        <v>0.033953018</v>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>0.166909336</v>
+      </c>
+      <c r="D128" s="1" t="n">
+        <v>0.55459356</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="1" t="n">
+        <v>0.034771194</v>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>0.169849466</v>
+      </c>
+      <c r="D129" s="1" t="n">
+        <v>0.561681521</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B130" s="1" t="n">
+        <v>0.035583001</v>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>0.172748532</v>
+      </c>
+      <c r="D130" s="1" t="n">
+        <v>0.5686377929999999</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B131" s="1" t="n">
+        <v>0.03638868</v>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>0.175608326</v>
+      </c>
+      <c r="D131" s="1" t="n">
+        <v>0.575468705</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B132" s="1" t="n">
+        <v>0.037188456</v>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>0.178430513</v>
+      </c>
+      <c r="D132" s="1" t="n">
+        <v>0.582180108</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B133" s="1" t="n">
+        <v>0.037982539</v>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>0.18121664</v>
+      </c>
+      <c r="D133" s="1" t="n">
+        <v>0.5887774180000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B134" s="1" t="n">
+        <v>0.038771126</v>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>0.183968152</v>
+      </c>
+      <c r="D134" s="1" t="n">
+        <v>0.595265666</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B135" s="1" t="n">
+        <v>0.039554401</v>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>0.186686398</v>
+      </c>
+      <c r="D135" s="1" t="n">
+        <v>0.601649532</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B136" s="1" t="n">
+        <v>0.04033254</v>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>0.189372639</v>
+      </c>
+      <c r="D136" s="1" t="n">
+        <v>0.607933376</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B137" s="1" t="n">
+        <v>0.041105706</v>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>0.19202806</v>
+      </c>
+      <c r="D137" s="1" t="n">
+        <v>0.614121272</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B138" s="1" t="n">
+        <v>0.041874054</v>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>0.19465377</v>
+      </c>
+      <c r="D138" s="1" t="n">
+        <v>0.6202170299999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B139" s="1" t="n">
+        <v>0.042637731</v>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>0.197250816</v>
+      </c>
+      <c r="D139" s="1" t="n">
+        <v>0.62622422</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17983,7 +25249,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18123,1914 +25389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D139"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Figure 4a-c</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Mass-loss response (%) to one-at-a-time parameter sweeps of k_f (panel a), k_d (panel b), and k_ORR (panel c). Baseline: k_f = 3.0×10⁵ h⁻¹, k_d = 1.0×10⁸ mm⁶ g⁻² h⁻¹, k_ORR = 80 mm h⁻¹ (middle curves); low/high = 0.13×/3.3× (k_f), 0.2×/4× (k_d), 0.2×/5× (k_ORR).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Predicted mass loss with kinetic parameter sweep</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Time (hrs)</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>kf 4.0×10⁴</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>kf 3.0×10⁵</t>
-        </is>
-      </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>kf 1.0×10⁶</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B8" s="1" t="n">
-        <v>0.024554562</v>
-      </c>
-      <c r="C8" s="1" t="n">
-        <v>0.020944463</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>0.016104173</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="n">
-        <v>0.037217756</v>
-      </c>
-      <c r="C9" s="1" t="n">
-        <v>0.03174587</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>0.024409362</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B10" s="1" t="n">
-        <v>0.047468438</v>
-      </c>
-      <c r="C10" s="1" t="n">
-        <v>0.04048946</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>0.031132298</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B11" s="1" t="n">
-        <v>0.056411569</v>
-      </c>
-      <c r="C11" s="1" t="n">
-        <v>0.048117741</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0.036997674</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>0.06449323899999999</v>
-      </c>
-      <c r="C12" s="1" t="n">
-        <v>0.055011215</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>0.042298058</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B13" s="1" t="n">
-        <v>0.07194869800000001</v>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>0.061370546</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0.047187739</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B14" s="1" t="n">
-        <v>0.078920715</v>
-      </c>
-      <c r="C14" s="1" t="n">
-        <v>0.067317512</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>0.051760355</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B15" s="1" t="n">
-        <v>0.08550395</v>
-      </c>
-      <c r="C15" s="1" t="n">
-        <v>0.072932857</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>0.056077987</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B16" s="1" t="n">
-        <v>0.091765132</v>
-      </c>
-      <c r="C16" s="1" t="n">
-        <v>0.078273497</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>0.060184399</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B17" s="1" t="n">
-        <v>0.09775347099999999</v>
-      </c>
-      <c r="C17" s="1" t="n">
-        <v>0.08338141</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>0.064111867</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" s="1" t="n">
-        <v>0.103506541</v>
-      </c>
-      <c r="C18" s="1" t="n">
-        <v>0.088288644</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>0.067885033</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B19" s="1" t="n">
-        <v>0.109053833</v>
-      </c>
-      <c r="C19" s="1" t="n">
-        <v>0.093020353</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>0.071523238</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B20" s="1" t="n">
-        <v>0.114419013</v>
-      </c>
-      <c r="C20" s="1" t="n">
-        <v>0.097596725</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>0.07504200599999999</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B21" s="1" t="n">
-        <v>0.119621435</v>
-      </c>
-      <c r="C21" s="1" t="n">
-        <v>0.102034269</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>0.078454028</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>0.124677172</v>
-      </c>
-      <c r="C22" s="1" t="n">
-        <v>0.106346693</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>0.08176984599999999</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>0.129599754</v>
-      </c>
-      <c r="C23" s="1" t="n">
-        <v>0.11054554</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>0.08499833399999999</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>0.134400703</v>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>0.114640636</v>
-      </c>
-      <c r="D24" s="1" t="n">
-        <v>0.08814704900000001</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>0.13908993</v>
-      </c>
-      <c r="C25" s="1" t="n">
-        <v>0.118640437</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>0.091222491</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>0.143676039</v>
-      </c>
-      <c r="C26" s="1" t="n">
-        <v>0.12255228</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>0.094230302</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>0.148166555</v>
-      </c>
-      <c r="C27" s="1" t="n">
-        <v>0.126382584</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>0.097175419</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>0.152568109</v>
-      </c>
-      <c r="C28" s="1" t="n">
-        <v>0.130137006</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>0.100062189</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>0.15688658</v>
-      </c>
-      <c r="C29" s="1" t="n">
-        <v>0.13382056</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>0.102894469</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>0.16112721</v>
-      </c>
-      <c r="C30" s="1" t="n">
-        <v>0.137437718</v>
-      </c>
-      <c r="D30" s="1" t="n">
-        <v>0.105675698</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>0.165294701</v>
-      </c>
-      <c r="C31" s="1" t="n">
-        <v>0.14099249</v>
-      </c>
-      <c r="D31" s="1" t="n">
-        <v>0.108408957</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>0.169393285</v>
-      </c>
-      <c r="C32" s="1" t="n">
-        <v>0.144488486</v>
-      </c>
-      <c r="D32" s="1" t="n">
-        <v>0.111097025</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>0.173426794</v>
-      </c>
-      <c r="C33" s="1" t="n">
-        <v>0.147928973</v>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>0.113742411</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>0.177398705</v>
-      </c>
-      <c r="C34" s="1" t="n">
-        <v>0.15131692</v>
-      </c>
-      <c r="D34" s="1" t="n">
-        <v>0.1163474</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>0.181312191</v>
-      </c>
-      <c r="C35" s="1" t="n">
-        <v>0.154655031</v>
-      </c>
-      <c r="D35" s="1" t="n">
-        <v>0.118914069</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>0.185170153</v>
-      </c>
-      <c r="C36" s="1" t="n">
-        <v>0.157945782</v>
-      </c>
-      <c r="D36" s="1" t="n">
-        <v>0.121444324</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>0.188975255</v>
-      </c>
-      <c r="C37" s="1" t="n">
-        <v>0.161191444</v>
-      </c>
-      <c r="D37" s="1" t="n">
-        <v>0.12393991</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>0.192729947</v>
-      </c>
-      <c r="C38" s="1" t="n">
-        <v>0.164394109</v>
-      </c>
-      <c r="D38" s="1" t="n">
-        <v>0.126402435</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>0.196436494</v>
-      </c>
-      <c r="C39" s="1" t="n">
-        <v>0.167555706</v>
-      </c>
-      <c r="D39" s="1" t="n">
-        <v>0.128833383</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>0.200096987</v>
-      </c>
-      <c r="C40" s="1" t="n">
-        <v>0.170678021</v>
-      </c>
-      <c r="D40" s="1" t="n">
-        <v>0.131234127</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>0.203713372</v>
-      </c>
-      <c r="C41" s="1" t="n">
-        <v>0.173762711</v>
-      </c>
-      <c r="D41" s="1" t="n">
-        <v>0.133605942</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>0.207287452</v>
-      </c>
-      <c r="C42" s="1" t="n">
-        <v>0.176811318</v>
-      </c>
-      <c r="D42" s="1" t="n">
-        <v>0.135950012</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>0.210820912</v>
-      </c>
-      <c r="C43" s="1" t="n">
-        <v>0.179825276</v>
-      </c>
-      <c r="D43" s="1" t="n">
-        <v>0.13826744</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>0.214315322</v>
-      </c>
-      <c r="C44" s="1" t="n">
-        <v>0.182805925</v>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>0.140559258</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>0.217772153</v>
-      </c>
-      <c r="C45" s="1" t="n">
-        <v>0.185754521</v>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>0.14282643</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>0.221192782</v>
-      </c>
-      <c r="C46" s="1" t="n">
-        <v>0.188672237</v>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>0.145069858</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>0.224578502</v>
-      </c>
-      <c r="C47" s="1" t="n">
-        <v>0.191560177</v>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>0.147290392</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>164</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>0.22793053</v>
-      </c>
-      <c r="C48" s="1" t="n">
-        <v>0.194419377</v>
-      </c>
-      <c r="D48" s="1" t="n">
-        <v>0.149488828</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>168</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>0.23125001</v>
-      </c>
-      <c r="C49" s="1" t="n">
-        <v>0.197250816</v>
-      </c>
-      <c r="D49" s="1" t="n">
-        <v>0.151665918</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>Time (hrs)</t>
-        </is>
-      </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>kd 2.0×10⁷</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>kd 1.0×10⁸</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>kd 4.0×10⁸</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>0.017904039</v>
-      </c>
-      <c r="C53" s="1" t="n">
-        <v>0.020944463</v>
-      </c>
-      <c r="D53" s="1" t="n">
-        <v>0.024554562</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>0.027137449</v>
-      </c>
-      <c r="C54" s="1" t="n">
-        <v>0.03174587</v>
-      </c>
-      <c r="D54" s="1" t="n">
-        <v>0.037217756</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>0.034611767</v>
-      </c>
-      <c r="C55" s="1" t="n">
-        <v>0.04048946</v>
-      </c>
-      <c r="D55" s="1" t="n">
-        <v>0.047468438</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>0.041132681</v>
-      </c>
-      <c r="C56" s="1" t="n">
-        <v>0.048117741</v>
-      </c>
-      <c r="D56" s="1" t="n">
-        <v>0.056411569</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B57" s="1" t="n">
-        <v>0.047025457</v>
-      </c>
-      <c r="C57" s="1" t="n">
-        <v>0.055011215</v>
-      </c>
-      <c r="D57" s="1" t="n">
-        <v>0.06449323899999999</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>0.052461629</v>
-      </c>
-      <c r="C58" s="1" t="n">
-        <v>0.061370546</v>
-      </c>
-      <c r="D58" s="1" t="n">
-        <v>0.07194869800000001</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B59" s="1" t="n">
-        <v>0.057545298</v>
-      </c>
-      <c r="C59" s="1" t="n">
-        <v>0.067317512</v>
-      </c>
-      <c r="D59" s="1" t="n">
-        <v>0.078920715</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>0.062345486</v>
-      </c>
-      <c r="C60" s="1" t="n">
-        <v>0.072932857</v>
-      </c>
-      <c r="D60" s="1" t="n">
-        <v>0.08550395</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>0.066910847</v>
-      </c>
-      <c r="C61" s="1" t="n">
-        <v>0.078273497</v>
-      </c>
-      <c r="D61" s="1" t="n">
-        <v>0.091765132</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>0.07127726400000001</v>
-      </c>
-      <c r="C62" s="1" t="n">
-        <v>0.08338141</v>
-      </c>
-      <c r="D62" s="1" t="n">
-        <v>0.09775347099999999</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>0.075472135</v>
-      </c>
-      <c r="C63" s="1" t="n">
-        <v>0.088288644</v>
-      </c>
-      <c r="D63" s="1" t="n">
-        <v>0.103506541</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>0.07951696</v>
-      </c>
-      <c r="C64" s="1" t="n">
-        <v>0.093020353</v>
-      </c>
-      <c r="D64" s="1" t="n">
-        <v>0.109053833</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>0.083428999</v>
-      </c>
-      <c r="C65" s="1" t="n">
-        <v>0.097596725</v>
-      </c>
-      <c r="D65" s="1" t="n">
-        <v>0.114419013</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B66" s="1" t="n">
-        <v>0.087222362</v>
-      </c>
-      <c r="C66" s="1" t="n">
-        <v>0.102034269</v>
-      </c>
-      <c r="D66" s="1" t="n">
-        <v>0.119621435</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="1" t="n">
-        <v>0.090908769</v>
-      </c>
-      <c r="C67" s="1" t="n">
-        <v>0.106346693</v>
-      </c>
-      <c r="D67" s="1" t="n">
-        <v>0.124677172</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B68" s="1" t="n">
-        <v>0.094498086</v>
-      </c>
-      <c r="C68" s="1" t="n">
-        <v>0.11054554</v>
-      </c>
-      <c r="D68" s="1" t="n">
-        <v>0.129599754</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>0.097998714</v>
-      </c>
-      <c r="C69" s="1" t="n">
-        <v>0.114640636</v>
-      </c>
-      <c r="D69" s="1" t="n">
-        <v>0.134400703</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B70" s="1" t="n">
-        <v>0.101417879</v>
-      </c>
-      <c r="C70" s="1" t="n">
-        <v>0.118640437</v>
-      </c>
-      <c r="D70" s="1" t="n">
-        <v>0.13908993</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>0.104761856</v>
-      </c>
-      <c r="C71" s="1" t="n">
-        <v>0.12255228</v>
-      </c>
-      <c r="D71" s="1" t="n">
-        <v>0.143676039</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>0.10803613</v>
-      </c>
-      <c r="C72" s="1" t="n">
-        <v>0.126382584</v>
-      </c>
-      <c r="D72" s="1" t="n">
-        <v>0.148166555</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>0.111245538</v>
-      </c>
-      <c r="C73" s="1" t="n">
-        <v>0.130137006</v>
-      </c>
-      <c r="D73" s="1" t="n">
-        <v>0.152568109</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B74" s="1" t="n">
-        <v>0.114394365</v>
-      </c>
-      <c r="C74" s="1" t="n">
-        <v>0.13382056</v>
-      </c>
-      <c r="D74" s="1" t="n">
-        <v>0.15688658</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B75" s="1" t="n">
-        <v>0.117486434</v>
-      </c>
-      <c r="C75" s="1" t="n">
-        <v>0.137437718</v>
-      </c>
-      <c r="D75" s="1" t="n">
-        <v>0.16112721</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B76" s="1" t="n">
-        <v>0.120525174</v>
-      </c>
-      <c r="C76" s="1" t="n">
-        <v>0.14099249</v>
-      </c>
-      <c r="D76" s="1" t="n">
-        <v>0.165294701</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>0.12351367</v>
-      </c>
-      <c r="C77" s="1" t="n">
-        <v>0.144488486</v>
-      </c>
-      <c r="D77" s="1" t="n">
-        <v>0.169393285</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <v>0.126454716</v>
-      </c>
-      <c r="C78" s="1" t="n">
-        <v>0.147928973</v>
-      </c>
-      <c r="D78" s="1" t="n">
-        <v>0.173426794</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B79" s="1" t="n">
-        <v>0.129350848</v>
-      </c>
-      <c r="C79" s="1" t="n">
-        <v>0.15131692</v>
-      </c>
-      <c r="D79" s="1" t="n">
-        <v>0.177398705</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <v>0.132204379</v>
-      </c>
-      <c r="C80" s="1" t="n">
-        <v>0.154655031</v>
-      </c>
-      <c r="D80" s="1" t="n">
-        <v>0.181312191</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>0.135017425</v>
-      </c>
-      <c r="C81" s="1" t="n">
-        <v>0.157945782</v>
-      </c>
-      <c r="D81" s="1" t="n">
-        <v>0.185170153</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B82" s="1" t="n">
-        <v>0.137791927</v>
-      </c>
-      <c r="C82" s="1" t="n">
-        <v>0.161191444</v>
-      </c>
-      <c r="D82" s="1" t="n">
-        <v>0.188975255</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B83" s="1" t="n">
-        <v>0.140529674</v>
-      </c>
-      <c r="C83" s="1" t="n">
-        <v>0.164394109</v>
-      </c>
-      <c r="D83" s="1" t="n">
-        <v>0.192729947</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B84" s="1" t="n">
-        <v>0.143232314</v>
-      </c>
-      <c r="C84" s="1" t="n">
-        <v>0.167555706</v>
-      </c>
-      <c r="D84" s="1" t="n">
-        <v>0.196436494</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B85" s="1" t="n">
-        <v>0.145901375</v>
-      </c>
-      <c r="C85" s="1" t="n">
-        <v>0.170678021</v>
-      </c>
-      <c r="D85" s="1" t="n">
-        <v>0.200096987</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>0.148538274</v>
-      </c>
-      <c r="C86" s="1" t="n">
-        <v>0.173762711</v>
-      </c>
-      <c r="D86" s="1" t="n">
-        <v>0.203713372</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>0.151144326</v>
-      </c>
-      <c r="C87" s="1" t="n">
-        <v>0.176811318</v>
-      </c>
-      <c r="D87" s="1" t="n">
-        <v>0.207287452</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>0.15372076</v>
-      </c>
-      <c r="C88" s="1" t="n">
-        <v>0.179825276</v>
-      </c>
-      <c r="D88" s="1" t="n">
-        <v>0.210820912</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>0.156268721</v>
-      </c>
-      <c r="C89" s="1" t="n">
-        <v>0.182805925</v>
-      </c>
-      <c r="D89" s="1" t="n">
-        <v>0.214315322</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>0.15878928</v>
-      </c>
-      <c r="C90" s="1" t="n">
-        <v>0.185754521</v>
-      </c>
-      <c r="D90" s="1" t="n">
-        <v>0.217772153</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>0.161283443</v>
-      </c>
-      <c r="C91" s="1" t="n">
-        <v>0.188672237</v>
-      </c>
-      <c r="D91" s="1" t="n">
-        <v>0.221192782</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>0.163752152</v>
-      </c>
-      <c r="C92" s="1" t="n">
-        <v>0.191560177</v>
-      </c>
-      <c r="D92" s="1" t="n">
-        <v>0.224578502</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="1" t="n">
-        <v>164</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>0.166196294</v>
-      </c>
-      <c r="C93" s="1" t="n">
-        <v>0.194419377</v>
-      </c>
-      <c r="D93" s="1" t="n">
-        <v>0.22793053</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="1" t="n">
-        <v>168</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>0.168616704</v>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>0.197250816</v>
-      </c>
-      <c r="D94" s="1" t="n">
-        <v>0.23125001</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="1" t="inlineStr">
-        <is>
-          <t>Time (hrs)</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>kORR 16</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>kORR 80</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>kORR 400</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>0.002584384</v>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>0.025248274</v>
-      </c>
-      <c r="D98" s="1" t="n">
-        <v>0.14042038</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>0.004346399</v>
-      </c>
-      <c r="C99" s="1" t="n">
-        <v>0.036965637</v>
-      </c>
-      <c r="D99" s="1" t="n">
-        <v>0.185285802</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>0.005891123</v>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>0.046200682</v>
-      </c>
-      <c r="D100" s="1" t="n">
-        <v>0.217910745</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>0.007309743</v>
-      </c>
-      <c r="C101" s="1" t="n">
-        <v>0.054120861</v>
-      </c>
-      <c r="D101" s="1" t="n">
-        <v>0.244486082</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>0.00864141</v>
-      </c>
-      <c r="C102" s="1" t="n">
-        <v>0.061187851</v>
-      </c>
-      <c r="D102" s="1" t="n">
-        <v>0.26731181</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>0.009907648</v>
-      </c>
-      <c r="C103" s="1" t="n">
-        <v>0.067641758</v>
-      </c>
-      <c r="D103" s="1" t="n">
-        <v>0.287534952</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>0.011121943</v>
-      </c>
-      <c r="C104" s="1" t="n">
-        <v>0.07362674800000001</v>
-      </c>
-      <c r="D104" s="1" t="n">
-        <v>0.305822448</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>0.012293473</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>0.079237578</v>
-      </c>
-      <c r="D105" s="1" t="n">
-        <v>0.322601319</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>0.013428855</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>0.084540552</v>
-      </c>
-      <c r="D106" s="1" t="n">
-        <v>0.338163826</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>0.014533062</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>0.089584258</v>
-      </c>
-      <c r="D107" s="1" t="n">
-        <v>0.352720048</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B108" s="1" t="n">
-        <v>0.015609954</v>
-      </c>
-      <c r="C108" s="1" t="n">
-        <v>0.094405582</v>
-      </c>
-      <c r="D108" s="1" t="n">
-        <v>0.36642679</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B109" s="1" t="n">
-        <v>0.016662611</v>
-      </c>
-      <c r="C109" s="1" t="n">
-        <v>0.09903333</v>
-      </c>
-      <c r="D109" s="1" t="n">
-        <v>0.379404644</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>0.017693536</v>
-      </c>
-      <c r="C110" s="1" t="n">
-        <v>0.103490514</v>
-      </c>
-      <c r="D110" s="1" t="n">
-        <v>0.391748629</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B111" s="1" t="n">
-        <v>0.018704803</v>
-      </c>
-      <c r="C111" s="1" t="n">
-        <v>0.107795869</v>
-      </c>
-      <c r="D111" s="1" t="n">
-        <v>0.403535139</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B112" s="1" t="n">
-        <v>0.019698155</v>
-      </c>
-      <c r="C112" s="1" t="n">
-        <v>0.111964899</v>
-      </c>
-      <c r="D112" s="1" t="n">
-        <v>0.414826649</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>0.020675075</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>0.116010604</v>
-      </c>
-      <c r="D113" s="1" t="n">
-        <v>0.425674993</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>0.021636839</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>0.119944021</v>
-      </c>
-      <c r="D114" s="1" t="n">
-        <v>0.436123725</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>0.022584553</v>
-      </c>
-      <c r="C115" s="1" t="n">
-        <v>0.123774613</v>
-      </c>
-      <c r="D115" s="1" t="n">
-        <v>0.446209843</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>0.023519188</v>
-      </c>
-      <c r="C116" s="1" t="n">
-        <v>0.127510568</v>
-      </c>
-      <c r="D116" s="1" t="n">
-        <v>0.455965081</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>0.024441599</v>
-      </c>
-      <c r="C117" s="1" t="n">
-        <v>0.13115903</v>
-      </c>
-      <c r="D117" s="1" t="n">
-        <v>0.465416893</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>0.025352546</v>
-      </c>
-      <c r="C118" s="1" t="n">
-        <v>0.134726278</v>
-      </c>
-      <c r="D118" s="1" t="n">
-        <v>0.474589212</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>0.026252709</v>
-      </c>
-      <c r="C119" s="1" t="n">
-        <v>0.138217863</v>
-      </c>
-      <c r="D119" s="1" t="n">
-        <v>0.483503049</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>0.027142697</v>
-      </c>
-      <c r="C120" s="1" t="n">
-        <v>0.141638725</v>
-      </c>
-      <c r="D120" s="1" t="n">
-        <v>0.492176959</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>0.028023059</v>
-      </c>
-      <c r="C121" s="1" t="n">
-        <v>0.144993282</v>
-      </c>
-      <c r="D121" s="1" t="n">
-        <v>0.50062743</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B122" s="1" t="n">
-        <v>0.028894296</v>
-      </c>
-      <c r="C122" s="1" t="n">
-        <v>0.148285506</v>
-      </c>
-      <c r="D122" s="1" t="n">
-        <v>0.5088691789999999</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="1" t="n">
-        <v>104</v>
-      </c>
-      <c r="B123" s="1" t="n">
-        <v>0.029756862</v>
-      </c>
-      <c r="C123" s="1" t="n">
-        <v>0.151518981</v>
-      </c>
-      <c r="D123" s="1" t="n">
-        <v>0.516915415</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="1" t="n">
-        <v>108</v>
-      </c>
-      <c r="B124" s="1" t="n">
-        <v>0.030611171</v>
-      </c>
-      <c r="C124" s="1" t="n">
-        <v>0.154696956</v>
-      </c>
-      <c r="D124" s="1" t="n">
-        <v>0.5247780359999999</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="1" t="n">
-        <v>112</v>
-      </c>
-      <c r="B125" s="1" t="n">
-        <v>0.031457604</v>
-      </c>
-      <c r="C125" s="1" t="n">
-        <v>0.15782239</v>
-      </c>
-      <c r="D125" s="1" t="n">
-        <v>0.532467809</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="1" t="n">
-        <v>116</v>
-      </c>
-      <c r="B126" s="1" t="n">
-        <v>0.032296511</v>
-      </c>
-      <c r="C126" s="1" t="n">
-        <v>0.160897982</v>
-      </c>
-      <c r="D126" s="1" t="n">
-        <v>0.539994509</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="1" t="n">
-        <v>120</v>
-      </c>
-      <c r="B127" s="1" t="n">
-        <v>0.033128217</v>
-      </c>
-      <c r="C127" s="1" t="n">
-        <v>0.163926206</v>
-      </c>
-      <c r="D127" s="1" t="n">
-        <v>0.547367045</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="1" t="n">
-        <v>124</v>
-      </c>
-      <c r="B128" s="1" t="n">
-        <v>0.033953018</v>
-      </c>
-      <c r="C128" s="1" t="n">
-        <v>0.166909336</v>
-      </c>
-      <c r="D128" s="1" t="n">
-        <v>0.55459356</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="1" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="1" t="n">
-        <v>0.034771194</v>
-      </c>
-      <c r="C129" s="1" t="n">
-        <v>0.169849466</v>
-      </c>
-      <c r="D129" s="1" t="n">
-        <v>0.561681521</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="1" t="n">
-        <v>132</v>
-      </c>
-      <c r="B130" s="1" t="n">
-        <v>0.035583001</v>
-      </c>
-      <c r="C130" s="1" t="n">
-        <v>0.172748532</v>
-      </c>
-      <c r="D130" s="1" t="n">
-        <v>0.5686377929999999</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="1" t="n">
-        <v>136</v>
-      </c>
-      <c r="B131" s="1" t="n">
-        <v>0.03638868</v>
-      </c>
-      <c r="C131" s="1" t="n">
-        <v>0.175608326</v>
-      </c>
-      <c r="D131" s="1" t="n">
-        <v>0.575468705</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="1" t="n">
-        <v>140</v>
-      </c>
-      <c r="B132" s="1" t="n">
-        <v>0.037188456</v>
-      </c>
-      <c r="C132" s="1" t="n">
-        <v>0.178430513</v>
-      </c>
-      <c r="D132" s="1" t="n">
-        <v>0.582180108</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="1" t="n">
-        <v>144</v>
-      </c>
-      <c r="B133" s="1" t="n">
-        <v>0.037982539</v>
-      </c>
-      <c r="C133" s="1" t="n">
-        <v>0.18121664</v>
-      </c>
-      <c r="D133" s="1" t="n">
-        <v>0.5887774180000001</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="1" t="n">
-        <v>148</v>
-      </c>
-      <c r="B134" s="1" t="n">
-        <v>0.038771126</v>
-      </c>
-      <c r="C134" s="1" t="n">
-        <v>0.183968152</v>
-      </c>
-      <c r="D134" s="1" t="n">
-        <v>0.595265666</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="1" t="n">
-        <v>152</v>
-      </c>
-      <c r="B135" s="1" t="n">
-        <v>0.039554401</v>
-      </c>
-      <c r="C135" s="1" t="n">
-        <v>0.186686398</v>
-      </c>
-      <c r="D135" s="1" t="n">
-        <v>0.601649532</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="1" t="n">
-        <v>156</v>
-      </c>
-      <c r="B136" s="1" t="n">
-        <v>0.04033254</v>
-      </c>
-      <c r="C136" s="1" t="n">
-        <v>0.189372639</v>
-      </c>
-      <c r="D136" s="1" t="n">
-        <v>0.607933376</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="1" t="n">
-        <v>160</v>
-      </c>
-      <c r="B137" s="1" t="n">
-        <v>0.041105706</v>
-      </c>
-      <c r="C137" s="1" t="n">
-        <v>0.19202806</v>
-      </c>
-      <c r="D137" s="1" t="n">
-        <v>0.614121272</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="1" t="n">
-        <v>164</v>
-      </c>
-      <c r="B138" s="1" t="n">
-        <v>0.041874054</v>
-      </c>
-      <c r="C138" s="1" t="n">
-        <v>0.19465377</v>
-      </c>
-      <c r="D138" s="1" t="n">
-        <v>0.6202170299999999</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="1" t="n">
-        <v>168</v>
-      </c>
-      <c r="B139" s="1" t="n">
-        <v>0.042637731</v>
-      </c>
-      <c r="C139" s="1" t="n">
-        <v>0.197250816</v>
-      </c>
-      <c r="D139" s="1" t="n">
-        <v>0.62622422</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20184,7 +25543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20370,7 +25729,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20577,7 +25936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -21,12 +21,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 1" sheetId="13" state="visible" r:id="rId13"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 2" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table 3" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 5" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6b" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 7" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9a,b" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 9c,d" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 1" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 3" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 4b" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 6" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8a,b" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 8c,d" sheetId="21" state="visible" r:id="rId21"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 10a" sheetId="22" state="visible" r:id="rId22"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplementary Figure 10b" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Table S1" sheetId="24" state="visible" r:id="rId24"/>
@@ -3658,7 +3658,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 3</t>
+          <t>Supplementary Figure 1</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 5</t>
+          <t>Supplementary Figure 3</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5141,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 6b</t>
+          <t>Supplementary Figure 4b</t>
         </is>
       </c>
     </row>
@@ -5949,7 +5949,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 7</t>
+          <t>Supplementary Figure 6</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9a,b</t>
+          <t>Supplementary Figure 8a,b</t>
         </is>
       </c>
     </row>
@@ -16218,7 +16218,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Supplementary Figure 9c,d</t>
+          <t>Supplementary Figure 8c,d</t>
         </is>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -2957,7 +2957,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3008,12 +3008,12 @@
           <t>Material properties</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n"/>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr"/>
+      <c r="C5" s="1" t="inlineStr"/>
+      <c r="D5" s="1" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>Zn density</t>
         </is>
@@ -3030,12 +3030,12 @@
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Zn molar mass</t>
         </is>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
@@ -3062,12 +3062,12 @@
           <t>Diffusion coefficients (37 °C)</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n"/>
-      <c r="C8" s="1" t="n"/>
-      <c r="D8" s="1" t="n"/>
+      <c r="B8" s="1" t="inlineStr"/>
+      <c r="C8" s="1" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>Zn2+ diffusivity</t>
         </is>
@@ -3084,12 +3084,12 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Cl- diffusivity</t>
         </is>
@@ -3106,12 +3106,12 @@
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>OH- diffusivity</t>
         </is>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>O2 diffusivity</t>
         </is>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>[48]</t>
+          <t>[33]</t>
         </is>
       </c>
     </row>
@@ -3160,12 +3160,12 @@
           <t>Film properties</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n"/>
-      <c r="C13" s="1" t="n"/>
-      <c r="D13" s="1" t="n"/>
+      <c r="B13" s="1" t="inlineStr"/>
+      <c r="C13" s="1" t="inlineStr"/>
+      <c r="D13" s="1" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Film density</t>
         </is>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>[47]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Film porosity</t>
         </is>
@@ -3197,17 +3197,19 @@
           <t>ε</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>0.25</v>
+      <c r="C15" s="1" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
-          <t>[49]</t>
+          <t>[34]</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>Film tortuosity</t>
         </is>
@@ -3217,17 +3219,19 @@
           <t>τ</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>2</v>
+      <c r="C16" s="1" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
-          <t>[50]</t>
+          <t>[35]</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>Film molar mass</t>
         </is>
@@ -3244,129 +3248,101 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>[46]</t>
+          <t>[32]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Interface conditions</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="n"/>
-      <c r="C18" s="1" t="n"/>
-      <c r="D18" s="1" t="n"/>
+          <t>Initial conditions</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr"/>
+      <c r="C18" s="1" t="inlineStr"/>
+      <c r="D18" s="1" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ sat. concentration</t>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Zn2+ concentration</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[Zn]_sat</t>
+          <t>C_Zn^0</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>10 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D19" s="1" t="inlineStr">
-        <is>
-          <t>[51]</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="1" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Initial conditions</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="n"/>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="n"/>
+          <t>Cl- concentration</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>C_Cl^0</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>1.42 × 10^-7 mol mm^-3</t>
+        </is>
+      </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>[36]</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>Zn2+ concentration</t>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>O2 concentration</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>C_Zn^0</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="1" t="n"/>
+          <t>C_O2^0</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="inlineStr">
+        <is>
+          <t>1.09 × 10^-10 mol mm^-3</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>[21]</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Cl- concentration</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>pH</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>C_Cl^0</t>
+          <t>–</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>142.3 mmol L^-1</t>
+          <t>7.40</t>
         </is>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>[52]</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>O2 concentration</t>
-        </is>
-      </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>C_O2^0</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>3.5 mg L^-1</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>[29]</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>pH</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>[53]</t>
+          <t>[37]</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3439,11 +3415,13 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>[1, 100]</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>35.91</v>
+          <t>[1×10⁴, 8×10⁵]</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>3×10⁵</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3454,16 +3432,18 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>L^2 mol^-2 h^-1</t>
+          <t>mm^6 g^-2 h^-1</t>
         </is>
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>[5, 100]</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>27.17</v>
+          <t>[2×10⁷, 4×10⁸]</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>1×10⁸</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3474,36 +3454,18 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>mm h^-1 (effective)</t>
+          <t>mm h^-1</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>[0.05, 5.0]</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>M_O2</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>g mol^-1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>fixed</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>32</v>
+          <t>[8, 800]</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21731,7 +21693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21749,85 +21711,76 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison of the candidate velocity-selection formulations. Rule A (hard minimum) best matched literature mass-loss measurements and was adopted in the final model.</t>
+          <t>Limiting regimes of the interfacial oxygen flux.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Regime</t>
         </is>
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Condition</t>
         </is>
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>RMSE (%)</t>
+          <t>Interfacial flux J_O₂</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>Reaction-controlled</t>
         </is>
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Hard minimum</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>0.0568</v>
+          <t>Da ≪ 1</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>k_ORR C_b</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Transition</t>
         </is>
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>Mixed control</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>0.077</v>
+          <t>Da ≈ 1</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>C_b /(1/k_ORR + δ/D_O₂,eff)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>Diffusion-controlled</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>Hybrid cathodic</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>0.0766</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Coupled ORR (no O2 cap)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>0.2983</v>
+          <t>Da ≫ 1</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>D_O₂,eff C_b /δ</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -21860,7 +21813,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh (21.25 million elements).</t>
+          <t>Mesh convergence study showing the effect of mesh resolution on predicted 7-day mass loss. Relative errors are calculated with respect to the reference mesh (Mass Loss values may differ from those of the calibrated model, as these validation cases were evaluated prior to model calibration).</t>
         </is>
       </c>
     </row>
@@ -21896,10 +21849,10 @@
         <v>182768</v>
       </c>
       <c r="C5" s="7" t="n">
-        <v>1.439</v>
+        <v>0.3009</v>
       </c>
       <c r="D5" s="8" t="n">
-        <v>1465.8</v>
+        <v>87.2</v>
       </c>
     </row>
     <row r="6">
@@ -21911,11 +21864,11 @@
       <c r="B6" s="9" t="n">
         <v>802365</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0.4977</v>
+      <c r="C6" s="7" t="n">
+        <v>0.2029</v>
       </c>
       <c r="D6" s="8" t="n">
-        <v>441.6</v>
+        <v>26.2</v>
       </c>
     </row>
     <row r="7">
@@ -21927,11 +21880,11 @@
       <c r="B7" s="9" t="n">
         <v>3454723</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0.1633</v>
+      <c r="C7" s="7" t="n">
+        <v>0.1682</v>
       </c>
       <c r="D7" s="8" t="n">
-        <v>77.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="8">
@@ -21943,11 +21896,11 @@
       <c r="B8" s="9" t="n">
         <v>4990080</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0.1208</v>
+      <c r="C8" s="7" t="n">
+        <v>0.1637</v>
       </c>
       <c r="D8" s="8" t="n">
-        <v>31.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -21959,11 +21912,11 @@
       <c r="B9" s="9" t="n">
         <v>11958220</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0.1002</v>
+      <c r="C9" s="7" t="n">
+        <v>0.1616</v>
       </c>
       <c r="D9" s="8" t="n">
-        <v>9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -21975,11 +21928,11 @@
       <c r="B10" s="9" t="n">
         <v>18864900</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0.0927</v>
-      </c>
-      <c r="D10" s="4" t="n">
-        <v>0.87</v>
+      <c r="C10" s="7" t="n">
+        <v>0.1611</v>
+      </c>
+      <c r="D10" s="8" t="n">
+        <v>0.19</v>
       </c>
     </row>
     <row r="11">
@@ -21991,10 +21944,10 @@
       <c r="B11" s="9" t="n">
         <v>21245850</v>
       </c>
-      <c r="C11" s="6" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="D11" s="1" t="inlineStr">
+      <c r="C11" s="7" t="n">
+        <v>0.1608</v>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -22031,7 +21984,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison between adaptive and uniform meshes at approximately 800,000 elements.</t>
+          <t>Comparison between an adaptive mesh and a uniform mesh (approximately 800,000 elements).</t>
         </is>
       </c>
     </row>
@@ -22069,13 +22022,13 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>799520</v>
+        <v>799000</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>2.8561</v>
+        <v>0.286</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>3007.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="E5" s="1" t="inlineStr">
         <is>
@@ -22093,13 +22046,13 @@
         <v>802365</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0.4977</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>441.6</v>
-      </c>
-      <c r="E6" s="6" t="n">
-        <v>0.8532</v>
+        <v>0.2029</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.663</v>
       </c>
     </row>
     <row r="7">
@@ -22112,14 +22065,14 @@
         <v>21245850</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.0919</v>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
+        <v>0.1608</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -22452,7 +22405,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>0.04 mm</t>
+          <t>0.005 mm</t>
         </is>
       </c>
       <c r="D18" s="1" t="inlineStr">
@@ -22598,7 +22551,7 @@
         </is>
       </c>
       <c r="B26" s="5" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>50</v>
@@ -22899,7 +22852,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Parameters included in the Morris sensitivity analysis.</t>
+          <t>Parameters included in the Morris sensitivity analysis (the ranges might differ from calibration space as this was done prior to calibration of the model).</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22891,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>50–200</t>
+          <t>1×10⁴ – 8×10⁵</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -22960,7 +22913,7 @@
       </c>
       <c r="C6" s="1" t="inlineStr">
         <is>
-          <t>1–50</t>
+          <t>2×10⁷ – 4×10⁸</t>
         </is>
       </c>
       <c r="D6" s="1" t="inlineStr">
@@ -22982,7 +22935,7 @@
       </c>
       <c r="C7" s="1" t="inlineStr">
         <is>
-          <t>0.1–5.0</t>
+          <t>8 – 800</t>
         </is>
       </c>
       <c r="D7" s="1" t="inlineStr">
@@ -23026,7 +22979,7 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>1×10^-9 to 1×10^-7</t>
+          <t>1×10^-9 – 1×10^-8</t>
         </is>
       </c>
       <c r="D9" s="1" t="inlineStr">
@@ -25157,7 +25110,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Literature mass-loss data used for Bayesian calibration (Liu et al. 2018).</t>
+          <t>Literature mass-loss data used for calibration (Liu et al. 2018).</t>
         </is>
       </c>
     </row>
@@ -25755,7 +25708,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Comparison of simulated and measured mass loss in HBSS (validation) with the experimental scatter. Experimental values are mean ± SD (n = 3).</t>
+          <t>Comparison of simulated and measured mass loss in HBSS (validation) with the experimental scatter. Experimental values are mean ± SD (n = 3); |Error|/SD is the absolute error divided by the SD at the same immersion time. The validation RMSE of 0.0159% (R² = 0.9734) corresponds to 8.6% of the mean measured mass loss (0.185%) and 5.1% of the 28-day value.</t>
         </is>
       </c>
     </row>
@@ -25963,7 +25916,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Geometric and computational parameters of the controlled test structures used in Figure 8.</t>
+          <t>Geometric and computational parameters of the controlled test structures used in main-text Figure 8.</t>
         </is>
       </c>
     </row>

--- a/deliver/SourceData.xlsx
+++ b/deliver/SourceData.xlsx
@@ -105,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -125,6 +125,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -22957,12 +22958,12 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>5–20</t>
+          <t>1.39×10⁻³ – 5.56×10⁻³</t>
         </is>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
-          <t>mm^2 h^-1</t>
+          <t>mm^2 s^-1</t>
         </is>
       </c>
     </row>
@@ -23001,12 +23002,12 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>1.5–5.0</t>
+          <t>4.17×10⁻⁴ – 1.39×10⁻³</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
-          <t>mm^2 h^-1</t>
+          <t>mm^2 s^-1</t>
         </is>
       </c>
     </row>
@@ -23023,12 +23024,12 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>5–15</t>
+          <t>1.39×10⁻³ – 4.17×10⁻³</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
-          <t>mm^2 h^-1</t>
+          <t>mm^2 s^-1</t>
         </is>
       </c>
     </row>
@@ -23045,12 +23046,12 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>15–35</t>
+          <t>4.17×10⁻³ – 9.72×10⁻³</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>mm^2 h^-1</t>
+          <t>mm^2 s^-1</t>
         </is>
       </c>
     </row>
@@ -43895,10 +43896,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K677"/>
+  <dimension ref="A1:Q677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="6" max="11"/>
+    <col width="28" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -43973,6 +43976,16 @@
           <t>Regime (surface share)</t>
         </is>
       </c>
+      <c r="M4" s="1" t="inlineStr">
+        <is>
+          <t>CR, ASTM G31 average (mm/yr)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Inputs (Table S4)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -44002,6 +44015,17 @@
           <t>NotYetComputed</t>
         </is>
       </c>
+      <c r="M5" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>K (mm/yr; t in h, A in cm², W in g, rho in g/cm³)</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>87600</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -44031,6 +44055,18 @@
           <t>ZnDiffusionLimited</t>
         </is>
       </c>
+      <c r="M6" s="13">
+        <f>$Q$5*(B6/100*$Q$7*$Q$6)/($Q$6*$Q$8*A6)</f>
+        <v/>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>rho_Zn (g/cm³)</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.14</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -44062,6 +44098,18 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M7" s="13">
+        <f>$Q$5*(B7/100*$Q$7*$Q$6)/($Q$6*$Q$8*A7)</f>
+        <v/>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Initial volume V0 (cm³)</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.000361</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -44093,6 +44141,18 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M8" s="13">
+        <f>$Q$5*(B8/100*$Q$7*$Q$6)/($Q$6*$Q$8*A8)</f>
+        <v/>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Initial surface area A0 (cm²)</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1946</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -44124,6 +44184,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M9" s="13">
+        <f>$Q$5*(B9/100*$Q$7*$Q$6)/($Q$6*$Q$8*A9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -44155,6 +44219,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M10" s="13">
+        <f>$Q$5*(B10/100*$Q$7*$Q$6)/($Q$6*$Q$8*A10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -44186,6 +44254,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M11" s="13">
+        <f>$Q$5*(B11/100*$Q$7*$Q$6)/($Q$6*$Q$8*A11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -44217,6 +44289,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M12" s="13">
+        <f>$Q$5*(B12/100*$Q$7*$Q$6)/($Q$6*$Q$8*A12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -44248,6 +44324,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M13" s="13">
+        <f>$Q$5*(B13/100*$Q$7*$Q$6)/($Q$6*$Q$8*A13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -44279,6 +44359,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M14" s="13">
+        <f>$Q$5*(B14/100*$Q$7*$Q$6)/($Q$6*$Q$8*A14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -44310,6 +44394,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M15" s="13">
+        <f>$Q$5*(B15/100*$Q$7*$Q$6)/($Q$6*$Q$8*A15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -44341,6 +44429,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M16" s="13">
+        <f>$Q$5*(B16/100*$Q$7*$Q$6)/($Q$6*$Q$8*A16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -44372,6 +44464,10 @@
           <t>O2ReactionLimited</t>
         </is>
       </c>
+      <c r="M17" s="13">
+        <f>$Q$5*(B17/100*$Q$7*$Q$6)/($Q$6*$Q$8*A17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -44403,6 +44499,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M18" s="13">
+        <f>$Q$5*(B18/100*$Q$7*$Q$6)/($Q$6*$Q$8*A18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -44434,6 +44534,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M19" s="13">
+        <f>$Q$5*(B19/100*$Q$7*$Q$6)/($Q$6*$Q$8*A19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -44465,6 +44569,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M20" s="13">
+        <f>$Q$5*(B20/100*$Q$7*$Q$6)/($Q$6*$Q$8*A20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -44496,6 +44604,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M21" s="13">
+        <f>$Q$5*(B21/100*$Q$7*$Q$6)/($Q$6*$Q$8*A21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -44527,6 +44639,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M22" s="13">
+        <f>$Q$5*(B22/100*$Q$7*$Q$6)/($Q$6*$Q$8*A22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -44558,6 +44674,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M23" s="13">
+        <f>$Q$5*(B23/100*$Q$7*$Q$6)/($Q$6*$Q$8*A23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -44589,6 +44709,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M24" s="13">
+        <f>$Q$5*(B24/100*$Q$7*$Q$6)/($Q$6*$Q$8*A24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -44620,6 +44744,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M25" s="13">
+        <f>$Q$5*(B25/100*$Q$7*$Q$6)/($Q$6*$Q$8*A25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -44651,6 +44779,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M26" s="13">
+        <f>$Q$5*(B26/100*$Q$7*$Q$6)/($Q$6*$Q$8*A26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -44682,6 +44814,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M27" s="13">
+        <f>$Q$5*(B27/100*$Q$7*$Q$6)/($Q$6*$Q$8*A27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -44713,6 +44849,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M28" s="13">
+        <f>$Q$5*(B28/100*$Q$7*$Q$6)/($Q$6*$Q$8*A28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -44744,6 +44884,10 @@
           <t>Transition</t>
         </is>
       </c>
+      <c r="M29" s="13">
+        <f>$Q$5*(B29/100*$Q$7*$Q$6)/($Q$6*$Q$8*A29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -44775,6 +44919,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M30" s="13">
+        <f>$Q$5*(B30/100*$Q$7*$Q$6)/($Q$6*$Q$8*A30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -44806,6 +44954,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M31" s="13">
+        <f>$Q$5*(B31/100*$Q$7*$Q$6)/($Q$6*$Q$8*A31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -44837,6 +44989,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M32" s="13">
+        <f>$Q$5*(B32/100*$Q$7*$Q$6)/($Q$6*$Q$8*A32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -44868,6 +45024,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M33" s="13">
+        <f>$Q$5*(B33/100*$Q$7*$Q$6)/($Q$6*$Q$8*A33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -44899,6 +45059,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M34" s="13">
+        <f>$Q$5*(B34/100*$Q$7*$Q$6)/($Q$6*$Q$8*A34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -44930,6 +45094,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M35" s="13">
+        <f>$Q$5*(B35/100*$Q$7*$Q$6)/($Q$6*$Q$8*A35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -44961,6 +45129,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M36" s="13">
+        <f>$Q$5*(B36/100*$Q$7*$Q$6)/($Q$6*$Q$8*A36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -44992,6 +45164,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M37" s="13">
+        <f>$Q$5*(B37/100*$Q$7*$Q$6)/($Q$6*$Q$8*A37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -45023,6 +45199,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M38" s="13">
+        <f>$Q$5*(B38/100*$Q$7*$Q$6)/($Q$6*$Q$8*A38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -45054,6 +45234,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M39" s="13">
+        <f>$Q$5*(B39/100*$Q$7*$Q$6)/($Q$6*$Q$8*A39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -45085,6 +45269,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M40" s="13">
+        <f>$Q$5*(B40/100*$Q$7*$Q$6)/($Q$6*$Q$8*A40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -45116,6 +45304,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M41" s="13">
+        <f>$Q$5*(B41/100*$Q$7*$Q$6)/($Q$6*$Q$8*A41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -45147,6 +45339,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M42" s="13">
+        <f>$Q$5*(B42/100*$Q$7*$Q$6)/($Q$6*$Q$8*A42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -45178,6 +45374,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M43" s="13">
+        <f>$Q$5*(B43/100*$Q$7*$Q$6)/($Q$6*$Q$8*A43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -45209,6 +45409,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M44" s="13">
+        <f>$Q$5*(B44/100*$Q$7*$Q$6)/($Q$6*$Q$8*A44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -45240,6 +45444,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M45" s="13">
+        <f>$Q$5*(B45/100*$Q$7*$Q$6)/($Q$6*$Q$8*A45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -45271,6 +45479,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M46" s="13">
+        <f>$Q$5*(B46/100*$Q$7*$Q$6)/($Q$6*$Q$8*A46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -45302,6 +45514,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M47" s="13">
+        <f>$Q$5*(B47/100*$Q$7*$Q$6)/($Q$6*$Q$8*A47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -45333,6 +45549,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M48" s="13">
+        <f>$Q$5*(B48/100*$Q$7*$Q$6)/($Q$6*$Q$8*A48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -45364,6 +45584,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M49" s="13">
+        <f>$Q$5*(B49/100*$Q$7*$Q$6)/($Q$6*$Q$8*A49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -45395,6 +45619,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M50" s="13">
+        <f>$Q$5*(B50/100*$Q$7*$Q$6)/($Q$6*$Q$8*A50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -45426,6 +45654,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M51" s="13">
+        <f>$Q$5*(B51/100*$Q$7*$Q$6)/($Q$6*$Q$8*A51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -45457,6 +45689,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M52" s="13">
+        <f>$Q$5*(B52/100*$Q$7*$Q$6)/($Q$6*$Q$8*A52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -45488,6 +45724,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M53" s="13">
+        <f>$Q$5*(B53/100*$Q$7*$Q$6)/($Q$6*$Q$8*A53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -45519,6 +45759,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M54" s="13">
+        <f>$Q$5*(B54/100*$Q$7*$Q$6)/($Q$6*$Q$8*A54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -45550,6 +45794,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M55" s="13">
+        <f>$Q$5*(B55/100*$Q$7*$Q$6)/($Q$6*$Q$8*A55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -45581,6 +45829,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M56" s="13">
+        <f>$Q$5*(B56/100*$Q$7*$Q$6)/($Q$6*$Q$8*A56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -45612,6 +45864,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M57" s="13">
+        <f>$Q$5*(B57/100*$Q$7*$Q$6)/($Q$6*$Q$8*A57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -45643,6 +45899,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M58" s="13">
+        <f>$Q$5*(B58/100*$Q$7*$Q$6)/($Q$6*$Q$8*A58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -45674,6 +45934,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M59" s="13">
+        <f>$Q$5*(B59/100*$Q$7*$Q$6)/($Q$6*$Q$8*A59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -45705,6 +45969,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M60" s="13">
+        <f>$Q$5*(B60/100*$Q$7*$Q$6)/($Q$6*$Q$8*A60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -45736,6 +46004,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M61" s="13">
+        <f>$Q$5*(B61/100*$Q$7*$Q$6)/($Q$6*$Q$8*A61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -45767,6 +46039,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M62" s="13">
+        <f>$Q$5*(B62/100*$Q$7*$Q$6)/($Q$6*$Q$8*A62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -45798,6 +46074,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M63" s="13">
+        <f>$Q$5*(B63/100*$Q$7*$Q$6)/($Q$6*$Q$8*A63)</f>
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -45829,6 +46109,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M64" s="13">
+        <f>$Q$5*(B64/100*$Q$7*$Q$6)/($Q$6*$Q$8*A64)</f>
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -45860,6 +46144,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M65" s="13">
+        <f>$Q$5*(B65/100*$Q$7*$Q$6)/($Q$6*$Q$8*A65)</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -45891,6 +46179,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M66" s="13">
+        <f>$Q$5*(B66/100*$Q$7*$Q$6)/($Q$6*$Q$8*A66)</f>
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -45922,6 +46214,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M67" s="13">
+        <f>$Q$5*(B67/100*$Q$7*$Q$6)/($Q$6*$Q$8*A67)</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -45953,6 +46249,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M68" s="13">
+        <f>$Q$5*(B68/100*$Q$7*$Q$6)/($Q$6*$Q$8*A68)</f>
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -45984,6 +46284,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M69" s="13">
+        <f>$Q$5*(B69/100*$Q$7*$Q$6)/($Q$6*$Q$8*A69)</f>
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -46015,6 +46319,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M70" s="13">
+        <f>$Q$5*(B70/100*$Q$7*$Q$6)/($Q$6*$Q$8*A70)</f>
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -46046,6 +46354,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M71" s="13">
+        <f>$Q$5*(B71/100*$Q$7*$Q$6)/($Q$6*$Q$8*A71)</f>
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -46077,6 +46389,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M72" s="13">
+        <f>$Q$5*(B72/100*$Q$7*$Q$6)/($Q$6*$Q$8*A72)</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -46108,6 +46424,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M73" s="13">
+        <f>$Q$5*(B73/100*$Q$7*$Q$6)/($Q$6*$Q$8*A73)</f>
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -46139,6 +46459,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M74" s="13">
+        <f>$Q$5*(B74/100*$Q$7*$Q$6)/($Q$6*$Q$8*A74)</f>
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -46170,6 +46494,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M75" s="13">
+        <f>$Q$5*(B75/100*$Q$7*$Q$6)/($Q$6*$Q$8*A75)</f>
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -46201,6 +46529,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M76" s="13">
+        <f>$Q$5*(B76/100*$Q$7*$Q$6)/($Q$6*$Q$8*A76)</f>
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -46232,6 +46564,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M77" s="13">
+        <f>$Q$5*(B77/100*$Q$7*$Q$6)/($Q$6*$Q$8*A77)</f>
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -46263,6 +46599,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M78" s="13">
+        <f>$Q$5*(B78/100*$Q$7*$Q$6)/($Q$6*$Q$8*A78)</f>
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -46294,6 +46634,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M79" s="13">
+        <f>$Q$5*(B79/100*$Q$7*$Q$6)/($Q$6*$Q$8*A79)</f>
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -46325,6 +46669,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M80" s="13">
+        <f>$Q$5*(B80/100*$Q$7*$Q$6)/($Q$6*$Q$8*A80)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -46356,6 +46704,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M81" s="13">
+        <f>$Q$5*(B81/100*$Q$7*$Q$6)/($Q$6*$Q$8*A81)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -46387,6 +46739,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M82" s="13">
+        <f>$Q$5*(B82/100*$Q$7*$Q$6)/($Q$6*$Q$8*A82)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -46418,6 +46774,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M83" s="13">
+        <f>$Q$5*(B83/100*$Q$7*$Q$6)/($Q$6*$Q$8*A83)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -46449,6 +46809,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M84" s="13">
+        <f>$Q$5*(B84/100*$Q$7*$Q$6)/($Q$6*$Q$8*A84)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -46480,6 +46844,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M85" s="13">
+        <f>$Q$5*(B85/100*$Q$7*$Q$6)/($Q$6*$Q$8*A85)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -46511,6 +46879,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M86" s="13">
+        <f>$Q$5*(B86/100*$Q$7*$Q$6)/($Q$6*$Q$8*A86)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -46542,6 +46914,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M87" s="13">
+        <f>$Q$5*(B87/100*$Q$7*$Q$6)/($Q$6*$Q$8*A87)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -46573,6 +46949,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M88" s="13">
+        <f>$Q$5*(B88/100*$Q$7*$Q$6)/($Q$6*$Q$8*A88)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -46604,6 +46984,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M89" s="13">
+        <f>$Q$5*(B89/100*$Q$7*$Q$6)/($Q$6*$Q$8*A89)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -46635,6 +47019,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M90" s="13">
+        <f>$Q$5*(B90/100*$Q$7*$Q$6)/($Q$6*$Q$8*A90)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -46666,6 +47054,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M91" s="13">
+        <f>$Q$5*(B91/100*$Q$7*$Q$6)/($Q$6*$Q$8*A91)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -46697,6 +47089,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M92" s="13">
+        <f>$Q$5*(B92/100*$Q$7*$Q$6)/($Q$6*$Q$8*A92)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -46728,6 +47124,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M93" s="13">
+        <f>$Q$5*(B93/100*$Q$7*$Q$6)/($Q$6*$Q$8*A93)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -46759,6 +47159,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M94" s="13">
+        <f>$Q$5*(B94/100*$Q$7*$Q$6)/($Q$6*$Q$8*A94)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -46790,6 +47194,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M95" s="13">
+        <f>$Q$5*(B95/100*$Q$7*$Q$6)/($Q$6*$Q$8*A95)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -46821,6 +47229,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M96" s="13">
+        <f>$Q$5*(B96/100*$Q$7*$Q$6)/($Q$6*$Q$8*A96)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -46852,6 +47264,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M97" s="13">
+        <f>$Q$5*(B97/100*$Q$7*$Q$6)/($Q$6*$Q$8*A97)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -46883,6 +47299,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M98" s="13">
+        <f>$Q$5*(B98/100*$Q$7*$Q$6)/($Q$6*$Q$8*A98)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -46914,6 +47334,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M99" s="13">
+        <f>$Q$5*(B99/100*$Q$7*$Q$6)/($Q$6*$Q$8*A99)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -46945,6 +47369,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M100" s="13">
+        <f>$Q$5*(B100/100*$Q$7*$Q$6)/($Q$6*$Q$8*A100)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -46976,6 +47404,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M101" s="13">
+        <f>$Q$5*(B101/100*$Q$7*$Q$6)/($Q$6*$Q$8*A101)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -47007,6 +47439,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M102" s="13">
+        <f>$Q$5*(B102/100*$Q$7*$Q$6)/($Q$6*$Q$8*A102)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -47038,6 +47474,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M103" s="13">
+        <f>$Q$5*(B103/100*$Q$7*$Q$6)/($Q$6*$Q$8*A103)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -47069,6 +47509,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M104" s="13">
+        <f>$Q$5*(B104/100*$Q$7*$Q$6)/($Q$6*$Q$8*A104)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -47100,6 +47544,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M105" s="13">
+        <f>$Q$5*(B105/100*$Q$7*$Q$6)/($Q$6*$Q$8*A105)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -47131,6 +47579,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M106" s="13">
+        <f>$Q$5*(B106/100*$Q$7*$Q$6)/($Q$6*$Q$8*A106)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -47162,6 +47614,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M107" s="13">
+        <f>$Q$5*(B107/100*$Q$7*$Q$6)/($Q$6*$Q$8*A107)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -47193,6 +47649,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M108" s="13">
+        <f>$Q$5*(B108/100*$Q$7*$Q$6)/($Q$6*$Q$8*A108)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -47224,6 +47684,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M109" s="13">
+        <f>$Q$5*(B109/100*$Q$7*$Q$6)/($Q$6*$Q$8*A109)</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -47255,6 +47719,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M110" s="13">
+        <f>$Q$5*(B110/100*$Q$7*$Q$6)/($Q$6*$Q$8*A110)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -47286,6 +47754,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M111" s="13">
+        <f>$Q$5*(B111/100*$Q$7*$Q$6)/($Q$6*$Q$8*A111)</f>
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -47317,6 +47789,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M112" s="13">
+        <f>$Q$5*(B112/100*$Q$7*$Q$6)/($Q$6*$Q$8*A112)</f>
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -47348,6 +47824,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M113" s="13">
+        <f>$Q$5*(B113/100*$Q$7*$Q$6)/($Q$6*$Q$8*A113)</f>
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -47379,6 +47859,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M114" s="13">
+        <f>$Q$5*(B114/100*$Q$7*$Q$6)/($Q$6*$Q$8*A114)</f>
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -47410,6 +47894,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M115" s="13">
+        <f>$Q$5*(B115/100*$Q$7*$Q$6)/($Q$6*$Q$8*A115)</f>
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -47441,6 +47929,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M116" s="13">
+        <f>$Q$5*(B116/100*$Q$7*$Q$6)/($Q$6*$Q$8*A116)</f>
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -47472,6 +47964,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M117" s="13">
+        <f>$Q$5*(B117/100*$Q$7*$Q$6)/($Q$6*$Q$8*A117)</f>
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -47503,6 +47999,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M118" s="13">
+        <f>$Q$5*(B118/100*$Q$7*$Q$6)/($Q$6*$Q$8*A118)</f>
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -47534,6 +48034,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M119" s="13">
+        <f>$Q$5*(B119/100*$Q$7*$Q$6)/($Q$6*$Q$8*A119)</f>
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -47565,6 +48069,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M120" s="13">
+        <f>$Q$5*(B120/100*$Q$7*$Q$6)/($Q$6*$Q$8*A120)</f>
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -47596,6 +48104,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M121" s="13">
+        <f>$Q$5*(B121/100*$Q$7*$Q$6)/($Q$6*$Q$8*A121)</f>
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -47627,6 +48139,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M122" s="13">
+        <f>$Q$5*(B122/100*$Q$7*$Q$6)/($Q$6*$Q$8*A122)</f>
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -47658,6 +48174,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M123" s="13">
+        <f>$Q$5*(B123/100*$Q$7*$Q$6)/($Q$6*$Q$8*A123)</f>
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -47689,6 +48209,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M124" s="13">
+        <f>$Q$5*(B124/100*$Q$7*$Q$6)/($Q$6*$Q$8*A124)</f>
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -47720,6 +48244,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M125" s="13">
+        <f>$Q$5*(B125/100*$Q$7*$Q$6)/($Q$6*$Q$8*A125)</f>
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -47751,6 +48279,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M126" s="13">
+        <f>$Q$5*(B126/100*$Q$7*$Q$6)/($Q$6*$Q$8*A126)</f>
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -47782,6 +48314,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M127" s="13">
+        <f>$Q$5*(B127/100*$Q$7*$Q$6)/($Q$6*$Q$8*A127)</f>
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -47813,6 +48349,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M128" s="13">
+        <f>$Q$5*(B128/100*$Q$7*$Q$6)/($Q$6*$Q$8*A128)</f>
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -47844,6 +48384,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M129" s="13">
+        <f>$Q$5*(B129/100*$Q$7*$Q$6)/($Q$6*$Q$8*A129)</f>
+        <v/>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -47875,6 +48419,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M130" s="13">
+        <f>$Q$5*(B130/100*$Q$7*$Q$6)/($Q$6*$Q$8*A130)</f>
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -47906,6 +48454,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M131" s="13">
+        <f>$Q$5*(B131/100*$Q$7*$Q$6)/($Q$6*$Q$8*A131)</f>
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -47937,6 +48489,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M132" s="13">
+        <f>$Q$5*(B132/100*$Q$7*$Q$6)/($Q$6*$Q$8*A132)</f>
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -47968,6 +48524,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M133" s="13">
+        <f>$Q$5*(B133/100*$Q$7*$Q$6)/($Q$6*$Q$8*A133)</f>
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -47999,6 +48559,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M134" s="13">
+        <f>$Q$5*(B134/100*$Q$7*$Q$6)/($Q$6*$Q$8*A134)</f>
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -48030,6 +48594,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M135" s="13">
+        <f>$Q$5*(B135/100*$Q$7*$Q$6)/($Q$6*$Q$8*A135)</f>
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -48061,6 +48629,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M136" s="13">
+        <f>$Q$5*(B136/100*$Q$7*$Q$6)/($Q$6*$Q$8*A136)</f>
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -48092,6 +48664,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M137" s="13">
+        <f>$Q$5*(B137/100*$Q$7*$Q$6)/($Q$6*$Q$8*A137)</f>
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -48123,6 +48699,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M138" s="13">
+        <f>$Q$5*(B138/100*$Q$7*$Q$6)/($Q$6*$Q$8*A138)</f>
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -48154,6 +48734,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M139" s="13">
+        <f>$Q$5*(B139/100*$Q$7*$Q$6)/($Q$6*$Q$8*A139)</f>
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -48185,6 +48769,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M140" s="13">
+        <f>$Q$5*(B140/100*$Q$7*$Q$6)/($Q$6*$Q$8*A140)</f>
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -48216,6 +48804,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M141" s="13">
+        <f>$Q$5*(B141/100*$Q$7*$Q$6)/($Q$6*$Q$8*A141)</f>
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -48247,6 +48839,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M142" s="13">
+        <f>$Q$5*(B142/100*$Q$7*$Q$6)/($Q$6*$Q$8*A142)</f>
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -48278,6 +48874,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M143" s="13">
+        <f>$Q$5*(B143/100*$Q$7*$Q$6)/($Q$6*$Q$8*A143)</f>
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -48309,6 +48909,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M144" s="13">
+        <f>$Q$5*(B144/100*$Q$7*$Q$6)/($Q$6*$Q$8*A144)</f>
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -48340,6 +48944,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M145" s="13">
+        <f>$Q$5*(B145/100*$Q$7*$Q$6)/($Q$6*$Q$8*A145)</f>
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -48371,6 +48979,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M146" s="13">
+        <f>$Q$5*(B146/100*$Q$7*$Q$6)/($Q$6*$Q$8*A146)</f>
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -48402,6 +49014,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M147" s="13">
+        <f>$Q$5*(B147/100*$Q$7*$Q$6)/($Q$6*$Q$8*A147)</f>
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -48433,6 +49049,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M148" s="13">
+        <f>$Q$5*(B148/100*$Q$7*$Q$6)/($Q$6*$Q$8*A148)</f>
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -48464,6 +49084,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M149" s="13">
+        <f>$Q$5*(B149/100*$Q$7*$Q$6)/($Q$6*$Q$8*A149)</f>
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -48495,6 +49119,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M150" s="13">
+        <f>$Q$5*(B150/100*$Q$7*$Q$6)/($Q$6*$Q$8*A150)</f>
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -48526,6 +49154,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M151" s="13">
+        <f>$Q$5*(B151/100*$Q$7*$Q$6)/($Q$6*$Q$8*A151)</f>
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -48557,6 +49189,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M152" s="13">
+        <f>$Q$5*(B152/100*$Q$7*$Q$6)/($Q$6*$Q$8*A152)</f>
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -48588,6 +49224,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M153" s="13">
+        <f>$Q$5*(B153/100*$Q$7*$Q$6)/($Q$6*$Q$8*A153)</f>
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -48619,6 +49259,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M154" s="13">
+        <f>$Q$5*(B154/100*$Q$7*$Q$6)/($Q$6*$Q$8*A154)</f>
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -48650,6 +49294,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M155" s="13">
+        <f>$Q$5*(B155/100*$Q$7*$Q$6)/($Q$6*$Q$8*A155)</f>
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -48681,6 +49329,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M156" s="13">
+        <f>$Q$5*(B156/100*$Q$7*$Q$6)/($Q$6*$Q$8*A156)</f>
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -48712,6 +49364,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M157" s="13">
+        <f>$Q$5*(B157/100*$Q$7*$Q$6)/($Q$6*$Q$8*A157)</f>
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -48743,6 +49399,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M158" s="13">
+        <f>$Q$5*(B158/100*$Q$7*$Q$6)/($Q$6*$Q$8*A158)</f>
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -48774,6 +49434,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M159" s="13">
+        <f>$Q$5*(B159/100*$Q$7*$Q$6)/($Q$6*$Q$8*A159)</f>
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -48805,6 +49469,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M160" s="13">
+        <f>$Q$5*(B160/100*$Q$7*$Q$6)/($Q$6*$Q$8*A160)</f>
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -48836,6 +49504,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M161" s="13">
+        <f>$Q$5*(B161/100*$Q$7*$Q$6)/($Q$6*$Q$8*A161)</f>
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -48867,6 +49539,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M162" s="13">
+        <f>$Q$5*(B162/100*$Q$7*$Q$6)/($Q$6*$Q$8*A162)</f>
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -48898,6 +49574,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M163" s="13">
+        <f>$Q$5*(B163/100*$Q$7*$Q$6)/($Q$6*$Q$8*A163)</f>
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -48929,6 +49609,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M164" s="13">
+        <f>$Q$5*(B164/100*$Q$7*$Q$6)/($Q$6*$Q$8*A164)</f>
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -48960,6 +49644,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M165" s="13">
+        <f>$Q$5*(B165/100*$Q$7*$Q$6)/($Q$6*$Q$8*A165)</f>
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -48991,6 +49679,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M166" s="13">
+        <f>$Q$5*(B166/100*$Q$7*$Q$6)/($Q$6*$Q$8*A166)</f>
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -49022,6 +49714,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M167" s="13">
+        <f>$Q$5*(B167/100*$Q$7*$Q$6)/($Q$6*$Q$8*A167)</f>
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -49053,6 +49749,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M168" s="13">
+        <f>$Q$5*(B168/100*$Q$7*$Q$6)/($Q$6*$Q$8*A168)</f>
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -49084,6 +49784,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M169" s="13">
+        <f>$Q$5*(B169/100*$Q$7*$Q$6)/($Q$6*$Q$8*A169)</f>
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -49115,6 +49819,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M170" s="13">
+        <f>$Q$5*(B170/100*$Q$7*$Q$6)/($Q$6*$Q$8*A170)</f>
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -49146,6 +49854,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M171" s="13">
+        <f>$Q$5*(B171/100*$Q$7*$Q$6)/($Q$6*$Q$8*A171)</f>
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -49177,6 +49889,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M172" s="13">
+        <f>$Q$5*(B172/100*$Q$7*$Q$6)/($Q$6*$Q$8*A172)</f>
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -49208,6 +49924,10 @@
           <t>O2DiffusionLimited</t>
         </is>
       </c>
+      <c r="M173" s="13">
+        <f>$Q$5*(B173/100*$Q$7*$Q$6)/($Q$6*$Q$8*A173)</f>
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -49219,6 +49939,10 @@
       <c r="C174" s="1" t="n">
         <v>0.096069</v>
       </c>
+      <c r="M174" s="13">
+        <f>$Q$5*(B174/100*$Q$7*$Q$6)/($Q$6*$Q$8*A174)</f>
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -49230,6 +49954,10 @@
       <c r="C175" s="1" t="n">
         <v>0.095849</v>
       </c>
+      <c r="M175" s="13">
+        <f>$Q$5*(B175/100*$Q$7*$Q$6)/($Q$6*$Q$8*A175)</f>
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -49241,6 +49969,10 @@
       <c r="C176" s="1" t="n">
         <v>0.09562900000000001</v>
       </c>
+      <c r="M176" s="13">
+        <f>$Q$5*(B176/100*$Q$7*$Q$6)/($Q$6*$Q$8*A176)</f>
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -49252,6 +49984,10 @@
       <c r="C177" s="1" t="n">
         <v>0.095416</v>
       </c>
+      <c r="M177" s="13">
+        <f>$Q$5*(B177/100*$Q$7*$Q$6)/($Q$6*$Q$8*A177)</f>
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -49263,6 +49999,10 @@
       <c r="C178" s="1" t="n">
         <v>0.095208</v>
       </c>
+      <c r="M178" s="13">
+        <f>$Q$5*(B178/100*$Q$7*$Q$6)/($Q$6*$Q$8*A178)</f>
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -49274,6 +50014,10 @@
       <c r="C179" s="1" t="n">
         <v>0.095</v>
       </c>
+      <c r="M179" s="13">
+        <f>$Q$5*(B179/100*$Q$7*$Q$6)/($Q$6*$Q$8*A179)</f>
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -49285,6 +50029,10 @@
       <c r="C180" s="1" t="n">
         <v>0.094791</v>
       </c>
+      <c r="M180" s="13">
+        <f>$Q$5*(B180/100*$Q$7*$Q$6)/($Q$6*$Q$8*A180)</f>
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -49296,6 +50044,10 @@
       <c r="C181" s="1" t="n">
         <v>0.094579</v>
       </c>
+      <c r="M181" s="13">
+        <f>$Q$5*(B181/100*$Q$7*$Q$6)/($Q$6*$Q$8*A181)</f>
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -49307,6 +50059,10 @@
       <c r="C182" s="1" t="n">
         <v>0.094374</v>
       </c>
+      <c r="M182" s="13">
+        <f>$Q$5*(B182/100*$Q$7*$Q$6)/($Q$6*$Q$8*A182)</f>
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -49318,6 +50074,10 @@
       <c r="C183" s="1" t="n">
         <v>0.09417200000000001</v>
       </c>
+      <c r="M183" s="13">
+        <f>$Q$5*(B183/100*$Q$7*$Q$6)/($Q$6*$Q$8*A183)</f>
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -49329,6 +50089,10 @@
       <c r="C184" s="1" t="n">
         <v>0.093971</v>
       </c>
+      <c r="M184" s="13">
+        <f>$Q$5*(B184/100*$Q$7*$Q$6)/($Q$6*$Q$8*A184)</f>
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -49340,6 +50104,10 @@
       <c r="C185" s="1" t="n">
         <v>0.09377199999999999</v>
       </c>
+      <c r="M185" s="13">
+        <f>$Q$5*(B185/100*$Q$7*$Q$6)/($Q$6*$Q$8*A185)</f>
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -49351,6 +50119,10 @@
       <c r="C186" s="1" t="n">
         <v>0.09357600000000001</v>
       </c>
+      <c r="M186" s="13">
+        <f>$Q$5*(B186/100*$Q$7*$Q$6)/($Q$6*$Q$8*A186)</f>
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -49362,6 +50134,10 @@
       <c r="C187" s="1" t="n">
         <v>0.09338100000000001</v>
       </c>
+      <c r="M187" s="13">
+        <f>$Q$5*(B187/100*$Q$7*$Q$6)/($Q$6*$Q$8*A187)</f>
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -49373,6 +50149,10 @@
       <c r="C188" s="1" t="n">
         <v>0.093184</v>
       </c>
+      <c r="M188" s="13">
+        <f>$Q$5*(B188/100*$Q$7*$Q$6)/($Q$6*$Q$8*A188)</f>
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -49384,6 +50164,10 @@
       <c r="C189" s="1" t="n">
         <v>0.092991</v>
       </c>
+      <c r="M189" s="13">
+        <f>$Q$5*(B189/100*$Q$7*$Q$6)/($Q$6*$Q$8*A189)</f>
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -49395,6 +50179,10 @@
       <c r="C190" s="1" t="n">
         <v>0.092805</v>
       </c>
+      <c r="M190" s="13">
+        <f>$Q$5*(B190/100*$Q$7*$Q$6)/($Q$6*$Q$8*A190)</f>
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -49406,6 +50194,10 @@
       <c r="C191" s="1" t="n">
         <v>0.09261800000000001</v>
       </c>
+      <c r="M191" s="13">
+        <f>$Q$5*(B191/100*$Q$7*$Q$6)/($Q$6*$Q$8*A191)</f>
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -49417,6 +50209,10 @@
       <c r="C192" s="1" t="n">
         <v>0.09243</v>
       </c>
+      <c r="M192" s="13">
+        <f>$Q$5*(B192/100*$Q$7*$Q$6)/($Q$6*$Q$8*A192)</f>
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -49428,6 +50224,10 @@
       <c r="C193" s="1" t="n">
         <v>0.092247</v>
       </c>
+      <c r="M193" s="13">
+        <f>$Q$5*(B193/100*$Q$7*$Q$6)/($Q$6*$Q$8*A193)</f>
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -49439,6 +50239,10 @@
       <c r="C194" s="1" t="n">
         <v>0.092058</v>
       </c>
+      <c r="M194" s="13">
+        <f>$Q$5*(B194/100*$Q$7*$Q$6)/($Q$6*$Q$8*A194)</f>
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -49450,6 +50254,10 @@
       <c r="C195" s="1" t="n">
         <v>0.091876</v>
       </c>
+      <c r="M195" s="13">
+        <f>$Q$5*(B195/100*$Q$7*$Q$6)/($Q$6*$Q$8*A195)</f>
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -49461,6 +50269,10 @@
       <c r="C196" s="1" t="n">
         <v>0.0917</v>
       </c>
+      <c r="M196" s="13">
+        <f>$Q$5*(B196/100*$Q$7*$Q$6)/($Q$6*$Q$8*A196)</f>
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -49472,6 +50284,10 @@
       <c r="C197" s="1" t="n">
         <v>0.09152100000000001</v>
       </c>
+      <c r="M197" s="13">
+        <f>$Q$5*(B197/100*$Q$7*$Q$6)/($Q$6*$Q$8*A197)</f>
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -49483,6 +50299,10 @@
       <c r="C198" s="1" t="n">
         <v>0.091347</v>
       </c>
+      <c r="M198" s="13">
+        <f>$Q$5*(B198/100*$Q$7*$Q$6)/($Q$6*$Q$8*A198)</f>
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -49494,6 +50314,10 @@
       <c r="C199" s="1" t="n">
         <v>0.091172</v>
       </c>
+      <c r="M199" s="13">
+        <f>$Q$5*(B199/100*$Q$7*$Q$6)/($Q$6*$Q$8*A199)</f>
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -49505,6 +50329,10 @@
       <c r="C200" s="1" t="n">
         <v>0.091001</v>
       </c>
+      <c r="M200" s="13">
+        <f>$Q$5*(B200/100*$Q$7*$Q$6)/($Q$6*$Q$8*A200)</f>
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -49516,6 +50344,10 @@
       <c r="C201" s="1" t="n">
         <v>0.090831</v>
       </c>
+      <c r="M201" s="13">
+        <f>$Q$5*(B201/100*$Q$7*$Q$6)/($Q$6*$Q$8*A201)</f>
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -49527,6 +50359,10 @@
       <c r="C202" s="1" t="n">
         <v>0.09066100000000001</v>
       </c>
+      <c r="M202" s="13">
+        <f>$Q$5*(B202/100*$Q$7*$Q$6)/($Q$6*$Q$8*A202)</f>
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -49538,6 +50374,10 @@
       <c r="C203" s="1" t="n">
         <v>0.090492</v>
       </c>
+      <c r="M203" s="13">
+        <f>$Q$5*(B203/100*$Q$7*$Q$6)/($Q$6*$Q$8*A203)</f>
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -49549,6 +50389,10 @@
       <c r="C204" s="1" t="n">
         <v>0.090326</v>
       </c>
+      <c r="M204" s="13">
+        <f>$Q$5*(B204/100*$Q$7*$Q$6)/($Q$6*$Q$8*A204)</f>
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -49560,6 +50404,10 @@
       <c r="C205" s="1" t="n">
         <v>0.090158</v>
       </c>
+      <c r="M205" s="13">
+        <f>$Q$5*(B205/100*$Q$7*$Q$6)/($Q$6*$Q$8*A205)</f>
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -49571,6 +50419,10 @@
       <c r="C206" s="1" t="n">
         <v>0.08999500000000001</v>
       </c>
+      <c r="M206" s="13">
+        <f>$Q$5*(B206/100*$Q$7*$Q$6)/($Q$6*$Q$8*A206)</f>
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -49582,6 +50434,10 @@
       <c r="C207" s="1" t="n">
         <v>0.089835</v>
       </c>
+      <c r="M207" s="13">
+        <f>$Q$5*(B207/100*$Q$7*$Q$6)/($Q$6*$Q$8*A207)</f>
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -49593,6 +50449,10 @@
       <c r="C208" s="1" t="n">
         <v>0.08967600000000001</v>
       </c>
+      <c r="M208" s="13">
+        <f>$Q$5*(B208/100*$Q$7*$Q$6)/($Q$6*$Q$8*A208)</f>
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -49604,6 +50464,10 @@
       <c r="C209" s="1" t="n">
         <v>0.089518</v>
       </c>
+      <c r="M209" s="13">
+        <f>$Q$5*(B209/100*$Q$7*$Q$6)/($Q$6*$Q$8*A209)</f>
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -49615,6 +50479,10 @@
       <c r="C210" s="1" t="n">
         <v>0.08935899999999999</v>
       </c>
+      <c r="M210" s="13">
+        <f>$Q$5*(B210/100*$Q$7*$Q$6)/($Q$6*$Q$8*A210)</f>
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -49626,6 +50494,10 @@
       <c r="C211" s="1" t="n">
         <v>0.08920599999999999</v>
       </c>
+      <c r="M211" s="13">
+        <f>$Q$5*(B211/100*$Q$7*$Q$6)/($Q$6*$Q$8*A211)</f>
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -49637,6 +50509,10 @@
       <c r="C212" s="1" t="n">
         <v>0.089049</v>
       </c>
+      <c r="M212" s="13">
+        <f>$Q$5*(B212/100*$Q$7*$Q$6)/($Q$6*$Q$8*A212)</f>
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -49648,6 +50524,10 @@
       <c r="C213" s="1" t="n">
         <v>0.088897</v>
       </c>
+      <c r="M213" s="13">
+        <f>$Q$5*(B213/100*$Q$7*$Q$6)/($Q$6*$Q$8*A213)</f>
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -49659,6 +50539,10 @@
       <c r="C214" s="1" t="n">
         <v>0.088745</v>
       </c>
+      <c r="M214" s="13">
+        <f>$Q$5*(B214/100*$Q$7*$Q$6)/($Q$6*$Q$8*A214)</f>
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -49670,6 +50554,10 @@
       <c r="C215" s="1" t="n">
         <v>0.08859499999999999</v>
       </c>
+      <c r="M215" s="13">
+        <f>$Q$5*(B215/100*$Q$7*$Q$6)/($Q$6*$Q$8*A215)</f>
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -49681,6 +50569,10 @@
       <c r="C216" s="1" t="n">
         <v>0.08844200000000001</v>
       </c>
+      <c r="M216" s="13">
+        <f>$Q$5*(B216/100*$Q$7*$Q$6)/($Q$6*$Q$8*A216)</f>
+        <v/>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -49692,6 +50584,10 @@
       <c r="C217" s="1" t="n">
         <v>0.08829099999999999</v>
       </c>
+      <c r="M217" s="13">
+        <f>$Q$5*(B217/100*$Q$7*$Q$6)/($Q$6*$Q$8*A217)</f>
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -49703,6 +50599,10 @@
       <c r="C218" s="1" t="n">
         <v>0.088145</v>
       </c>
+      <c r="M218" s="13">
+        <f>$Q$5*(B218/100*$Q$7*$Q$6)/($Q$6*$Q$8*A218)</f>
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -49714,6 +50614,10 @@
       <c r="C219" s="1" t="n">
         <v>0.08799899999999999</v>
       </c>
+      <c r="M219" s="13">
+        <f>$Q$5*(B219/100*$Q$7*$Q$6)/($Q$6*$Q$8*A219)</f>
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -49725,6 +50629,10 @@
       <c r="C220" s="1" t="n">
         <v>0.087852</v>
       </c>
+      <c r="M220" s="13">
+        <f>$Q$5*(B220/100*$Q$7*$Q$6)/($Q$6*$Q$8*A220)</f>
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -49736,6 +50644,10 @@
       <c r="C221" s="1" t="n">
         <v>0.08770600000000001</v>
       </c>
+      <c r="M221" s="13">
+        <f>$Q$5*(B221/100*$Q$7*$Q$6)/($Q$6*$Q$8*A221)</f>
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -49747,6 +50659,10 @@
       <c r="C222" s="1" t="n">
         <v>0.087559</v>
       </c>
+      <c r="M222" s="13">
+        <f>$Q$5*(B222/100*$Q$7*$Q$6)/($Q$6*$Q$8*A222)</f>
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -49758,6 +50674,10 @@
       <c r="C223" s="1" t="n">
         <v>0.08741599999999999</v>
       </c>
+      <c r="M223" s="13">
+        <f>$Q$5*(B223/100*$Q$7*$Q$6)/($Q$6*$Q$8*A223)</f>
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -49769,6 +50689,10 @@
       <c r="C224" s="1" t="n">
         <v>0.08727699999999999</v>
       </c>
+      <c r="M224" s="13">
+        <f>$Q$5*(B224/100*$Q$7*$Q$6)/($Q$6*$Q$8*A224)</f>
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -49780,6 +50704,10 @@
       <c r="C225" s="1" t="n">
         <v>0.087134</v>
       </c>
+      <c r="M225" s="13">
+        <f>$Q$5*(B225/100*$Q$7*$Q$6)/($Q$6*$Q$8*A225)</f>
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -49791,6 +50719,10 @@
       <c r="C226" s="1" t="n">
         <v>0.08699800000000001</v>
       </c>
+      <c r="M226" s="13">
+        <f>$Q$5*(B226/100*$Q$7*$Q$6)/($Q$6*$Q$8*A226)</f>
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -49802,6 +50734,10 @@
       <c r="C227" s="1" t="n">
         <v>0.08686099999999999</v>
       </c>
+      <c r="M227" s="13">
+        <f>$Q$5*(B227/100*$Q$7*$Q$6)/($Q$6*$Q$8*A227)</f>
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -49813,6 +50749,10 @@
       <c r="C228" s="1" t="n">
         <v>0.086727</v>
       </c>
+      <c r="M228" s="13">
+        <f>$Q$5*(B228/100*$Q$7*$Q$6)/($Q$6*$Q$8*A228)</f>
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -49824,6 +50764,10 @@
       <c r="C229" s="1" t="n">
         <v>0.086589</v>
       </c>
+      <c r="M229" s="13">
+        <f>$Q$5*(B229/100*$Q$7*$Q$6)/($Q$6*$Q$8*A229)</f>
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -49835,6 +50779,10 @@
       <c r="C230" s="1" t="n">
         <v>0.086455</v>
       </c>
+      <c r="M230" s="13">
+        <f>$Q$5*(B230/100*$Q$7*$Q$6)/($Q$6*$Q$8*A230)</f>
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -49846,6 +50794,10 @@
       <c r="C231" s="1" t="n">
         <v>0.086323</v>
       </c>
+      <c r="M231" s="13">
+        <f>$Q$5*(B231/100*$Q$7*$Q$6)/($Q$6*$Q$8*A231)</f>
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -49857,6 +50809,10 @@
       <c r="C232" s="1" t="n">
         <v>0.08619</v>
       </c>
+      <c r="M232" s="13">
+        <f>$Q$5*(B232/100*$Q$7*$Q$6)/($Q$6*$Q$8*A232)</f>
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -49868,6 +50824,10 @@
       <c r="C233" s="1" t="n">
         <v>0.08605400000000001</v>
       </c>
+      <c r="M233" s="13">
+        <f>$Q$5*(B233/100*$Q$7*$Q$6)/($Q$6*$Q$8*A233)</f>
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -49879,6 +50839,10 @@
       <c r="C234" s="1" t="n">
         <v>0.085923</v>
       </c>
+      <c r="M234" s="13">
+        <f>$Q$5*(B234/100*$Q$7*$Q$6)/($Q$6*$Q$8*A234)</f>
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -49890,6 +50854,10 @@
       <c r="C235" s="1" t="n">
         <v>0.08579299999999999</v>
       </c>
+      <c r="M235" s="13">
+        <f>$Q$5*(B235/100*$Q$7*$Q$6)/($Q$6*$Q$8*A235)</f>
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -49901,6 +50869,10 @@
       <c r="C236" s="1" t="n">
         <v>0.085663</v>
       </c>
+      <c r="M236" s="13">
+        <f>$Q$5*(B236/100*$Q$7*$Q$6)/($Q$6*$Q$8*A236)</f>
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -49912,6 +50884,10 @@
       <c r="C237" s="1" t="n">
         <v>0.085534</v>
       </c>
+      <c r="M237" s="13">
+        <f>$Q$5*(B237/100*$Q$7*$Q$6)/($Q$6*$Q$8*A237)</f>
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -49923,6 +50899,10 @@
       <c r="C238" s="1" t="n">
         <v>0.085408</v>
       </c>
+      <c r="M238" s="13">
+        <f>$Q$5*(B238/100*$Q$7*$Q$6)/($Q$6*$Q$8*A238)</f>
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -49934,6 +50914,10 @@
       <c r="C239" s="1" t="n">
         <v>0.085281</v>
       </c>
+      <c r="M239" s="13">
+        <f>$Q$5*(B239/100*$Q$7*$Q$6)/($Q$6*$Q$8*A239)</f>
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -49945,6 +50929,10 @@
       <c r="C240" s="1" t="n">
         <v>0.08515499999999999</v>
       </c>
+      <c r="M240" s="13">
+        <f>$Q$5*(B240/100*$Q$7*$Q$6)/($Q$6*$Q$8*A240)</f>
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -49956,6 +50944,10 @@
       <c r="C241" s="1" t="n">
         <v>0.08502700000000001</v>
       </c>
+      <c r="M241" s="13">
+        <f>$Q$5*(B241/100*$Q$7*$Q$6)/($Q$6*$Q$8*A241)</f>
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -49967,6 +50959,10 @@
       <c r="C242" s="1" t="n">
         <v>0.08490499999999999</v>
       </c>
+      <c r="M242" s="13">
+        <f>$Q$5*(B242/100*$Q$7*$Q$6)/($Q$6*$Q$8*A242)</f>
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -49978,6 +50974,10 @@
       <c r="C243" s="1" t="n">
         <v>0.084783</v>
       </c>
+      <c r="M243" s="13">
+        <f>$Q$5*(B243/100*$Q$7*$Q$6)/($Q$6*$Q$8*A243)</f>
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -49989,6 +50989,10 @@
       <c r="C244" s="1" t="n">
         <v>0.084661</v>
       </c>
+      <c r="M244" s="13">
+        <f>$Q$5*(B244/100*$Q$7*$Q$6)/($Q$6*$Q$8*A244)</f>
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -50000,6 +51004,10 @@
       <c r="C245" s="1" t="n">
         <v>0.084539</v>
       </c>
+      <c r="M245" s="13">
+        <f>$Q$5*(B245/100*$Q$7*$Q$6)/($Q$6*$Q$8*A245)</f>
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -50011,6 +51019,10 @@
       <c r="C246" s="1" t="n">
         <v>0.084416</v>
       </c>
+      <c r="M246" s="13">
+        <f>$Q$5*(B246/100*$Q$7*$Q$6)/($Q$6*$Q$8*A246)</f>
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -50022,6 +51034,10 @@
       <c r="C247" s="1" t="n">
         <v>0.08429399999999999</v>
       </c>
+      <c r="M247" s="13">
+        <f>$Q$5*(B247/100*$Q$7*$Q$6)/($Q$6*$Q$8*A247)</f>
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -50033,6 +51049,10 @@
       <c r="C248" s="1" t="n">
         <v>0.084175</v>
       </c>
+      <c r="M248" s="13">
+        <f>$Q$5*(B248/100*$Q$7*$Q$6)/($Q$6*$Q$8*A248)</f>
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -50044,6 +51064,10 @@
       <c r="C249" s="1" t="n">
         <v>0.084054</v>
       </c>
+      <c r="M249" s="13">
+        <f>$Q$5*(B249/100*$Q$7*$Q$6)/($Q$6*$Q$8*A249)</f>
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -50055,6 +51079,10 @@
       <c r="C250" s="1" t="n">
         <v>0.083936</v>
       </c>
+      <c r="M250" s="13">
+        <f>$Q$5*(B250/100*$Q$7*$Q$6)/($Q$6*$Q$8*A250)</f>
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -50066,6 +51094,10 @@
       <c r="C251" s="1" t="n">
         <v>0.083819</v>
       </c>
+      <c r="M251" s="13">
+        <f>$Q$5*(B251/100*$Q$7*$Q$6)/($Q$6*$Q$8*A251)</f>
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -50077,6 +51109,10 @@
       <c r="C252" s="1" t="n">
         <v>0.083702</v>
       </c>
+      <c r="M252" s="13">
+        <f>$Q$5*(B252/100*$Q$7*$Q$6)/($Q$6*$Q$8*A252)</f>
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -50088,6 +51124,10 @@
       <c r="C253" s="1" t="n">
         <v>0.083588</v>
       </c>
+      <c r="M253" s="13">
+        <f>$Q$5*(B253/100*$Q$7*$Q$6)/($Q$6*$Q$8*A253)</f>
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -50099,6 +51139,10 @@
       <c r="C254" s="1" t="n">
         <v>0.08347300000000001</v>
       </c>
+      <c r="M254" s="13">
+        <f>$Q$5*(B254/100*$Q$7*$Q$6)/($Q$6*$Q$8*A254)</f>
+        <v/>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -50110,6 +51154,10 @@
       <c r="C255" s="1" t="n">
         <v>0.08336200000000001</v>
       </c>
+      <c r="M255" s="13">
+        <f>$Q$5*(B255/100*$Q$7*$Q$6)/($Q$6*$Q$8*A255)</f>
+        <v/>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -50121,6 +51169,10 @@
       <c r="C256" s="1" t="n">
         <v>0.083247</v>
       </c>
+      <c r="M256" s="13">
+        <f>$Q$5*(B256/100*$Q$7*$Q$6)/($Q$6*$Q$8*A256)</f>
+        <v/>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -50132,6 +51184,10 @@
       <c r="C257" s="1" t="n">
         <v>0.083133</v>
       </c>
+      <c r="M257" s="13">
+        <f>$Q$5*(B257/100*$Q$7*$Q$6)/($Q$6*$Q$8*A257)</f>
+        <v/>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -50143,6 +51199,10 @@
       <c r="C258" s="1" t="n">
         <v>0.083021</v>
       </c>
+      <c r="M258" s="13">
+        <f>$Q$5*(B258/100*$Q$7*$Q$6)/($Q$6*$Q$8*A258)</f>
+        <v/>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -50154,6 +51214,10 @@
       <c r="C259" s="1" t="n">
         <v>0.08290699999999999</v>
       </c>
+      <c r="M259" s="13">
+        <f>$Q$5*(B259/100*$Q$7*$Q$6)/($Q$6*$Q$8*A259)</f>
+        <v/>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -50165,6 +51229,10 @@
       <c r="C260" s="1" t="n">
         <v>0.08279400000000001</v>
       </c>
+      <c r="M260" s="13">
+        <f>$Q$5*(B260/100*$Q$7*$Q$6)/($Q$6*$Q$8*A260)</f>
+        <v/>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -50176,6 +51244,10 @@
       <c r="C261" s="1" t="n">
         <v>0.08268</v>
       </c>
+      <c r="M261" s="13">
+        <f>$Q$5*(B261/100*$Q$7*$Q$6)/($Q$6*$Q$8*A261)</f>
+        <v/>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -50187,6 +51259,10 @@
       <c r="C262" s="1" t="n">
         <v>0.082566</v>
       </c>
+      <c r="M262" s="13">
+        <f>$Q$5*(B262/100*$Q$7*$Q$6)/($Q$6*$Q$8*A262)</f>
+        <v/>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -50198,6 +51274,10 @@
       <c r="C263" s="1" t="n">
         <v>0.082455</v>
       </c>
+      <c r="M263" s="13">
+        <f>$Q$5*(B263/100*$Q$7*$Q$6)/($Q$6*$Q$8*A263)</f>
+        <v/>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -50209,6 +51289,10 @@
       <c r="C264" s="1" t="n">
         <v>0.082342</v>
       </c>
+      <c r="M264" s="13">
+        <f>$Q$5*(B264/100*$Q$7*$Q$6)/($Q$6*$Q$8*A264)</f>
+        <v/>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -50220,6 +51304,10 @@
       <c r="C265" s="1" t="n">
         <v>0.082232</v>
       </c>
+      <c r="M265" s="13">
+        <f>$Q$5*(B265/100*$Q$7*$Q$6)/($Q$6*$Q$8*A265)</f>
+        <v/>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -50231,6 +51319,10 @@
       <c r="C266" s="1" t="n">
         <v>0.082125</v>
       </c>
+      <c r="M266" s="13">
+        <f>$Q$5*(B266/100*$Q$7*$Q$6)/($Q$6*$Q$8*A266)</f>
+        <v/>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -50242,6 +51334,10 @@
       <c r="C267" s="1" t="n">
         <v>0.082015</v>
       </c>
+      <c r="M267" s="13">
+        <f>$Q$5*(B267/100*$Q$7*$Q$6)/($Q$6*$Q$8*A267)</f>
+        <v/>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -50253,6 +51349,10 @@
       <c r="C268" s="1" t="n">
         <v>0.08190500000000001</v>
       </c>
+      <c r="M268" s="13">
+        <f>$Q$5*(B268/100*$Q$7*$Q$6)/($Q$6*$Q$8*A268)</f>
+        <v/>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -50264,6 +51364,10 @@
       <c r="C269" s="1" t="n">
         <v>0.08179699999999999</v>
       </c>
+      <c r="M269" s="13">
+        <f>$Q$5*(B269/100*$Q$7*$Q$6)/($Q$6*$Q$8*A269)</f>
+        <v/>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -50275,6 +51379,10 @@
       <c r="C270" s="1" t="n">
         <v>0.08169</v>
       </c>
+      <c r="M270" s="13">
+        <f>$Q$5*(B270/100*$Q$7*$Q$6)/($Q$6*$Q$8*A270)</f>
+        <v/>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -50286,6 +51394,10 @@
       <c r="C271" s="1" t="n">
         <v>0.081584</v>
       </c>
+      <c r="M271" s="13">
+        <f>$Q$5*(B271/100*$Q$7*$Q$6)/($Q$6*$Q$8*A271)</f>
+        <v/>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -50297,6 +51409,10 @@
       <c r="C272" s="1" t="n">
         <v>0.08147799999999999</v>
       </c>
+      <c r="M272" s="13">
+        <f>$Q$5*(B272/100*$Q$7*$Q$6)/($Q$6*$Q$8*A272)</f>
+        <v/>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -50308,6 +51424,10 @@
       <c r="C273" s="1" t="n">
         <v>0.081369</v>
       </c>
+      <c r="M273" s="13">
+        <f>$Q$5*(B273/100*$Q$7*$Q$6)/($Q$6*$Q$8*A273)</f>
+        <v/>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -50319,6 +51439,10 @@
       <c r="C274" s="1" t="n">
         <v>0.081264</v>
       </c>
+      <c r="M274" s="13">
+        <f>$Q$5*(B274/100*$Q$7*$Q$6)/($Q$6*$Q$8*A274)</f>
+        <v/>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -50330,6 +51454,10 @@
       <c r="C275" s="1" t="n">
         <v>0.08115700000000001</v>
       </c>
+      <c r="M275" s="13">
+        <f>$Q$5*(B275/100*$Q$7*$Q$6)/($Q$6*$Q$8*A275)</f>
+        <v/>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -50341,6 +51469,10 @@
       <c r="C276" s="1" t="n">
         <v>0.081052</v>
       </c>
+      <c r="M276" s="13">
+        <f>$Q$5*(B276/100*$Q$7*$Q$6)/($Q$6*$Q$8*A276)</f>
+        <v/>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -50352,6 +51484,10 @@
       <c r="C277" s="1" t="n">
         <v>0.080944</v>
       </c>
+      <c r="M277" s="13">
+        <f>$Q$5*(B277/100*$Q$7*$Q$6)/($Q$6*$Q$8*A277)</f>
+        <v/>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -50363,6 +51499,10 @@
       <c r="C278" s="1" t="n">
         <v>0.080842</v>
       </c>
+      <c r="M278" s="13">
+        <f>$Q$5*(B278/100*$Q$7*$Q$6)/($Q$6*$Q$8*A278)</f>
+        <v/>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -50374,6 +51514,10 @@
       <c r="C279" s="1" t="n">
         <v>0.08074000000000001</v>
       </c>
+      <c r="M279" s="13">
+        <f>$Q$5*(B279/100*$Q$7*$Q$6)/($Q$6*$Q$8*A279)</f>
+        <v/>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -50385,6 +51529,10 @@
       <c r="C280" s="1" t="n">
         <v>0.08064300000000001</v>
       </c>
+      <c r="M280" s="13">
+        <f>$Q$5*(B280/100*$Q$7*$Q$6)/($Q$6*$Q$8*A280)</f>
+        <v/>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -50396,6 +51544,10 @@
       <c r="C281" s="1" t="n">
         <v>0.080541</v>
       </c>
+      <c r="M281" s="13">
+        <f>$Q$5*(B281/100*$Q$7*$Q$6)/($Q$6*$Q$8*A281)</f>
+        <v/>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -50407,6 +51559,10 @@
       <c r="C282" s="1" t="n">
         <v>0.080438</v>
       </c>
+      <c r="M282" s="13">
+        <f>$Q$5*(B282/100*$Q$7*$Q$6)/($Q$6*$Q$8*A282)</f>
+        <v/>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -50418,6 +51574,10 @@
       <c r="C283" s="1" t="n">
         <v>0.080336</v>
       </c>
+      <c r="M283" s="13">
+        <f>$Q$5*(B283/100*$Q$7*$Q$6)/($Q$6*$Q$8*A283)</f>
+        <v/>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -50429,6 +51589,10 @@
       <c r="C284" s="1" t="n">
         <v>0.080236</v>
       </c>
+      <c r="M284" s="13">
+        <f>$Q$5*(B284/100*$Q$7*$Q$6)/($Q$6*$Q$8*A284)</f>
+        <v/>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -50440,6 +51604,10 @@
       <c r="C285" s="1" t="n">
         <v>0.080135</v>
       </c>
+      <c r="M285" s="13">
+        <f>$Q$5*(B285/100*$Q$7*$Q$6)/($Q$6*$Q$8*A285)</f>
+        <v/>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -50451,6 +51619,10 @@
       <c r="C286" s="1" t="n">
         <v>0.08003399999999999</v>
       </c>
+      <c r="M286" s="13">
+        <f>$Q$5*(B286/100*$Q$7*$Q$6)/($Q$6*$Q$8*A286)</f>
+        <v/>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -50462,6 +51634,10 @@
       <c r="C287" s="1" t="n">
         <v>0.07993400000000001</v>
       </c>
+      <c r="M287" s="13">
+        <f>$Q$5*(B287/100*$Q$7*$Q$6)/($Q$6*$Q$8*A287)</f>
+        <v/>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -50473,6 +51649,10 @@
       <c r="C288" s="1" t="n">
         <v>0.079833</v>
       </c>
+      <c r="M288" s="13">
+        <f>$Q$5*(B288/100*$Q$7*$Q$6)/($Q$6*$Q$8*A288)</f>
+        <v/>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -50484,6 +51664,10 @@
       <c r="C289" s="1" t="n">
         <v>0.079734</v>
       </c>
+      <c r="M289" s="13">
+        <f>$Q$5*(B289/100*$Q$7*$Q$6)/($Q$6*$Q$8*A289)</f>
+        <v/>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -50495,6 +51679,10 @@
       <c r="C290" s="1" t="n">
         <v>0.079635</v>
       </c>
+      <c r="M290" s="13">
+        <f>$Q$5*(B290/100*$Q$7*$Q$6)/($Q$6*$Q$8*A290)</f>
+        <v/>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -50506,6 +51694,10 @@
       <c r="C291" s="1" t="n">
         <v>0.079536</v>
       </c>
+      <c r="M291" s="13">
+        <f>$Q$5*(B291/100*$Q$7*$Q$6)/($Q$6*$Q$8*A291)</f>
+        <v/>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -50517,6 +51709,10 @@
       <c r="C292" s="1" t="n">
         <v>0.07943799999999999</v>
       </c>
+      <c r="M292" s="13">
+        <f>$Q$5*(B292/100*$Q$7*$Q$6)/($Q$6*$Q$8*A292)</f>
+        <v/>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -50528,6 +51724,10 @@
       <c r="C293" s="1" t="n">
         <v>0.07933999999999999</v>
       </c>
+      <c r="M293" s="13">
+        <f>$Q$5*(B293/100*$Q$7*$Q$6)/($Q$6*$Q$8*A293)</f>
+        <v/>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -50539,6 +51739,10 @@
       <c r="C294" s="1" t="n">
         <v>0.07924200000000001</v>
       </c>
+      <c r="M294" s="13">
+        <f>$Q$5*(B294/100*$Q$7*$Q$6)/($Q$6*$Q$8*A294)</f>
+        <v/>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -50550,6 +51754,10 @@
       <c r="C295" s="1" t="n">
         <v>0.079149</v>
       </c>
+      <c r="M295" s="13">
+        <f>$Q$5*(B295/100*$Q$7*$Q$6)/($Q$6*$Q$8*A295)</f>
+        <v/>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -50561,6 +51769,10 @@
       <c r="C296" s="1" t="n">
         <v>0.079055</v>
       </c>
+      <c r="M296" s="13">
+        <f>$Q$5*(B296/100*$Q$7*$Q$6)/($Q$6*$Q$8*A296)</f>
+        <v/>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -50572,6 +51784,10 @@
       <c r="C297" s="1" t="n">
         <v>0.07896</v>
       </c>
+      <c r="M297" s="13">
+        <f>$Q$5*(B297/100*$Q$7*$Q$6)/($Q$6*$Q$8*A297)</f>
+        <v/>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -50583,6 +51799,10 @@
       <c r="C298" s="1" t="n">
         <v>0.078865</v>
       </c>
+      <c r="M298" s="13">
+        <f>$Q$5*(B298/100*$Q$7*$Q$6)/($Q$6*$Q$8*A298)</f>
+        <v/>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -50594,6 +51814,10 @@
       <c r="C299" s="1" t="n">
         <v>0.078767</v>
       </c>
+      <c r="M299" s="13">
+        <f>$Q$5*(B299/100*$Q$7*$Q$6)/($Q$6*$Q$8*A299)</f>
+        <v/>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -50605,6 +51829,10 @@
       <c r="C300" s="1" t="n">
         <v>0.07867300000000001</v>
       </c>
+      <c r="M300" s="13">
+        <f>$Q$5*(B300/100*$Q$7*$Q$6)/($Q$6*$Q$8*A300)</f>
+        <v/>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -50616,6 +51844,10 @@
       <c r="C301" s="1" t="n">
         <v>0.078581</v>
       </c>
+      <c r="M301" s="13">
+        <f>$Q$5*(B301/100*$Q$7*$Q$6)/($Q$6*$Q$8*A301)</f>
+        <v/>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -50627,6 +51859,10 @@
       <c r="C302" s="1" t="n">
         <v>0.078487</v>
       </c>
+      <c r="M302" s="13">
+        <f>$Q$5*(B302/100*$Q$7*$Q$6)/($Q$6*$Q$8*A302)</f>
+        <v/>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -50638,6 +51874,10 @@
       <c r="C303" s="1" t="n">
         <v>0.07839500000000001</v>
       </c>
+      <c r="M303" s="13">
+        <f>$Q$5*(B303/100*$Q$7*$Q$6)/($Q$6*$Q$8*A303)</f>
+        <v/>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -50649,6 +51889,10 @@
       <c r="C304" s="1" t="n">
         <v>0.07829999999999999</v>
       </c>
+      <c r="M304" s="13">
+        <f>$Q$5*(B304/100*$Q$7*$Q$6)/($Q$6*$Q$8*A304)</f>
+        <v/>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -50660,6 +51904,10 @@
       <c r="C305" s="1" t="n">
         <v>0.078204</v>
       </c>
+      <c r="M305" s="13">
+        <f>$Q$5*(B305/100*$Q$7*$Q$6)/($Q$6*$Q$8*A305)</f>
+        <v/>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -50671,6 +51919,10 @@
       <c r="C306" s="1" t="n">
         <v>0.078113</v>
       </c>
+      <c r="M306" s="13">
+        <f>$Q$5*(B306/100*$Q$7*$Q$6)/($Q$6*$Q$8*A306)</f>
+        <v/>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -50682,6 +51934,10 @@
       <c r="C307" s="1" t="n">
         <v>0.07802099999999999</v>
       </c>
+      <c r="M307" s="13">
+        <f>$Q$5*(B307/100*$Q$7*$Q$6)/($Q$6*$Q$8*A307)</f>
+        <v/>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -50693,6 +51949,10 @@
       <c r="C308" s="1" t="n">
         <v>0.07793</v>
       </c>
+      <c r="M308" s="13">
+        <f>$Q$5*(B308/100*$Q$7*$Q$6)/($Q$6*$Q$8*A308)</f>
+        <v/>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -50704,6 +51964,10 @@
       <c r="C309" s="1" t="n">
         <v>0.07783900000000001</v>
       </c>
+      <c r="M309" s="13">
+        <f>$Q$5*(B309/100*$Q$7*$Q$6)/($Q$6*$Q$8*A309)</f>
+        <v/>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -50715,6 +51979,10 @@
       <c r="C310" s="1" t="n">
         <v>0.077748</v>
       </c>
+      <c r="M310" s="13">
+        <f>$Q$5*(B310/100*$Q$7*$Q$6)/($Q$6*$Q$8*A310)</f>
+        <v/>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -50726,6 +51994,10 @@
       <c r="C311" s="1" t="n">
         <v>0.077657</v>
       </c>
+      <c r="M311" s="13">
+        <f>$Q$5*(B311/100*$Q$7*$Q$6)/($Q$6*$Q$8*A311)</f>
+        <v/>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
@@ -50737,6 +52009,10 @@
       <c r="C312" s="1" t="n">
         <v>0.077565</v>
       </c>
+      <c r="M312" s="13">
+        <f>$Q$5*(B312/100*$Q$7*$Q$6)/($Q$6*$Q$8*A312)</f>
+        <v/>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
@@ -50748,6 +52024,10 @@
       <c r="C313" s="1" t="n">
         <v>0.07747800000000001</v>
       </c>
+      <c r="M313" s="13">
+        <f>$Q$5*(B313/100*$Q$7*$Q$6)/($Q$6*$Q$8*A313)</f>
+        <v/>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
@@ -50759,6 +52039,10 @@
       <c r="C314" s="1" t="n">
         <v>0.077387</v>
       </c>
+      <c r="M314" s="13">
+        <f>$Q$5*(B314/100*$Q$7*$Q$6)/($Q$6*$Q$8*A314)</f>
+        <v/>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
@@ -50770,6 +52054,10 @@
       <c r="C315" s="1" t="n">
         <v>0.07729800000000001</v>
       </c>
+      <c r="M315" s="13">
+        <f>$Q$5*(B315/100*$Q$7*$Q$6)/($Q$6*$Q$8*A315)</f>
+        <v/>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
@@ -50781,6 +52069,10 @@
       <c r="C316" s="1" t="n">
         <v>0.07721</v>
       </c>
+      <c r="M316" s="13">
+        <f>$Q$5*(B316/100*$Q$7*$Q$6)/($Q$6*$Q$8*A316)</f>
+        <v/>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -50792,6 +52084,10 @@
       <c r="C317" s="1" t="n">
         <v>0.077121</v>
       </c>
+      <c r="M317" s="13">
+        <f>$Q$5*(B317/100*$Q$7*$Q$6)/($Q$6*$Q$8*A317)</f>
+        <v/>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -50803,6 +52099,10 @@
       <c r="C318" s="1" t="n">
         <v>0.077032</v>
       </c>
+      <c r="M318" s="13">
+        <f>$Q$5*(B318/100*$Q$7*$Q$6)/($Q$6*$Q$8*A318)</f>
+        <v/>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -50814,6 +52114,10 @@
       <c r="C319" s="1" t="n">
         <v>0.076948</v>
       </c>
+      <c r="M319" s="13">
+        <f>$Q$5*(B319/100*$Q$7*$Q$6)/($Q$6*$Q$8*A319)</f>
+        <v/>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -50825,6 +52129,10 @@
       <c r="C320" s="1" t="n">
         <v>0.076863</v>
       </c>
+      <c r="M320" s="13">
+        <f>$Q$5*(B320/100*$Q$7*$Q$6)/($Q$6*$Q$8*A320)</f>
+        <v/>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -50836,6 +52144,10 @@
       <c r="C321" s="1" t="n">
         <v>0.076777</v>
       </c>
+      <c r="M321" s="13">
+        <f>$Q$5*(B321/100*$Q$7*$Q$6)/($Q$6*$Q$8*A321)</f>
+        <v/>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -50847,6 +52159,10 @@
       <c r="C322" s="1" t="n">
         <v>0.07668899999999999</v>
       </c>
+      <c r="M322" s="13">
+        <f>$Q$5*(B322/100*$Q$7*$Q$6)/($Q$6*$Q$8*A322)</f>
+        <v/>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -50858,6 +52174,10 @@
       <c r="C323" s="1" t="n">
         <v>0.07660400000000001</v>
       </c>
+      <c r="M323" s="13">
+        <f>$Q$5*(B323/100*$Q$7*$Q$6)/($Q$6*$Q$8*A323)</f>
+        <v/>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -50869,6 +52189,10 @@
       <c r="C324" s="1" t="n">
         <v>0.076517</v>
       </c>
+      <c r="M324" s="13">
+        <f>$Q$5*(B324/100*$Q$7*$Q$6)/($Q$6*$Q$8*A324)</f>
+        <v/>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -50880,6 +52204,10 @@
       <c r="C325" s="1" t="n">
         <v>0.076434</v>
       </c>
+      <c r="M325" s="13">
+        <f>$Q$5*(B325/100*$Q$7*$Q$6)/($Q$6*$Q$8*A325)</f>
+        <v/>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -50891,6 +52219,10 @@
       <c r="C326" s="1" t="n">
         <v>0.076347</v>
       </c>
+      <c r="M326" s="13">
+        <f>$Q$5*(B326/100*$Q$7*$Q$6)/($Q$6*$Q$8*A326)</f>
+        <v/>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -50902,6 +52234,10 @@
       <c r="C327" s="1" t="n">
         <v>0.076265</v>
       </c>
+      <c r="M327" s="13">
+        <f>$Q$5*(B327/100*$Q$7*$Q$6)/($Q$6*$Q$8*A327)</f>
+        <v/>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -50913,6 +52249,10 @@
       <c r="C328" s="1" t="n">
         <v>0.076182</v>
       </c>
+      <c r="M328" s="13">
+        <f>$Q$5*(B328/100*$Q$7*$Q$6)/($Q$6*$Q$8*A328)</f>
+        <v/>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -50924,6 +52264,10 @@
       <c r="C329" s="1" t="n">
         <v>0.076098</v>
       </c>
+      <c r="M329" s="13">
+        <f>$Q$5*(B329/100*$Q$7*$Q$6)/($Q$6*$Q$8*A329)</f>
+        <v/>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -50935,6 +52279,10 @@
       <c r="C330" s="1" t="n">
         <v>0.076014</v>
       </c>
+      <c r="M330" s="13">
+        <f>$Q$5*(B330/100*$Q$7*$Q$6)/($Q$6*$Q$8*A330)</f>
+        <v/>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -50946,6 +52294,10 @@
       <c r="C331" s="1" t="n">
         <v>0.075931</v>
       </c>
+      <c r="M331" s="13">
+        <f>$Q$5*(B331/100*$Q$7*$Q$6)/($Q$6*$Q$8*A331)</f>
+        <v/>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -50957,6 +52309,10 @@
       <c r="C332" s="1" t="n">
         <v>0.07585</v>
       </c>
+      <c r="M332" s="13">
+        <f>$Q$5*(B332/100*$Q$7*$Q$6)/($Q$6*$Q$8*A332)</f>
+        <v/>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -50968,6 +52324,10 @@
       <c r="C333" s="1" t="n">
         <v>0.075766</v>
       </c>
+      <c r="M333" s="13">
+        <f>$Q$5*(B333/100*$Q$7*$Q$6)/($Q$6*$Q$8*A333)</f>
+        <v/>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -50979,6 +52339,10 @@
       <c r="C334" s="1" t="n">
         <v>0.075687</v>
       </c>
+      <c r="M334" s="13">
+        <f>$Q$5*(B334/100*$Q$7*$Q$6)/($Q$6*$Q$8*A334)</f>
+        <v/>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -50990,6 +52354,10 @@
       <c r="C335" s="1" t="n">
         <v>0.075603</v>
       </c>
+      <c r="M335" s="13">
+        <f>$Q$5*(B335/100*$Q$7*$Q$6)/($Q$6*$Q$8*A335)</f>
+        <v/>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -51001,6 +52369,10 @@
       <c r="C336" s="1" t="n">
         <v>0.07552300000000001</v>
       </c>
+      <c r="M336" s="13">
+        <f>$Q$5*(B336/100*$Q$7*$Q$6)/($Q$6*$Q$8*A336)</f>
+        <v/>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -51012,6 +52384,10 @@
       <c r="C337" s="1" t="n">
         <v>0.075442</v>
       </c>
+      <c r="M337" s="13">
+        <f>$Q$5*(B337/100*$Q$7*$Q$6)/($Q$6*$Q$8*A337)</f>
+        <v/>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -51023,6 +52399,10 @@
       <c r="C338" s="1" t="n">
         <v>0.075363</v>
       </c>
+      <c r="M338" s="13">
+        <f>$Q$5*(B338/100*$Q$7*$Q$6)/($Q$6*$Q$8*A338)</f>
+        <v/>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -51034,6 +52414,10 @@
       <c r="C339" s="1" t="n">
         <v>0.075285</v>
       </c>
+      <c r="M339" s="13">
+        <f>$Q$5*(B339/100*$Q$7*$Q$6)/($Q$6*$Q$8*A339)</f>
+        <v/>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -51045,6 +52429,10 @@
       <c r="C340" s="1" t="n">
         <v>0.075207</v>
       </c>
+      <c r="M340" s="13">
+        <f>$Q$5*(B340/100*$Q$7*$Q$6)/($Q$6*$Q$8*A340)</f>
+        <v/>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -51056,6 +52444,10 @@
       <c r="C341" s="1" t="n">
         <v>0.075126</v>
       </c>
+      <c r="M341" s="13">
+        <f>$Q$5*(B341/100*$Q$7*$Q$6)/($Q$6*$Q$8*A341)</f>
+        <v/>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -51067,6 +52459,10 @@
       <c r="C342" s="1" t="n">
         <v>0.075049</v>
       </c>
+      <c r="M342" s="13">
+        <f>$Q$5*(B342/100*$Q$7*$Q$6)/($Q$6*$Q$8*A342)</f>
+        <v/>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -51078,6 +52474,10 @@
       <c r="C343" s="1" t="n">
         <v>0.074972</v>
       </c>
+      <c r="M343" s="13">
+        <f>$Q$5*(B343/100*$Q$7*$Q$6)/($Q$6*$Q$8*A343)</f>
+        <v/>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -51089,6 +52489,10 @@
       <c r="C344" s="1" t="n">
         <v>0.074894</v>
       </c>
+      <c r="M344" s="13">
+        <f>$Q$5*(B344/100*$Q$7*$Q$6)/($Q$6*$Q$8*A344)</f>
+        <v/>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -51100,6 +52504,10 @@
       <c r="C345" s="1" t="n">
         <v>0.074821</v>
       </c>
+      <c r="M345" s="13">
+        <f>$Q$5*(B345/100*$Q$7*$Q$6)/($Q$6*$Q$8*A345)</f>
+        <v/>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -51111,6 +52519,10 @@
       <c r="C346" s="1" t="n">
         <v>0.074744</v>
       </c>
+      <c r="M346" s="13">
+        <f>$Q$5*(B346/100*$Q$7*$Q$6)/($Q$6*$Q$8*A346)</f>
+        <v/>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -51122,6 +52534,10 @@
       <c r="C347" s="1" t="n">
         <v>0.074668</v>
       </c>
+      <c r="M347" s="13">
+        <f>$Q$5*(B347/100*$Q$7*$Q$6)/($Q$6*$Q$8*A347)</f>
+        <v/>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -51133,6 +52549,10 @@
       <c r="C348" s="1" t="n">
         <v>0.07459200000000001</v>
       </c>
+      <c r="M348" s="13">
+        <f>$Q$5*(B348/100*$Q$7*$Q$6)/($Q$6*$Q$8*A348)</f>
+        <v/>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -51144,6 +52564,10 @@
       <c r="C349" s="1" t="n">
         <v>0.074516</v>
       </c>
+      <c r="M349" s="13">
+        <f>$Q$5*(B349/100*$Q$7*$Q$6)/($Q$6*$Q$8*A349)</f>
+        <v/>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -51155,6 +52579,10 @@
       <c r="C350" s="1" t="n">
         <v>0.07443900000000001</v>
       </c>
+      <c r="M350" s="13">
+        <f>$Q$5*(B350/100*$Q$7*$Q$6)/($Q$6*$Q$8*A350)</f>
+        <v/>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -51166,6 +52594,10 @@
       <c r="C351" s="1" t="n">
         <v>0.074365</v>
       </c>
+      <c r="M351" s="13">
+        <f>$Q$5*(B351/100*$Q$7*$Q$6)/($Q$6*$Q$8*A351)</f>
+        <v/>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -51177,6 +52609,10 @@
       <c r="C352" s="1" t="n">
         <v>0.07428999999999999</v>
       </c>
+      <c r="M352" s="13">
+        <f>$Q$5*(B352/100*$Q$7*$Q$6)/($Q$6*$Q$8*A352)</f>
+        <v/>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -51188,6 +52624,10 @@
       <c r="C353" s="1" t="n">
         <v>0.074212</v>
       </c>
+      <c r="M353" s="13">
+        <f>$Q$5*(B353/100*$Q$7*$Q$6)/($Q$6*$Q$8*A353)</f>
+        <v/>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -51199,6 +52639,10 @@
       <c r="C354" s="1" t="n">
         <v>0.07413699999999999</v>
       </c>
+      <c r="M354" s="13">
+        <f>$Q$5*(B354/100*$Q$7*$Q$6)/($Q$6*$Q$8*A354)</f>
+        <v/>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -51210,6 +52654,10 @@
       <c r="C355" s="1" t="n">
         <v>0.074064</v>
       </c>
+      <c r="M355" s="13">
+        <f>$Q$5*(B355/100*$Q$7*$Q$6)/($Q$6*$Q$8*A355)</f>
+        <v/>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -51221,6 +52669,10 @@
       <c r="C356" s="1" t="n">
         <v>0.073991</v>
       </c>
+      <c r="M356" s="13">
+        <f>$Q$5*(B356/100*$Q$7*$Q$6)/($Q$6*$Q$8*A356)</f>
+        <v/>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -51232,6 +52684,10 @@
       <c r="C357" s="1" t="n">
         <v>0.073919</v>
       </c>
+      <c r="M357" s="13">
+        <f>$Q$5*(B357/100*$Q$7*$Q$6)/($Q$6*$Q$8*A357)</f>
+        <v/>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -51243,6 +52699,10 @@
       <c r="C358" s="1" t="n">
         <v>0.07384599999999999</v>
       </c>
+      <c r="M358" s="13">
+        <f>$Q$5*(B358/100*$Q$7*$Q$6)/($Q$6*$Q$8*A358)</f>
+        <v/>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -51254,6 +52714,10 @@
       <c r="C359" s="1" t="n">
         <v>0.07377499999999999</v>
       </c>
+      <c r="M359" s="13">
+        <f>$Q$5*(B359/100*$Q$7*$Q$6)/($Q$6*$Q$8*A359)</f>
+        <v/>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -51265,6 +52729,10 @@
       <c r="C360" s="1" t="n">
         <v>0.07370400000000001</v>
       </c>
+      <c r="M360" s="13">
+        <f>$Q$5*(B360/100*$Q$7*$Q$6)/($Q$6*$Q$8*A360)</f>
+        <v/>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -51276,6 +52744,10 @@
       <c r="C361" s="1" t="n">
         <v>0.073633</v>
       </c>
+      <c r="M361" s="13">
+        <f>$Q$5*(B361/100*$Q$7*$Q$6)/($Q$6*$Q$8*A361)</f>
+        <v/>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -51287,6 +52759,10 @@
       <c r="C362" s="1" t="n">
         <v>0.073562</v>
       </c>
+      <c r="M362" s="13">
+        <f>$Q$5*(B362/100*$Q$7*$Q$6)/($Q$6*$Q$8*A362)</f>
+        <v/>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -51298,6 +52774,10 @@
       <c r="C363" s="1" t="n">
         <v>0.073493</v>
       </c>
+      <c r="M363" s="13">
+        <f>$Q$5*(B363/100*$Q$7*$Q$6)/($Q$6*$Q$8*A363)</f>
+        <v/>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -51309,6 +52789,10 @@
       <c r="C364" s="1" t="n">
         <v>0.073422</v>
       </c>
+      <c r="M364" s="13">
+        <f>$Q$5*(B364/100*$Q$7*$Q$6)/($Q$6*$Q$8*A364)</f>
+        <v/>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -51320,6 +52804,10 @@
       <c r="C365" s="1" t="n">
         <v>0.073352</v>
       </c>
+      <c r="M365" s="13">
+        <f>$Q$5*(B365/100*$Q$7*$Q$6)/($Q$6*$Q$8*A365)</f>
+        <v/>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -51331,6 +52819,10 @@
       <c r="C366" s="1" t="n">
         <v>0.073284</v>
       </c>
+      <c r="M366" s="13">
+        <f>$Q$5*(B366/100*$Q$7*$Q$6)/($Q$6*$Q$8*A366)</f>
+        <v/>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -51342,6 +52834,10 @@
       <c r="C367" s="1" t="n">
         <v>0.073214</v>
       </c>
+      <c r="M367" s="13">
+        <f>$Q$5*(B367/100*$Q$7*$Q$6)/($Q$6*$Q$8*A367)</f>
+        <v/>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -51353,6 +52849,10 @@
       <c r="C368" s="1" t="n">
         <v>0.073147</v>
       </c>
+      <c r="M368" s="13">
+        <f>$Q$5*(B368/100*$Q$7*$Q$6)/($Q$6*$Q$8*A368)</f>
+        <v/>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -51364,6 +52864,10 @@
       <c r="C369" s="1" t="n">
         <v>0.073077</v>
       </c>
+      <c r="M369" s="13">
+        <f>$Q$5*(B369/100*$Q$7*$Q$6)/($Q$6*$Q$8*A369)</f>
+        <v/>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -51375,6 +52879,10 @@
       <c r="C370" s="1" t="n">
         <v>0.073009</v>
       </c>
+      <c r="M370" s="13">
+        <f>$Q$5*(B370/100*$Q$7*$Q$6)/($Q$6*$Q$8*A370)</f>
+        <v/>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -51386,6 +52894,10 @@
       <c r="C371" s="1" t="n">
         <v>0.07294200000000001</v>
       </c>
+      <c r="M371" s="13">
+        <f>$Q$5*(B371/100*$Q$7*$Q$6)/($Q$6*$Q$8*A371)</f>
+        <v/>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -51397,6 +52909,10 @@
       <c r="C372" s="1" t="n">
         <v>0.07287399999999999</v>
       </c>
+      <c r="M372" s="13">
+        <f>$Q$5*(B372/100*$Q$7*$Q$6)/($Q$6*$Q$8*A372)</f>
+        <v/>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -51408,6 +52924,10 @@
       <c r="C373" s="1" t="n">
         <v>0.072808</v>
       </c>
+      <c r="M373" s="13">
+        <f>$Q$5*(B373/100*$Q$7*$Q$6)/($Q$6*$Q$8*A373)</f>
+        <v/>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -51419,6 +52939,10 @@
       <c r="C374" s="1" t="n">
         <v>0.072738</v>
       </c>
+      <c r="M374" s="13">
+        <f>$Q$5*(B374/100*$Q$7*$Q$6)/($Q$6*$Q$8*A374)</f>
+        <v/>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -51430,6 +52954,10 @@
       <c r="C375" s="1" t="n">
         <v>0.072674</v>
       </c>
+      <c r="M375" s="13">
+        <f>$Q$5*(B375/100*$Q$7*$Q$6)/($Q$6*$Q$8*A375)</f>
+        <v/>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -51441,6 +52969,10 @@
       <c r="C376" s="1" t="n">
         <v>0.07260800000000001</v>
       </c>
+      <c r="M376" s="13">
+        <f>$Q$5*(B376/100*$Q$7*$Q$6)/($Q$6*$Q$8*A376)</f>
+        <v/>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -51452,6 +52984,10 @@
       <c r="C377" s="1" t="n">
         <v>0.072544</v>
       </c>
+      <c r="M377" s="13">
+        <f>$Q$5*(B377/100*$Q$7*$Q$6)/($Q$6*$Q$8*A377)</f>
+        <v/>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -51463,6 +52999,10 @@
       <c r="C378" s="1" t="n">
         <v>0.07248</v>
       </c>
+      <c r="M378" s="13">
+        <f>$Q$5*(B378/100*$Q$7*$Q$6)/($Q$6*$Q$8*A378)</f>
+        <v/>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -51474,6 +53014,10 @@
       <c r="C379" s="1" t="n">
         <v>0.07241599999999999</v>
       </c>
+      <c r="M379" s="13">
+        <f>$Q$5*(B379/100*$Q$7*$Q$6)/($Q$6*$Q$8*A379)</f>
+        <v/>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -51485,6 +53029,10 @@
       <c r="C380" s="1" t="n">
         <v>0.072352</v>
       </c>
+      <c r="M380" s="13">
+        <f>$Q$5*(B380/100*$Q$7*$Q$6)/($Q$6*$Q$8*A380)</f>
+        <v/>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -51496,6 +53044,10 @@
       <c r="C381" s="1" t="n">
         <v>0.07228900000000001</v>
       </c>
+      <c r="M381" s="13">
+        <f>$Q$5*(B381/100*$Q$7*$Q$6)/($Q$6*$Q$8*A381)</f>
+        <v/>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -51507,6 +53059,10 @@
       <c r="C382" s="1" t="n">
         <v>0.072228</v>
       </c>
+      <c r="M382" s="13">
+        <f>$Q$5*(B382/100*$Q$7*$Q$6)/($Q$6*$Q$8*A382)</f>
+        <v/>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -51518,6 +53074,10 @@
       <c r="C383" s="1" t="n">
         <v>0.072167</v>
       </c>
+      <c r="M383" s="13">
+        <f>$Q$5*(B383/100*$Q$7*$Q$6)/($Q$6*$Q$8*A383)</f>
+        <v/>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -51529,6 +53089,10 @@
       <c r="C384" s="1" t="n">
         <v>0.072104</v>
       </c>
+      <c r="M384" s="13">
+        <f>$Q$5*(B384/100*$Q$7*$Q$6)/($Q$6*$Q$8*A384)</f>
+        <v/>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -51540,6 +53104,10 @@
       <c r="C385" s="1" t="n">
         <v>0.072043</v>
       </c>
+      <c r="M385" s="13">
+        <f>$Q$5*(B385/100*$Q$7*$Q$6)/($Q$6*$Q$8*A385)</f>
+        <v/>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -51551,6 +53119,10 @@
       <c r="C386" s="1" t="n">
         <v>0.071982</v>
       </c>
+      <c r="M386" s="13">
+        <f>$Q$5*(B386/100*$Q$7*$Q$6)/($Q$6*$Q$8*A386)</f>
+        <v/>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -51562,6 +53134,10 @@
       <c r="C387" s="1" t="n">
         <v>0.07192</v>
       </c>
+      <c r="M387" s="13">
+        <f>$Q$5*(B387/100*$Q$7*$Q$6)/($Q$6*$Q$8*A387)</f>
+        <v/>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -51573,6 +53149,10 @@
       <c r="C388" s="1" t="n">
         <v>0.07185800000000001</v>
       </c>
+      <c r="M388" s="13">
+        <f>$Q$5*(B388/100*$Q$7*$Q$6)/($Q$6*$Q$8*A388)</f>
+        <v/>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -51584,6 +53164,10 @@
       <c r="C389" s="1" t="n">
         <v>0.071797</v>
       </c>
+      <c r="M389" s="13">
+        <f>$Q$5*(B389/100*$Q$7*$Q$6)/($Q$6*$Q$8*A389)</f>
+        <v/>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -51595,6 +53179,10 @@
       <c r="C390" s="1" t="n">
         <v>0.071737</v>
       </c>
+      <c r="M390" s="13">
+        <f>$Q$5*(B390/100*$Q$7*$Q$6)/($Q$6*$Q$8*A390)</f>
+        <v/>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -51606,6 +53194,10 @@
       <c r="C391" s="1" t="n">
         <v>0.071676</v>
       </c>
+      <c r="M391" s="13">
+        <f>$Q$5*(B391/100*$Q$7*$Q$6)/($Q$6*$Q$8*A391)</f>
+        <v/>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -51617,6 +53209,10 @@
       <c r="C392" s="1" t="n">
         <v>0.071616</v>
       </c>
+      <c r="M392" s="13">
+        <f>$Q$5*(B392/100*$Q$7*$Q$6)/($Q$6*$Q$8*A392)</f>
+        <v/>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -51628,6 +53224,10 @@
       <c r="C393" s="1" t="n">
         <v>0.07155400000000001</v>
       </c>
+      <c r="M393" s="13">
+        <f>$Q$5*(B393/100*$Q$7*$Q$6)/($Q$6*$Q$8*A393)</f>
+        <v/>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -51639,6 +53239,10 @@
       <c r="C394" s="1" t="n">
         <v>0.071493</v>
       </c>
+      <c r="M394" s="13">
+        <f>$Q$5*(B394/100*$Q$7*$Q$6)/($Q$6*$Q$8*A394)</f>
+        <v/>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -51650,6 +53254,10 @@
       <c r="C395" s="1" t="n">
         <v>0.071433</v>
       </c>
+      <c r="M395" s="13">
+        <f>$Q$5*(B395/100*$Q$7*$Q$6)/($Q$6*$Q$8*A395)</f>
+        <v/>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -51661,6 +53269,10 @@
       <c r="C396" s="1" t="n">
         <v>0.071371</v>
       </c>
+      <c r="M396" s="13">
+        <f>$Q$5*(B396/100*$Q$7*$Q$6)/($Q$6*$Q$8*A396)</f>
+        <v/>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -51672,6 +53284,10 @@
       <c r="C397" s="1" t="n">
         <v>0.071311</v>
       </c>
+      <c r="M397" s="13">
+        <f>$Q$5*(B397/100*$Q$7*$Q$6)/($Q$6*$Q$8*A397)</f>
+        <v/>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -51683,6 +53299,10 @@
       <c r="C398" s="1" t="n">
         <v>0.07125099999999999</v>
       </c>
+      <c r="M398" s="13">
+        <f>$Q$5*(B398/100*$Q$7*$Q$6)/($Q$6*$Q$8*A398)</f>
+        <v/>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -51694,6 +53314,10 @@
       <c r="C399" s="1" t="n">
         <v>0.07119300000000001</v>
       </c>
+      <c r="M399" s="13">
+        <f>$Q$5*(B399/100*$Q$7*$Q$6)/($Q$6*$Q$8*A399)</f>
+        <v/>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -51705,6 +53329,10 @@
       <c r="C400" s="1" t="n">
         <v>0.071134</v>
       </c>
+      <c r="M400" s="13">
+        <f>$Q$5*(B400/100*$Q$7*$Q$6)/($Q$6*$Q$8*A400)</f>
+        <v/>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -51716,6 +53344,10 @@
       <c r="C401" s="1" t="n">
         <v>0.071074</v>
       </c>
+      <c r="M401" s="13">
+        <f>$Q$5*(B401/100*$Q$7*$Q$6)/($Q$6*$Q$8*A401)</f>
+        <v/>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -51727,6 +53359,10 @@
       <c r="C402" s="1" t="n">
         <v>0.071018</v>
       </c>
+      <c r="M402" s="13">
+        <f>$Q$5*(B402/100*$Q$7*$Q$6)/($Q$6*$Q$8*A402)</f>
+        <v/>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -51738,6 +53374,10 @@
       <c r="C403" s="1" t="n">
         <v>0.07095899999999999</v>
       </c>
+      <c r="M403" s="13">
+        <f>$Q$5*(B403/100*$Q$7*$Q$6)/($Q$6*$Q$8*A403)</f>
+        <v/>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -51749,6 +53389,10 @@
       <c r="C404" s="1" t="n">
         <v>0.070899</v>
       </c>
+      <c r="M404" s="13">
+        <f>$Q$5*(B404/100*$Q$7*$Q$6)/($Q$6*$Q$8*A404)</f>
+        <v/>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -51760,6 +53404,10 @@
       <c r="C405" s="1" t="n">
         <v>0.070842</v>
       </c>
+      <c r="M405" s="13">
+        <f>$Q$5*(B405/100*$Q$7*$Q$6)/($Q$6*$Q$8*A405)</f>
+        <v/>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -51771,6 +53419,10 @@
       <c r="C406" s="1" t="n">
         <v>0.070782</v>
       </c>
+      <c r="M406" s="13">
+        <f>$Q$5*(B406/100*$Q$7*$Q$6)/($Q$6*$Q$8*A406)</f>
+        <v/>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -51782,6 +53434,10 @@
       <c r="C407" s="1" t="n">
         <v>0.070725</v>
       </c>
+      <c r="M407" s="13">
+        <f>$Q$5*(B407/100*$Q$7*$Q$6)/($Q$6*$Q$8*A407)</f>
+        <v/>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -51793,6 +53449,10 @@
       <c r="C408" s="1" t="n">
         <v>0.07066600000000001</v>
       </c>
+      <c r="M408" s="13">
+        <f>$Q$5*(B408/100*$Q$7*$Q$6)/($Q$6*$Q$8*A408)</f>
+        <v/>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -51804,6 +53464,10 @@
       <c r="C409" s="1" t="n">
         <v>0.070608</v>
       </c>
+      <c r="M409" s="13">
+        <f>$Q$5*(B409/100*$Q$7*$Q$6)/($Q$6*$Q$8*A409)</f>
+        <v/>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -51815,6 +53479,10 @@
       <c r="C410" s="1" t="n">
         <v>0.070549</v>
       </c>
+      <c r="M410" s="13">
+        <f>$Q$5*(B410/100*$Q$7*$Q$6)/($Q$6*$Q$8*A410)</f>
+        <v/>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -51826,6 +53494,10 @@
       <c r="C411" s="1" t="n">
         <v>0.070492</v>
       </c>
+      <c r="M411" s="13">
+        <f>$Q$5*(B411/100*$Q$7*$Q$6)/($Q$6*$Q$8*A411)</f>
+        <v/>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -51837,6 +53509,10 @@
       <c r="C412" s="1" t="n">
         <v>0.070434</v>
       </c>
+      <c r="M412" s="13">
+        <f>$Q$5*(B412/100*$Q$7*$Q$6)/($Q$6*$Q$8*A412)</f>
+        <v/>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -51848,6 +53524,10 @@
       <c r="C413" s="1" t="n">
         <v>0.070377</v>
       </c>
+      <c r="M413" s="13">
+        <f>$Q$5*(B413/100*$Q$7*$Q$6)/($Q$6*$Q$8*A413)</f>
+        <v/>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -51859,6 +53539,10 @@
       <c r="C414" s="1" t="n">
         <v>0.07031800000000001</v>
       </c>
+      <c r="M414" s="13">
+        <f>$Q$5*(B414/100*$Q$7*$Q$6)/($Q$6*$Q$8*A414)</f>
+        <v/>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -51870,6 +53554,10 @@
       <c r="C415" s="1" t="n">
         <v>0.070261</v>
       </c>
+      <c r="M415" s="13">
+        <f>$Q$5*(B415/100*$Q$7*$Q$6)/($Q$6*$Q$8*A415)</f>
+        <v/>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
@@ -51881,6 +53569,10 @@
       <c r="C416" s="1" t="n">
         <v>0.070204</v>
       </c>
+      <c r="M416" s="13">
+        <f>$Q$5*(B416/100*$Q$7*$Q$6)/($Q$6*$Q$8*A416)</f>
+        <v/>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
@@ -51892,6 +53584,10 @@
       <c r="C417" s="1" t="n">
         <v>0.070147</v>
       </c>
+      <c r="M417" s="13">
+        <f>$Q$5*(B417/100*$Q$7*$Q$6)/($Q$6*$Q$8*A417)</f>
+        <v/>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
@@ -51903,6 +53599,10 @@
       <c r="C418" s="1" t="n">
         <v>0.070091</v>
       </c>
+      <c r="M418" s="13">
+        <f>$Q$5*(B418/100*$Q$7*$Q$6)/($Q$6*$Q$8*A418)</f>
+        <v/>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
@@ -51914,6 +53614,10 @@
       <c r="C419" s="1" t="n">
         <v>0.070034</v>
       </c>
+      <c r="M419" s="13">
+        <f>$Q$5*(B419/100*$Q$7*$Q$6)/($Q$6*$Q$8*A419)</f>
+        <v/>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
@@ -51925,6 +53629,10 @@
       <c r="C420" s="1" t="n">
         <v>0.069977</v>
       </c>
+      <c r="M420" s="13">
+        <f>$Q$5*(B420/100*$Q$7*$Q$6)/($Q$6*$Q$8*A420)</f>
+        <v/>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
@@ -51936,6 +53644,10 @@
       <c r="C421" s="1" t="n">
         <v>0.069921</v>
       </c>
+      <c r="M421" s="13">
+        <f>$Q$5*(B421/100*$Q$7*$Q$6)/($Q$6*$Q$8*A421)</f>
+        <v/>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
@@ -51947,6 +53659,10 @@
       <c r="C422" s="1" t="n">
         <v>0.069865</v>
       </c>
+      <c r="M422" s="13">
+        <f>$Q$5*(B422/100*$Q$7*$Q$6)/($Q$6*$Q$8*A422)</f>
+        <v/>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
@@ -51958,6 +53674,10 @@
       <c r="C423" s="1" t="n">
         <v>0.06981</v>
       </c>
+      <c r="M423" s="13">
+        <f>$Q$5*(B423/100*$Q$7*$Q$6)/($Q$6*$Q$8*A423)</f>
+        <v/>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
@@ -51969,6 +53689,10 @@
       <c r="C424" s="1" t="n">
         <v>0.069754</v>
       </c>
+      <c r="M424" s="13">
+        <f>$Q$5*(B424/100*$Q$7*$Q$6)/($Q$6*$Q$8*A424)</f>
+        <v/>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
@@ -51980,6 +53704,10 @@
       <c r="C425" s="1" t="n">
         <v>0.069698</v>
       </c>
+      <c r="M425" s="13">
+        <f>$Q$5*(B425/100*$Q$7*$Q$6)/($Q$6*$Q$8*A425)</f>
+        <v/>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
@@ -51991,6 +53719,10 @@
       <c r="C426" s="1" t="n">
         <v>0.069642</v>
       </c>
+      <c r="M426" s="13">
+        <f>$Q$5*(B426/100*$Q$7*$Q$6)/($Q$6*$Q$8*A426)</f>
+        <v/>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
@@ -52002,6 +53734,10 @@
       <c r="C427" s="1" t="n">
         <v>0.069586</v>
       </c>
+      <c r="M427" s="13">
+        <f>$Q$5*(B427/100*$Q$7*$Q$6)/($Q$6*$Q$8*A427)</f>
+        <v/>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
@@ -52013,6 +53749,10 @@
       <c r="C428" s="1" t="n">
         <v>0.069532</v>
       </c>
+      <c r="M428" s="13">
+        <f>$Q$5*(B428/100*$Q$7*$Q$6)/($Q$6*$Q$8*A428)</f>
+        <v/>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
@@ -52024,6 +53764,10 @@
       <c r="C429" s="1" t="n">
         <v>0.069478</v>
       </c>
+      <c r="M429" s="13">
+        <f>$Q$5*(B429/100*$Q$7*$Q$6)/($Q$6*$Q$8*A429)</f>
+        <v/>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
@@ -52035,6 +53779,10 @@
       <c r="C430" s="1" t="n">
         <v>0.069422</v>
       </c>
+      <c r="M430" s="13">
+        <f>$Q$5*(B430/100*$Q$7*$Q$6)/($Q$6*$Q$8*A430)</f>
+        <v/>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
@@ -52046,6 +53794,10 @@
       <c r="C431" s="1" t="n">
         <v>0.069368</v>
       </c>
+      <c r="M431" s="13">
+        <f>$Q$5*(B431/100*$Q$7*$Q$6)/($Q$6*$Q$8*A431)</f>
+        <v/>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
@@ -52057,6 +53809,10 @@
       <c r="C432" s="1" t="n">
         <v>0.069313</v>
       </c>
+      <c r="M432" s="13">
+        <f>$Q$5*(B432/100*$Q$7*$Q$6)/($Q$6*$Q$8*A432)</f>
+        <v/>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
@@ -52068,6 +53824,10 @@
       <c r="C433" s="1" t="n">
         <v>0.069258</v>
       </c>
+      <c r="M433" s="13">
+        <f>$Q$5*(B433/100*$Q$7*$Q$6)/($Q$6*$Q$8*A433)</f>
+        <v/>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
@@ -52079,6 +53839,10 @@
       <c r="C434" s="1" t="n">
         <v>0.069204</v>
       </c>
+      <c r="M434" s="13">
+        <f>$Q$5*(B434/100*$Q$7*$Q$6)/($Q$6*$Q$8*A434)</f>
+        <v/>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
@@ -52090,6 +53854,10 @@
       <c r="C435" s="1" t="n">
         <v>0.069151</v>
       </c>
+      <c r="M435" s="13">
+        <f>$Q$5*(B435/100*$Q$7*$Q$6)/($Q$6*$Q$8*A435)</f>
+        <v/>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
@@ -52101,6 +53869,10 @@
       <c r="C436" s="1" t="n">
         <v>0.06909899999999999</v>
       </c>
+      <c r="M436" s="13">
+        <f>$Q$5*(B436/100*$Q$7*$Q$6)/($Q$6*$Q$8*A436)</f>
+        <v/>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
@@ -52112,6 +53884,10 @@
       <c r="C437" s="1" t="n">
         <v>0.069045</v>
       </c>
+      <c r="M437" s="13">
+        <f>$Q$5*(B437/100*$Q$7*$Q$6)/($Q$6*$Q$8*A437)</f>
+        <v/>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
@@ -52123,6 +53899,10 @@
       <c r="C438" s="1" t="n">
         <v>0.068992</v>
       </c>
+      <c r="M438" s="13">
+        <f>$Q$5*(B438/100*$Q$7*$Q$6)/($Q$6*$Q$8*A438)</f>
+        <v/>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
@@ -52134,6 +53914,10 @@
       <c r="C439" s="1" t="n">
         <v>0.068939</v>
       </c>
+      <c r="M439" s="13">
+        <f>$Q$5*(B439/100*$Q$7*$Q$6)/($Q$6*$Q$8*A439)</f>
+        <v/>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
@@ -52145,6 +53929,10 @@
       <c r="C440" s="1" t="n">
         <v>0.068886</v>
       </c>
+      <c r="M440" s="13">
+        <f>$Q$5*(B440/100*$Q$7*$Q$6)/($Q$6*$Q$8*A440)</f>
+        <v/>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
@@ -52156,6 +53944,10 @@
       <c r="C441" s="1" t="n">
         <v>0.06883400000000001</v>
       </c>
+      <c r="M441" s="13">
+        <f>$Q$5*(B441/100*$Q$7*$Q$6)/($Q$6*$Q$8*A441)</f>
+        <v/>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
@@ -52167,6 +53959,10 @@
       <c r="C442" s="1" t="n">
         <v>0.068782</v>
       </c>
+      <c r="M442" s="13">
+        <f>$Q$5*(B442/100*$Q$7*$Q$6)/($Q$6*$Q$8*A442)</f>
+        <v/>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
@@ -52178,6 +53974,10 @@
       <c r="C443" s="1" t="n">
         <v>0.068728</v>
       </c>
+      <c r="M443" s="13">
+        <f>$Q$5*(B443/100*$Q$7*$Q$6)/($Q$6*$Q$8*A443)</f>
+        <v/>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
@@ -52189,6 +53989,10 @@
       <c r="C444" s="1" t="n">
         <v>0.068675</v>
       </c>
+      <c r="M444" s="13">
+        <f>$Q$5*(B444/100*$Q$7*$Q$6)/($Q$6*$Q$8*A444)</f>
+        <v/>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
@@ -52200,6 +54004,10 @@
       <c r="C445" s="1" t="n">
         <v>0.068622</v>
       </c>
+      <c r="M445" s="13">
+        <f>$Q$5*(B445/100*$Q$7*$Q$6)/($Q$6*$Q$8*A445)</f>
+        <v/>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
@@ -52211,6 +54019,10 @@
       <c r="C446" s="1" t="n">
         <v>0.06857000000000001</v>
       </c>
+      <c r="M446" s="13">
+        <f>$Q$5*(B446/100*$Q$7*$Q$6)/($Q$6*$Q$8*A446)</f>
+        <v/>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
@@ -52222,6 +54034,10 @@
       <c r="C447" s="1" t="n">
         <v>0.06851599999999999</v>
       </c>
+      <c r="M447" s="13">
+        <f>$Q$5*(B447/100*$Q$7*$Q$6)/($Q$6*$Q$8*A447)</f>
+        <v/>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
@@ -52233,6 +54049,10 @@
       <c r="C448" s="1" t="n">
         <v>0.068464</v>
       </c>
+      <c r="M448" s="13">
+        <f>$Q$5*(B448/100*$Q$7*$Q$6)/($Q$6*$Q$8*A448)</f>
+        <v/>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
@@ -52244,6 +54064,10 @@
       <c r="C449" s="1" t="n">
         <v>0.06841</v>
       </c>
+      <c r="M449" s="13">
+        <f>$Q$5*(B449/100*$Q$7*$Q$6)/($Q$6*$Q$8*A449)</f>
+        <v/>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
@@ -52255,6 +54079,10 @@
       <c r="C450" s="1" t="n">
         <v>0.068358</v>
       </c>
+      <c r="M450" s="13">
+        <f>$Q$5*(B450/100*$Q$7*$Q$6)/($Q$6*$Q$8*A450)</f>
+        <v/>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
@@ -52266,6 +54094,10 @@
       <c r="C451" s="1" t="n">
         <v>0.06830700000000001</v>
       </c>
+      <c r="M451" s="13">
+        <f>$Q$5*(B451/100*$Q$7*$Q$6)/($Q$6*$Q$8*A451)</f>
+        <v/>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
@@ -52277,6 +54109,10 @@
       <c r="C452" s="1" t="n">
         <v>0.068256</v>
       </c>
+      <c r="M452" s="13">
+        <f>$Q$5*(B452/100*$Q$7*$Q$6)/($Q$6*$Q$8*A452)</f>
+        <v/>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
@@ -52288,6 +54124,10 @@
       <c r="C453" s="1" t="n">
         <v>0.068202</v>
       </c>
+      <c r="M453" s="13">
+        <f>$Q$5*(B453/100*$Q$7*$Q$6)/($Q$6*$Q$8*A453)</f>
+        <v/>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
@@ -52299,6 +54139,10 @@
       <c r="C454" s="1" t="n">
         <v>0.068151</v>
       </c>
+      <c r="M454" s="13">
+        <f>$Q$5*(B454/100*$Q$7*$Q$6)/($Q$6*$Q$8*A454)</f>
+        <v/>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
@@ -52310,6 +54154,10 @@
       <c r="C455" s="1" t="n">
         <v>0.06809900000000001</v>
       </c>
+      <c r="M455" s="13">
+        <f>$Q$5*(B455/100*$Q$7*$Q$6)/($Q$6*$Q$8*A455)</f>
+        <v/>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
@@ -52321,6 +54169,10 @@
       <c r="C456" s="1" t="n">
         <v>0.068047</v>
       </c>
+      <c r="M456" s="13">
+        <f>$Q$5*(B456/100*$Q$7*$Q$6)/($Q$6*$Q$8*A456)</f>
+        <v/>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
@@ -52332,6 +54184,10 @@
       <c r="C457" s="1" t="n">
         <v>0.067996</v>
       </c>
+      <c r="M457" s="13">
+        <f>$Q$5*(B457/100*$Q$7*$Q$6)/($Q$6*$Q$8*A457)</f>
+        <v/>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
@@ -52343,6 +54199,10 @@
       <c r="C458" s="1" t="n">
         <v>0.06794500000000001</v>
       </c>
+      <c r="M458" s="13">
+        <f>$Q$5*(B458/100*$Q$7*$Q$6)/($Q$6*$Q$8*A458)</f>
+        <v/>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
@@ -52354,6 +54214,10 @@
       <c r="C459" s="1" t="n">
         <v>0.06789199999999999</v>
       </c>
+      <c r="M459" s="13">
+        <f>$Q$5*(B459/100*$Q$7*$Q$6)/($Q$6*$Q$8*A459)</f>
+        <v/>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
@@ -52365,6 +54229,10 @@
       <c r="C460" s="1" t="n">
         <v>0.067842</v>
       </c>
+      <c r="M460" s="13">
+        <f>$Q$5*(B460/100*$Q$7*$Q$6)/($Q$6*$Q$8*A460)</f>
+        <v/>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
@@ -52376,6 +54244,10 @@
       <c r="C461" s="1" t="n">
         <v>0.067791</v>
       </c>
+      <c r="M461" s="13">
+        <f>$Q$5*(B461/100*$Q$7*$Q$6)/($Q$6*$Q$8*A461)</f>
+        <v/>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
@@ -52387,6 +54259,10 @@
       <c r="C462" s="1" t="n">
         <v>0.06773899999999999</v>
       </c>
+      <c r="M462" s="13">
+        <f>$Q$5*(B462/100*$Q$7*$Q$6)/($Q$6*$Q$8*A462)</f>
+        <v/>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
@@ -52398,6 +54274,10 @@
       <c r="C463" s="1" t="n">
         <v>0.067688</v>
       </c>
+      <c r="M463" s="13">
+        <f>$Q$5*(B463/100*$Q$7*$Q$6)/($Q$6*$Q$8*A463)</f>
+        <v/>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
@@ -52409,6 +54289,10 @@
       <c r="C464" s="1" t="n">
         <v>0.067637</v>
       </c>
+      <c r="M464" s="13">
+        <f>$Q$5*(B464/100*$Q$7*$Q$6)/($Q$6*$Q$8*A464)</f>
+        <v/>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
@@ -52420,6 +54304,10 @@
       <c r="C465" s="1" t="n">
         <v>0.067589</v>
       </c>
+      <c r="M465" s="13">
+        <f>$Q$5*(B465/100*$Q$7*$Q$6)/($Q$6*$Q$8*A465)</f>
+        <v/>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
@@ -52431,6 +54319,10 @@
       <c r="C466" s="1" t="n">
         <v>0.067538</v>
       </c>
+      <c r="M466" s="13">
+        <f>$Q$5*(B466/100*$Q$7*$Q$6)/($Q$6*$Q$8*A466)</f>
+        <v/>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
@@ -52442,6 +54334,10 @@
       <c r="C467" s="1" t="n">
         <v>0.06748800000000001</v>
       </c>
+      <c r="M467" s="13">
+        <f>$Q$5*(B467/100*$Q$7*$Q$6)/($Q$6*$Q$8*A467)</f>
+        <v/>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
@@ -52453,6 +54349,10 @@
       <c r="C468" s="1" t="n">
         <v>0.067437</v>
       </c>
+      <c r="M468" s="13">
+        <f>$Q$5*(B468/100*$Q$7*$Q$6)/($Q$6*$Q$8*A468)</f>
+        <v/>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
@@ -52464,6 +54364,10 @@
       <c r="C469" s="1" t="n">
         <v>0.067387</v>
       </c>
+      <c r="M469" s="13">
+        <f>$Q$5*(B469/100*$Q$7*$Q$6)/($Q$6*$Q$8*A469)</f>
+        <v/>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
@@ -52475,6 +54379,10 @@
       <c r="C470" s="1" t="n">
         <v>0.06733599999999999</v>
       </c>
+      <c r="M470" s="13">
+        <f>$Q$5*(B470/100*$Q$7*$Q$6)/($Q$6*$Q$8*A470)</f>
+        <v/>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
@@ -52486,6 +54394,10 @@
       <c r="C471" s="1" t="n">
         <v>0.067287</v>
       </c>
+      <c r="M471" s="13">
+        <f>$Q$5*(B471/100*$Q$7*$Q$6)/($Q$6*$Q$8*A471)</f>
+        <v/>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
@@ -52497,6 +54409,10 @@
       <c r="C472" s="1" t="n">
         <v>0.06723700000000001</v>
       </c>
+      <c r="M472" s="13">
+        <f>$Q$5*(B472/100*$Q$7*$Q$6)/($Q$6*$Q$8*A472)</f>
+        <v/>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
@@ -52508,6 +54424,10 @@
       <c r="C473" s="1" t="n">
         <v>0.067186</v>
       </c>
+      <c r="M473" s="13">
+        <f>$Q$5*(B473/100*$Q$7*$Q$6)/($Q$6*$Q$8*A473)</f>
+        <v/>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
@@ -52519,6 +54439,10 @@
       <c r="C474" s="1" t="n">
         <v>0.067139</v>
       </c>
+      <c r="M474" s="13">
+        <f>$Q$5*(B474/100*$Q$7*$Q$6)/($Q$6*$Q$8*A474)</f>
+        <v/>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
@@ -52530,6 +54454,10 @@
       <c r="C475" s="1" t="n">
         <v>0.06708799999999999</v>
       </c>
+      <c r="M475" s="13">
+        <f>$Q$5*(B475/100*$Q$7*$Q$6)/($Q$6*$Q$8*A475)</f>
+        <v/>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
@@ -52541,6 +54469,10 @@
       <c r="C476" s="1" t="n">
         <v>0.067039</v>
       </c>
+      <c r="M476" s="13">
+        <f>$Q$5*(B476/100*$Q$7*$Q$6)/($Q$6*$Q$8*A476)</f>
+        <v/>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
@@ -52552,6 +54484,10 @@
       <c r="C477" s="1" t="n">
         <v>0.06698999999999999</v>
       </c>
+      <c r="M477" s="13">
+        <f>$Q$5*(B477/100*$Q$7*$Q$6)/($Q$6*$Q$8*A477)</f>
+        <v/>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
@@ -52563,6 +54499,10 @@
       <c r="C478" s="1" t="n">
         <v>0.066942</v>
       </c>
+      <c r="M478" s="13">
+        <f>$Q$5*(B478/100*$Q$7*$Q$6)/($Q$6*$Q$8*A478)</f>
+        <v/>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
@@ -52574,6 +54514,10 @@
       <c r="C479" s="1" t="n">
         <v>0.066895</v>
       </c>
+      <c r="M479" s="13">
+        <f>$Q$5*(B479/100*$Q$7*$Q$6)/($Q$6*$Q$8*A479)</f>
+        <v/>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
@@ -52585,6 +54529,10 @@
       <c r="C480" s="1" t="n">
         <v>0.066845</v>
       </c>
+      <c r="M480" s="13">
+        <f>$Q$5*(B480/100*$Q$7*$Q$6)/($Q$6*$Q$8*A480)</f>
+        <v/>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
@@ -52596,6 +54544,10 @@
       <c r="C481" s="1" t="n">
         <v>0.066797</v>
       </c>
+      <c r="M481" s="13">
+        <f>$Q$5*(B481/100*$Q$7*$Q$6)/($Q$6*$Q$8*A481)</f>
+        <v/>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
@@ -52607,6 +54559,10 @@
       <c r="C482" s="1" t="n">
         <v>0.066748</v>
       </c>
+      <c r="M482" s="13">
+        <f>$Q$5*(B482/100*$Q$7*$Q$6)/($Q$6*$Q$8*A482)</f>
+        <v/>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
@@ -52618,6 +54574,10 @@
       <c r="C483" s="1" t="n">
         <v>0.066701</v>
       </c>
+      <c r="M483" s="13">
+        <f>$Q$5*(B483/100*$Q$7*$Q$6)/($Q$6*$Q$8*A483)</f>
+        <v/>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
@@ -52629,6 +54589,10 @@
       <c r="C484" s="1" t="n">
         <v>0.066654</v>
       </c>
+      <c r="M484" s="13">
+        <f>$Q$5*(B484/100*$Q$7*$Q$6)/($Q$6*$Q$8*A484)</f>
+        <v/>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
@@ -52640,6 +54604,10 @@
       <c r="C485" s="1" t="n">
         <v>0.066606</v>
       </c>
+      <c r="M485" s="13">
+        <f>$Q$5*(B485/100*$Q$7*$Q$6)/($Q$6*$Q$8*A485)</f>
+        <v/>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
@@ -52651,6 +54619,10 @@
       <c r="C486" s="1" t="n">
         <v>0.06655800000000001</v>
       </c>
+      <c r="M486" s="13">
+        <f>$Q$5*(B486/100*$Q$7*$Q$6)/($Q$6*$Q$8*A486)</f>
+        <v/>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="n">
@@ -52662,6 +54634,10 @@
       <c r="C487" s="1" t="n">
         <v>0.066509</v>
       </c>
+      <c r="M487" s="13">
+        <f>$Q$5*(B487/100*$Q$7*$Q$6)/($Q$6*$Q$8*A487)</f>
+        <v/>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
@@ -52673,6 +54649,10 @@
       <c r="C488" s="1" t="n">
         <v>0.06646199999999999</v>
       </c>
+      <c r="M488" s="13">
+        <f>$Q$5*(B488/100*$Q$7*$Q$6)/($Q$6*$Q$8*A488)</f>
+        <v/>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
@@ -52684,6 +54664,10 @@
       <c r="C489" s="1" t="n">
         <v>0.066416</v>
       </c>
+      <c r="M489" s="13">
+        <f>$Q$5*(B489/100*$Q$7*$Q$6)/($Q$6*$Q$8*A489)</f>
+        <v/>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
@@ -52695,6 +54679,10 @@
       <c r="C490" s="1" t="n">
         <v>0.066367</v>
       </c>
+      <c r="M490" s="13">
+        <f>$Q$5*(B490/100*$Q$7*$Q$6)/($Q$6*$Q$8*A490)</f>
+        <v/>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="n">
@@ -52706,6 +54694,10 @@
       <c r="C491" s="1" t="n">
         <v>0.066319</v>
       </c>
+      <c r="M491" s="13">
+        <f>$Q$5*(B491/100*$Q$7*$Q$6)/($Q$6*$Q$8*A491)</f>
+        <v/>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
@@ -52717,6 +54709,10 @@
       <c r="C492" s="1" t="n">
         <v>0.066273</v>
       </c>
+      <c r="M492" s="13">
+        <f>$Q$5*(B492/100*$Q$7*$Q$6)/($Q$6*$Q$8*A492)</f>
+        <v/>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
@@ -52728,6 +54724,10 @@
       <c r="C493" s="1" t="n">
         <v>0.06622500000000001</v>
       </c>
+      <c r="M493" s="13">
+        <f>$Q$5*(B493/100*$Q$7*$Q$6)/($Q$6*$Q$8*A493)</f>
+        <v/>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
@@ -52739,6 +54739,10 @@
       <c r="C494" s="1" t="n">
         <v>0.066178</v>
       </c>
+      <c r="M494" s="13">
+        <f>$Q$5*(B494/100*$Q$7*$Q$6)/($Q$6*$Q$8*A494)</f>
+        <v/>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
@@ -52750,6 +54754,10 @@
       <c r="C495" s="1" t="n">
         <v>0.066131</v>
       </c>
+      <c r="M495" s="13">
+        <f>$Q$5*(B495/100*$Q$7*$Q$6)/($Q$6*$Q$8*A495)</f>
+        <v/>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
@@ -52761,6 +54769,10 @@
       <c r="C496" s="1" t="n">
         <v>0.066083</v>
       </c>
+      <c r="M496" s="13">
+        <f>$Q$5*(B496/100*$Q$7*$Q$6)/($Q$6*$Q$8*A496)</f>
+        <v/>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
@@ -52772,6 +54784,10 @@
       <c r="C497" s="1" t="n">
         <v>0.066035</v>
       </c>
+      <c r="M497" s="13">
+        <f>$Q$5*(B497/100*$Q$7*$Q$6)/($Q$6*$Q$8*A497)</f>
+        <v/>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
@@ -52783,6 +54799,10 @@
       <c r="C498" s="1" t="n">
         <v>0.06598900000000001</v>
       </c>
+      <c r="M498" s="13">
+        <f>$Q$5*(B498/100*$Q$7*$Q$6)/($Q$6*$Q$8*A498)</f>
+        <v/>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
@@ -52794,6 +54814,10 @@
       <c r="C499" s="1" t="n">
         <v>0.065943</v>
       </c>
+      <c r="M499" s="13">
+        <f>$Q$5*(B499/100*$Q$7*$Q$6)/($Q$6*$Q$8*A499)</f>
+        <v/>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="n">
@@ -52805,6 +54829,10 @@
       <c r="C500" s="1" t="n">
         <v>0.065895</v>
       </c>
+      <c r="M500" s="13">
+        <f>$Q$5*(B500/100*$Q$7*$Q$6)/($Q$6*$Q$8*A500)</f>
+        <v/>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="n">
@@ -52816,6 +54844,10 @@
       <c r="C501" s="1" t="n">
         <v>0.065849</v>
       </c>
+      <c r="M501" s="13">
+        <f>$Q$5*(B501/100*$Q$7*$Q$6)/($Q$6*$Q$8*A501)</f>
+        <v/>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="1" t="n">
@@ -52827,6 +54859,10 @@
       <c r="C502" s="1" t="n">
         <v>0.065801</v>
       </c>
+      <c r="M502" s="13">
+        <f>$Q$5*(B502/100*$Q$7*$Q$6)/($Q$6*$Q$8*A502)</f>
+        <v/>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="1" t="n">
@@ -52838,6 +54874,10 @@
       <c r="C503" s="1" t="n">
         <v>0.065756</v>
       </c>
+      <c r="M503" s="13">
+        <f>$Q$5*(B503/100*$Q$7*$Q$6)/($Q$6*$Q$8*A503)</f>
+        <v/>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="1" t="n">
@@ -52849,6 +54889,10 @@
       <c r="C504" s="1" t="n">
         <v>0.06571</v>
       </c>
+      <c r="M504" s="13">
+        <f>$Q$5*(B504/100*$Q$7*$Q$6)/($Q$6*$Q$8*A504)</f>
+        <v/>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="n">
@@ -52860,6 +54904,10 @@
       <c r="C505" s="1" t="n">
         <v>0.065665</v>
       </c>
+      <c r="M505" s="13">
+        <f>$Q$5*(B505/100*$Q$7*$Q$6)/($Q$6*$Q$8*A505)</f>
+        <v/>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="1" t="n">
@@ -52871,6 +54919,10 @@
       <c r="C506" s="1" t="n">
         <v>0.065618</v>
       </c>
+      <c r="M506" s="13">
+        <f>$Q$5*(B506/100*$Q$7*$Q$6)/($Q$6*$Q$8*A506)</f>
+        <v/>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="n">
@@ -52882,6 +54934,10 @@
       <c r="C507" s="1" t="n">
         <v>0.06557300000000001</v>
       </c>
+      <c r="M507" s="13">
+        <f>$Q$5*(B507/100*$Q$7*$Q$6)/($Q$6*$Q$8*A507)</f>
+        <v/>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="1" t="n">
@@ -52893,6 +54949,10 @@
       <c r="C508" s="1" t="n">
         <v>0.065527</v>
       </c>
+      <c r="M508" s="13">
+        <f>$Q$5*(B508/100*$Q$7*$Q$6)/($Q$6*$Q$8*A508)</f>
+        <v/>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="n">
@@ -52904,6 +54964,10 @@
       <c r="C509" s="1" t="n">
         <v>0.065482</v>
       </c>
+      <c r="M509" s="13">
+        <f>$Q$5*(B509/100*$Q$7*$Q$6)/($Q$6*$Q$8*A509)</f>
+        <v/>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="n">
@@ -52915,6 +54979,10 @@
       <c r="C510" s="1" t="n">
         <v>0.065439</v>
       </c>
+      <c r="M510" s="13">
+        <f>$Q$5*(B510/100*$Q$7*$Q$6)/($Q$6*$Q$8*A510)</f>
+        <v/>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="n">
@@ -52926,6 +54994,10 @@
       <c r="C511" s="1" t="n">
         <v>0.06539399999999999</v>
       </c>
+      <c r="M511" s="13">
+        <f>$Q$5*(B511/100*$Q$7*$Q$6)/($Q$6*$Q$8*A511)</f>
+        <v/>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="n">
@@ -52937,6 +55009,10 @@
       <c r="C512" s="1" t="n">
         <v>0.06535100000000001</v>
       </c>
+      <c r="M512" s="13">
+        <f>$Q$5*(B512/100*$Q$7*$Q$6)/($Q$6*$Q$8*A512)</f>
+        <v/>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="n">
@@ -52948,6 +55024,10 @@
       <c r="C513" s="1" t="n">
         <v>0.065306</v>
       </c>
+      <c r="M513" s="13">
+        <f>$Q$5*(B513/100*$Q$7*$Q$6)/($Q$6*$Q$8*A513)</f>
+        <v/>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="1" t="n">
@@ -52959,6 +55039,10 @@
       <c r="C514" s="1" t="n">
         <v>0.065261</v>
       </c>
+      <c r="M514" s="13">
+        <f>$Q$5*(B514/100*$Q$7*$Q$6)/($Q$6*$Q$8*A514)</f>
+        <v/>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="1" t="n">
@@ -52970,6 +55054,10 @@
       <c r="C515" s="1" t="n">
         <v>0.065218</v>
       </c>
+      <c r="M515" s="13">
+        <f>$Q$5*(B515/100*$Q$7*$Q$6)/($Q$6*$Q$8*A515)</f>
+        <v/>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="n">
@@ -52981,6 +55069,10 @@
       <c r="C516" s="1" t="n">
         <v>0.06517199999999999</v>
       </c>
+      <c r="M516" s="13">
+        <f>$Q$5*(B516/100*$Q$7*$Q$6)/($Q$6*$Q$8*A516)</f>
+        <v/>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="n">
@@ -52992,6 +55084,10 @@
       <c r="C517" s="1" t="n">
         <v>0.065127</v>
       </c>
+      <c r="M517" s="13">
+        <f>$Q$5*(B517/100*$Q$7*$Q$6)/($Q$6*$Q$8*A517)</f>
+        <v/>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="1" t="n">
@@ -53003,6 +55099,10 @@
       <c r="C518" s="1" t="n">
         <v>0.065084</v>
       </c>
+      <c r="M518" s="13">
+        <f>$Q$5*(B518/100*$Q$7*$Q$6)/($Q$6*$Q$8*A518)</f>
+        <v/>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="1" t="n">
@@ -53014,6 +55114,10 @@
       <c r="C519" s="1" t="n">
         <v>0.065039</v>
       </c>
+      <c r="M519" s="13">
+        <f>$Q$5*(B519/100*$Q$7*$Q$6)/($Q$6*$Q$8*A519)</f>
+        <v/>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="1" t="n">
@@ -53025,6 +55129,10 @@
       <c r="C520" s="1" t="n">
         <v>0.064995</v>
       </c>
+      <c r="M520" s="13">
+        <f>$Q$5*(B520/100*$Q$7*$Q$6)/($Q$6*$Q$8*A520)</f>
+        <v/>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="n">
@@ -53036,6 +55144,10 @@
       <c r="C521" s="1" t="n">
         <v>0.064953</v>
       </c>
+      <c r="M521" s="13">
+        <f>$Q$5*(B521/100*$Q$7*$Q$6)/($Q$6*$Q$8*A521)</f>
+        <v/>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="1" t="n">
@@ -53047,6 +55159,10 @@
       <c r="C522" s="1" t="n">
         <v>0.06490799999999999</v>
       </c>
+      <c r="M522" s="13">
+        <f>$Q$5*(B522/100*$Q$7*$Q$6)/($Q$6*$Q$8*A522)</f>
+        <v/>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="n">
@@ -53058,6 +55174,10 @@
       <c r="C523" s="1" t="n">
         <v>0.06486599999999999</v>
       </c>
+      <c r="M523" s="13">
+        <f>$Q$5*(B523/100*$Q$7*$Q$6)/($Q$6*$Q$8*A523)</f>
+        <v/>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="n">
@@ -53069,6 +55189,10 @@
       <c r="C524" s="1" t="n">
         <v>0.064822</v>
       </c>
+      <c r="M524" s="13">
+        <f>$Q$5*(B524/100*$Q$7*$Q$6)/($Q$6*$Q$8*A524)</f>
+        <v/>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="n">
@@ -53080,6 +55204,10 @@
       <c r="C525" s="1" t="n">
         <v>0.064779</v>
       </c>
+      <c r="M525" s="13">
+        <f>$Q$5*(B525/100*$Q$7*$Q$6)/($Q$6*$Q$8*A525)</f>
+        <v/>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
@@ -53091,6 +55219,10 @@
       <c r="C526" s="1" t="n">
         <v>0.064737</v>
       </c>
+      <c r="M526" s="13">
+        <f>$Q$5*(B526/100*$Q$7*$Q$6)/($Q$6*$Q$8*A526)</f>
+        <v/>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="n">
@@ -53102,6 +55234,10 @@
       <c r="C527" s="1" t="n">
         <v>0.064695</v>
       </c>
+      <c r="M527" s="13">
+        <f>$Q$5*(B527/100*$Q$7*$Q$6)/($Q$6*$Q$8*A527)</f>
+        <v/>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="1" t="n">
@@ -53113,6 +55249,10 @@
       <c r="C528" s="1" t="n">
         <v>0.064652</v>
       </c>
+      <c r="M528" s="13">
+        <f>$Q$5*(B528/100*$Q$7*$Q$6)/($Q$6*$Q$8*A528)</f>
+        <v/>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="n">
@@ -53124,6 +55264,10 @@
       <c r="C529" s="1" t="n">
         <v>0.064609</v>
       </c>
+      <c r="M529" s="13">
+        <f>$Q$5*(B529/100*$Q$7*$Q$6)/($Q$6*$Q$8*A529)</f>
+        <v/>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="n">
@@ -53135,6 +55279,10 @@
       <c r="C530" s="1" t="n">
         <v>0.064566</v>
       </c>
+      <c r="M530" s="13">
+        <f>$Q$5*(B530/100*$Q$7*$Q$6)/($Q$6*$Q$8*A530)</f>
+        <v/>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="1" t="n">
@@ -53146,6 +55294,10 @@
       <c r="C531" s="1" t="n">
         <v>0.064525</v>
       </c>
+      <c r="M531" s="13">
+        <f>$Q$5*(B531/100*$Q$7*$Q$6)/($Q$6*$Q$8*A531)</f>
+        <v/>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="n">
@@ -53157,6 +55309,10 @@
       <c r="C532" s="1" t="n">
         <v>0.064483</v>
       </c>
+      <c r="M532" s="13">
+        <f>$Q$5*(B532/100*$Q$7*$Q$6)/($Q$6*$Q$8*A532)</f>
+        <v/>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="1" t="n">
@@ -53168,6 +55324,10 @@
       <c r="C533" s="1" t="n">
         <v>0.064443</v>
       </c>
+      <c r="M533" s="13">
+        <f>$Q$5*(B533/100*$Q$7*$Q$6)/($Q$6*$Q$8*A533)</f>
+        <v/>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="n">
@@ -53179,6 +55339,10 @@
       <c r="C534" s="1" t="n">
         <v>0.064401</v>
       </c>
+      <c r="M534" s="13">
+        <f>$Q$5*(B534/100*$Q$7*$Q$6)/($Q$6*$Q$8*A534)</f>
+        <v/>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="1" t="n">
@@ -53190,6 +55354,10 @@
       <c r="C535" s="1" t="n">
         <v>0.06436</v>
       </c>
+      <c r="M535" s="13">
+        <f>$Q$5*(B535/100*$Q$7*$Q$6)/($Q$6*$Q$8*A535)</f>
+        <v/>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="1" t="n">
@@ -53201,6 +55369,10 @@
       <c r="C536" s="1" t="n">
         <v>0.064318</v>
       </c>
+      <c r="M536" s="13">
+        <f>$Q$5*(B536/100*$Q$7*$Q$6)/($Q$6*$Q$8*A536)</f>
+        <v/>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="1" t="n">
@@ -53212,6 +55384,10 @@
       <c r="C537" s="1" t="n">
         <v>0.064278</v>
       </c>
+      <c r="M537" s="13">
+        <f>$Q$5*(B537/100*$Q$7*$Q$6)/($Q$6*$Q$8*A537)</f>
+        <v/>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="1" t="n">
@@ -53223,6 +55399,10 @@
       <c r="C538" s="1" t="n">
         <v>0.064239</v>
       </c>
+      <c r="M538" s="13">
+        <f>$Q$5*(B538/100*$Q$7*$Q$6)/($Q$6*$Q$8*A538)</f>
+        <v/>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="1" t="n">
@@ -53234,6 +55414,10 @@
       <c r="C539" s="1" t="n">
         <v>0.06419800000000001</v>
       </c>
+      <c r="M539" s="13">
+        <f>$Q$5*(B539/100*$Q$7*$Q$6)/($Q$6*$Q$8*A539)</f>
+        <v/>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="1" t="n">
@@ -53245,6 +55429,10 @@
       <c r="C540" s="1" t="n">
         <v>0.06415899999999999</v>
       </c>
+      <c r="M540" s="13">
+        <f>$Q$5*(B540/100*$Q$7*$Q$6)/($Q$6*$Q$8*A540)</f>
+        <v/>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="n">
@@ -53256,6 +55444,10 @@
       <c r="C541" s="1" t="n">
         <v>0.06411699999999999</v>
       </c>
+      <c r="M541" s="13">
+        <f>$Q$5*(B541/100*$Q$7*$Q$6)/($Q$6*$Q$8*A541)</f>
+        <v/>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="n">
@@ -53267,6 +55459,10 @@
       <c r="C542" s="1" t="n">
         <v>0.064078</v>
       </c>
+      <c r="M542" s="13">
+        <f>$Q$5*(B542/100*$Q$7*$Q$6)/($Q$6*$Q$8*A542)</f>
+        <v/>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="1" t="n">
@@ -53278,6 +55474,10 @@
       <c r="C543" s="1" t="n">
         <v>0.064038</v>
       </c>
+      <c r="M543" s="13">
+        <f>$Q$5*(B543/100*$Q$7*$Q$6)/($Q$6*$Q$8*A543)</f>
+        <v/>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="1" t="n">
@@ -53289,6 +55489,10 @@
       <c r="C544" s="1" t="n">
         <v>0.063997</v>
       </c>
+      <c r="M544" s="13">
+        <f>$Q$5*(B544/100*$Q$7*$Q$6)/($Q$6*$Q$8*A544)</f>
+        <v/>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="1" t="n">
@@ -53300,6 +55504,10 @@
       <c r="C545" s="1" t="n">
         <v>0.063958</v>
       </c>
+      <c r="M545" s="13">
+        <f>$Q$5*(B545/100*$Q$7*$Q$6)/($Q$6*$Q$8*A545)</f>
+        <v/>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="1" t="n">
@@ -53311,6 +55519,10 @@
       <c r="C546" s="1" t="n">
         <v>0.063919</v>
       </c>
+      <c r="M546" s="13">
+        <f>$Q$5*(B546/100*$Q$7*$Q$6)/($Q$6*$Q$8*A546)</f>
+        <v/>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="1" t="n">
@@ -53322,6 +55534,10 @@
       <c r="C547" s="1" t="n">
         <v>0.06388000000000001</v>
       </c>
+      <c r="M547" s="13">
+        <f>$Q$5*(B547/100*$Q$7*$Q$6)/($Q$6*$Q$8*A547)</f>
+        <v/>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="n">
@@ -53333,6 +55549,10 @@
       <c r="C548" s="1" t="n">
         <v>0.06383999999999999</v>
       </c>
+      <c r="M548" s="13">
+        <f>$Q$5*(B548/100*$Q$7*$Q$6)/($Q$6*$Q$8*A548)</f>
+        <v/>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="1" t="n">
@@ -53344,6 +55564,10 @@
       <c r="C549" s="1" t="n">
         <v>0.0638</v>
       </c>
+      <c r="M549" s="13">
+        <f>$Q$5*(B549/100*$Q$7*$Q$6)/($Q$6*$Q$8*A549)</f>
+        <v/>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="1" t="n">
@@ -53355,6 +55579,10 @@
       <c r="C550" s="1" t="n">
         <v>0.063761</v>
       </c>
+      <c r="M550" s="13">
+        <f>$Q$5*(B550/100*$Q$7*$Q$6)/($Q$6*$Q$8*A550)</f>
+        <v/>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="1" t="n">
@@ -53366,6 +55594,10 @@
       <c r="C551" s="1" t="n">
         <v>0.063721</v>
       </c>
+      <c r="M551" s="13">
+        <f>$Q$5*(B551/100*$Q$7*$Q$6)/($Q$6*$Q$8*A551)</f>
+        <v/>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="n">
@@ -53377,6 +55609,10 @@
       <c r="C552" s="1" t="n">
         <v>0.063684</v>
       </c>
+      <c r="M552" s="13">
+        <f>$Q$5*(B552/100*$Q$7*$Q$6)/($Q$6*$Q$8*A552)</f>
+        <v/>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="1" t="n">
@@ -53388,6 +55624,10 @@
       <c r="C553" s="1" t="n">
         <v>0.06364400000000001</v>
       </c>
+      <c r="M553" s="13">
+        <f>$Q$5*(B553/100*$Q$7*$Q$6)/($Q$6*$Q$8*A553)</f>
+        <v/>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="n">
@@ -53399,6 +55639,10 @@
       <c r="C554" s="1" t="n">
         <v>0.06360499999999999</v>
       </c>
+      <c r="M554" s="13">
+        <f>$Q$5*(B554/100*$Q$7*$Q$6)/($Q$6*$Q$8*A554)</f>
+        <v/>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="1" t="n">
@@ -53410,6 +55654,10 @@
       <c r="C555" s="1" t="n">
         <v>0.063567</v>
       </c>
+      <c r="M555" s="13">
+        <f>$Q$5*(B555/100*$Q$7*$Q$6)/($Q$6*$Q$8*A555)</f>
+        <v/>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="1" t="n">
@@ -53421,6 +55669,10 @@
       <c r="C556" s="1" t="n">
         <v>0.063527</v>
       </c>
+      <c r="M556" s="13">
+        <f>$Q$5*(B556/100*$Q$7*$Q$6)/($Q$6*$Q$8*A556)</f>
+        <v/>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="1" t="n">
@@ -53432,6 +55684,10 @@
       <c r="C557" s="1" t="n">
         <v>0.063488</v>
       </c>
+      <c r="M557" s="13">
+        <f>$Q$5*(B557/100*$Q$7*$Q$6)/($Q$6*$Q$8*A557)</f>
+        <v/>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="1" t="n">
@@ -53443,6 +55699,10 @@
       <c r="C558" s="1" t="n">
         <v>0.06345099999999999</v>
       </c>
+      <c r="M558" s="13">
+        <f>$Q$5*(B558/100*$Q$7*$Q$6)/($Q$6*$Q$8*A558)</f>
+        <v/>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="1" t="n">
@@ -53454,6 +55714,10 @@
       <c r="C559" s="1" t="n">
         <v>0.063413</v>
       </c>
+      <c r="M559" s="13">
+        <f>$Q$5*(B559/100*$Q$7*$Q$6)/($Q$6*$Q$8*A559)</f>
+        <v/>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="n">
@@ -53465,6 +55729,10 @@
       <c r="C560" s="1" t="n">
         <v>0.063375</v>
       </c>
+      <c r="M560" s="13">
+        <f>$Q$5*(B560/100*$Q$7*$Q$6)/($Q$6*$Q$8*A560)</f>
+        <v/>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="1" t="n">
@@ -53476,6 +55744,10 @@
       <c r="C561" s="1" t="n">
         <v>0.063337</v>
       </c>
+      <c r="M561" s="13">
+        <f>$Q$5*(B561/100*$Q$7*$Q$6)/($Q$6*$Q$8*A561)</f>
+        <v/>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="1" t="n">
@@ -53487,6 +55759,10 @@
       <c r="C562" s="1" t="n">
         <v>0.06329899999999999</v>
       </c>
+      <c r="M562" s="13">
+        <f>$Q$5*(B562/100*$Q$7*$Q$6)/($Q$6*$Q$8*A562)</f>
+        <v/>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="1" t="n">
@@ -53498,6 +55774,10 @@
       <c r="C563" s="1" t="n">
         <v>0.06326</v>
       </c>
+      <c r="M563" s="13">
+        <f>$Q$5*(B563/100*$Q$7*$Q$6)/($Q$6*$Q$8*A563)</f>
+        <v/>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="1" t="n">
@@ -53509,6 +55789,10 @@
       <c r="C564" s="1" t="n">
         <v>0.063224</v>
       </c>
+      <c r="M564" s="13">
+        <f>$Q$5*(B564/100*$Q$7*$Q$6)/($Q$6*$Q$8*A564)</f>
+        <v/>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="1" t="n">
@@ -53520,6 +55804,10 @@
       <c r="C565" s="1" t="n">
         <v>0.06318699999999999</v>
       </c>
+      <c r="M565" s="13">
+        <f>$Q$5*(B565/100*$Q$7*$Q$6)/($Q$6*$Q$8*A565)</f>
+        <v/>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="n">
@@ -53531,6 +55819,10 @@
       <c r="C566" s="1" t="n">
         <v>0.063151</v>
       </c>
+      <c r="M566" s="13">
+        <f>$Q$5*(B566/100*$Q$7*$Q$6)/($Q$6*$Q$8*A566)</f>
+        <v/>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="1" t="n">
@@ -53542,6 +55834,10 @@
       <c r="C567" s="1" t="n">
         <v>0.063114</v>
       </c>
+      <c r="M567" s="13">
+        <f>$Q$5*(B567/100*$Q$7*$Q$6)/($Q$6*$Q$8*A567)</f>
+        <v/>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="1" t="n">
@@ -53553,6 +55849,10 @@
       <c r="C568" s="1" t="n">
         <v>0.063078</v>
       </c>
+      <c r="M568" s="13">
+        <f>$Q$5*(B568/100*$Q$7*$Q$6)/($Q$6*$Q$8*A568)</f>
+        <v/>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="1" t="n">
@@ -53564,6 +55864,10 @@
       <c r="C569" s="1" t="n">
         <v>0.063043</v>
       </c>
+      <c r="M569" s="13">
+        <f>$Q$5*(B569/100*$Q$7*$Q$6)/($Q$6*$Q$8*A569)</f>
+        <v/>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="1" t="n">
@@ -53575,6 +55879,10 @@
       <c r="C570" s="1" t="n">
         <v>0.063004</v>
       </c>
+      <c r="M570" s="13">
+        <f>$Q$5*(B570/100*$Q$7*$Q$6)/($Q$6*$Q$8*A570)</f>
+        <v/>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="1" t="n">
@@ -53586,6 +55894,10 @@
       <c r="C571" s="1" t="n">
         <v>0.062968</v>
       </c>
+      <c r="M571" s="13">
+        <f>$Q$5*(B571/100*$Q$7*$Q$6)/($Q$6*$Q$8*A571)</f>
+        <v/>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="1" t="n">
@@ -53597,6 +55909,10 @@
       <c r="C572" s="1" t="n">
         <v>0.062931</v>
       </c>
+      <c r="M572" s="13">
+        <f>$Q$5*(B572/100*$Q$7*$Q$6)/($Q$6*$Q$8*A572)</f>
+        <v/>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="1" t="n">
@@ -53608,6 +55924,10 @@
       <c r="C573" s="1" t="n">
         <v>0.06289500000000001</v>
       </c>
+      <c r="M573" s="13">
+        <f>$Q$5*(B573/100*$Q$7*$Q$6)/($Q$6*$Q$8*A573)</f>
+        <v/>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="1" t="n">
@@ -53619,6 +55939,10 @@
       <c r="C574" s="1" t="n">
         <v>0.062859</v>
       </c>
+      <c r="M574" s="13">
+        <f>$Q$5*(B574/100*$Q$7*$Q$6)/($Q$6*$Q$8*A574)</f>
+        <v/>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="1" t="n">
@@ -53630,6 +55954,10 @@
       <c r="C575" s="1" t="n">
         <v>0.062824</v>
       </c>
+      <c r="M575" s="13">
+        <f>$Q$5*(B575/100*$Q$7*$Q$6)/($Q$6*$Q$8*A575)</f>
+        <v/>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="1" t="n">
@@ -53641,6 +55969,10 @@
       <c r="C576" s="1" t="n">
         <v>0.062788</v>
       </c>
+      <c r="M576" s="13">
+        <f>$Q$5*(B576/100*$Q$7*$Q$6)/($Q$6*$Q$8*A576)</f>
+        <v/>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="1" t="n">
@@ -53652,6 +55984,10 @@
       <c r="C577" s="1" t="n">
         <v>0.062751</v>
       </c>
+      <c r="M577" s="13">
+        <f>$Q$5*(B577/100*$Q$7*$Q$6)/($Q$6*$Q$8*A577)</f>
+        <v/>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="1" t="n">
@@ -53663,6 +55999,10 @@
       <c r="C578" s="1" t="n">
         <v>0.06271500000000001</v>
       </c>
+      <c r="M578" s="13">
+        <f>$Q$5*(B578/100*$Q$7*$Q$6)/($Q$6*$Q$8*A578)</f>
+        <v/>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="1" t="n">
@@ -53674,6 +56014,10 @@
       <c r="C579" s="1" t="n">
         <v>0.062679</v>
       </c>
+      <c r="M579" s="13">
+        <f>$Q$5*(B579/100*$Q$7*$Q$6)/($Q$6*$Q$8*A579)</f>
+        <v/>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="1" t="n">
@@ -53685,6 +56029,10 @@
       <c r="C580" s="1" t="n">
         <v>0.06264400000000001</v>
       </c>
+      <c r="M580" s="13">
+        <f>$Q$5*(B580/100*$Q$7*$Q$6)/($Q$6*$Q$8*A580)</f>
+        <v/>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="1" t="n">
@@ -53696,6 +56044,10 @@
       <c r="C581" s="1" t="n">
         <v>0.062608</v>
       </c>
+      <c r="M581" s="13">
+        <f>$Q$5*(B581/100*$Q$7*$Q$6)/($Q$6*$Q$8*A581)</f>
+        <v/>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="1" t="n">
@@ -53707,6 +56059,10 @@
       <c r="C582" s="1" t="n">
         <v>0.062572</v>
       </c>
+      <c r="M582" s="13">
+        <f>$Q$5*(B582/100*$Q$7*$Q$6)/($Q$6*$Q$8*A582)</f>
+        <v/>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="1" t="n">
@@ -53718,6 +56074,10 @@
       <c r="C583" s="1" t="n">
         <v>0.06253499999999999</v>
       </c>
+      <c r="M583" s="13">
+        <f>$Q$5*(B583/100*$Q$7*$Q$6)/($Q$6*$Q$8*A583)</f>
+        <v/>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="1" t="n">
@@ -53729,6 +56089,10 @@
       <c r="C584" s="1" t="n">
         <v>0.062499</v>
       </c>
+      <c r="M584" s="13">
+        <f>$Q$5*(B584/100*$Q$7*$Q$6)/($Q$6*$Q$8*A584)</f>
+        <v/>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="1" t="n">
@@ -53740,6 +56104,10 @@
       <c r="C585" s="1" t="n">
         <v>0.062464</v>
       </c>
+      <c r="M585" s="13">
+        <f>$Q$5*(B585/100*$Q$7*$Q$6)/($Q$6*$Q$8*A585)</f>
+        <v/>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="1" t="n">
@@ -53751,6 +56119,10 @@
       <c r="C586" s="1" t="n">
         <v>0.062427</v>
       </c>
+      <c r="M586" s="13">
+        <f>$Q$5*(B586/100*$Q$7*$Q$6)/($Q$6*$Q$8*A586)</f>
+        <v/>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="1" t="n">
@@ -53762,6 +56134,10 @@
       <c r="C587" s="1" t="n">
         <v>0.062392</v>
       </c>
+      <c r="M587" s="13">
+        <f>$Q$5*(B587/100*$Q$7*$Q$6)/($Q$6*$Q$8*A587)</f>
+        <v/>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="1" t="n">
@@ -53773,6 +56149,10 @@
       <c r="C588" s="1" t="n">
         <v>0.062357</v>
       </c>
+      <c r="M588" s="13">
+        <f>$Q$5*(B588/100*$Q$7*$Q$6)/($Q$6*$Q$8*A588)</f>
+        <v/>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="1" t="n">
@@ -53784,6 +56164,10 @@
       <c r="C589" s="1" t="n">
         <v>0.062323</v>
       </c>
+      <c r="M589" s="13">
+        <f>$Q$5*(B589/100*$Q$7*$Q$6)/($Q$6*$Q$8*A589)</f>
+        <v/>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="1" t="n">
@@ -53795,6 +56179,10 @@
       <c r="C590" s="1" t="n">
         <v>0.062286</v>
       </c>
+      <c r="M590" s="13">
+        <f>$Q$5*(B590/100*$Q$7*$Q$6)/($Q$6*$Q$8*A590)</f>
+        <v/>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="1" t="n">
@@ -53806,6 +56194,10 @@
       <c r="C591" s="1" t="n">
         <v>0.062252</v>
       </c>
+      <c r="M591" s="13">
+        <f>$Q$5*(B591/100*$Q$7*$Q$6)/($Q$6*$Q$8*A591)</f>
+        <v/>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="1" t="n">
@@ -53817,6 +56209,10 @@
       <c r="C592" s="1" t="n">
         <v>0.062216</v>
       </c>
+      <c r="M592" s="13">
+        <f>$Q$5*(B592/100*$Q$7*$Q$6)/($Q$6*$Q$8*A592)</f>
+        <v/>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="1" t="n">
@@ -53828,6 +56224,10 @@
       <c r="C593" s="1" t="n">
         <v>0.062181</v>
       </c>
+      <c r="M593" s="13">
+        <f>$Q$5*(B593/100*$Q$7*$Q$6)/($Q$6*$Q$8*A593)</f>
+        <v/>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1" t="n">
@@ -53839,6 +56239,10 @@
       <c r="C594" s="1" t="n">
         <v>0.062146</v>
       </c>
+      <c r="M594" s="13">
+        <f>$Q$5*(B594/100*$Q$7*$Q$6)/($Q$6*$Q$8*A594)</f>
+        <v/>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="1" t="n">
@@ -53850,6 +56254,10 @@
       <c r="C595" s="1" t="n">
         <v>0.062113</v>
       </c>
+      <c r="M595" s="13">
+        <f>$Q$5*(B595/100*$Q$7*$Q$6)/($Q$6*$Q$8*A595)</f>
+        <v/>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="1" t="n">
@@ -53861,6 +56269,10 @@
       <c r="C596" s="1" t="n">
         <v>0.062078</v>
       </c>
+      <c r="M596" s="13">
+        <f>$Q$5*(B596/100*$Q$7*$Q$6)/($Q$6*$Q$8*A596)</f>
+        <v/>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="1" t="n">
@@ -53872,6 +56284,10 @@
       <c r="C597" s="1" t="n">
         <v>0.062042</v>
       </c>
+      <c r="M597" s="13">
+        <f>$Q$5*(B597/100*$Q$7*$Q$6)/($Q$6*$Q$8*A597)</f>
+        <v/>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="1" t="n">
@@ -53883,6 +56299,10 @@
       <c r="C598" s="1" t="n">
         <v>0.062007</v>
       </c>
+      <c r="M598" s="13">
+        <f>$Q$5*(B598/100*$Q$7*$Q$6)/($Q$6*$Q$8*A598)</f>
+        <v/>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="1" t="n">
@@ -53894,6 +56314,10 @@
       <c r="C599" s="1" t="n">
         <v>0.061972</v>
       </c>
+      <c r="M599" s="13">
+        <f>$Q$5*(B599/100*$Q$7*$Q$6)/($Q$6*$Q$8*A599)</f>
+        <v/>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="n">
@@ -53905,6 +56329,10 @@
       <c r="C600" s="1" t="n">
         <v>0.061939</v>
       </c>
+      <c r="M600" s="13">
+        <f>$Q$5*(B600/100*$Q$7*$Q$6)/($Q$6*$Q$8*A600)</f>
+        <v/>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="1" t="n">
@@ -53916,6 +56344,10 @@
       <c r="C601" s="1" t="n">
         <v>0.061905</v>
       </c>
+      <c r="M601" s="13">
+        <f>$Q$5*(B601/100*$Q$7*$Q$6)/($Q$6*$Q$8*A601)</f>
+        <v/>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="1" t="n">
@@ -53927,6 +56359,10 @@
       <c r="C602" s="1" t="n">
         <v>0.061872</v>
       </c>
+      <c r="M602" s="13">
+        <f>$Q$5*(B602/100*$Q$7*$Q$6)/($Q$6*$Q$8*A602)</f>
+        <v/>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="1" t="n">
@@ -53938,6 +56374,10 @@
       <c r="C603" s="1" t="n">
         <v>0.061836</v>
       </c>
+      <c r="M603" s="13">
+        <f>$Q$5*(B603/100*$Q$7*$Q$6)/($Q$6*$Q$8*A603)</f>
+        <v/>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="1" t="n">
@@ -53949,6 +56389,10 @@
       <c r="C604" s="1" t="n">
         <v>0.061803</v>
       </c>
+      <c r="M604" s="13">
+        <f>$Q$5*(B604/100*$Q$7*$Q$6)/($Q$6*$Q$8*A604)</f>
+        <v/>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="1" t="n">
@@ -53960,6 +56404,10 @@
       <c r="C605" s="1" t="n">
         <v>0.061769</v>
       </c>
+      <c r="M605" s="13">
+        <f>$Q$5*(B605/100*$Q$7*$Q$6)/($Q$6*$Q$8*A605)</f>
+        <v/>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="1" t="n">
@@ -53971,6 +56419,10 @@
       <c r="C606" s="1" t="n">
         <v>0.061735</v>
       </c>
+      <c r="M606" s="13">
+        <f>$Q$5*(B606/100*$Q$7*$Q$6)/($Q$6*$Q$8*A606)</f>
+        <v/>
+      </c>
     </row>
     <row r="607">
       <c r="A607" s="1" t="n">
@@ -53982,6 +56434,10 @@
       <c r="C607" s="1" t="n">
         <v>0.061702</v>
       </c>
+      <c r="M607" s="13">
+        <f>$Q$5*(B607/100*$Q$7*$Q$6)/($Q$6*$Q$8*A607)</f>
+        <v/>
+      </c>
     </row>
     <row r="608">
       <c r="A608" s="1" t="n">
@@ -53993,6 +56449,10 @@
       <c r="C608" s="1" t="n">
         <v>0.061667</v>
       </c>
+      <c r="M608" s="13">
+        <f>$Q$5*(B608/100*$Q$7*$Q$6)/($Q$6*$Q$8*A608)</f>
+        <v/>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="1" t="n">
@@ -54004,6 +56464,10 @@
       <c r="C609" s="1" t="n">
         <v>0.061633</v>
       </c>
+      <c r="M609" s="13">
+        <f>$Q$5*(B609/100*$Q$7*$Q$6)/($Q$6*$Q$8*A609)</f>
+        <v/>
+      </c>
     </row>
     <row r="610">
       <c r="A610" s="1" t="n">
@@ -54015,6 +56479,10 @@
       <c r="C610" s="1" t="n">
         <v>0.061599</v>
       </c>
+      <c r="M610" s="13">
+        <f>$Q$5*(B610/100*$Q$7*$Q$6)/($Q$6*$Q$8*A610)</f>
+        <v/>
+      </c>
     </row>
     <row r="611">
       <c r="A611" s="1" t="n">
@@ -54026,6 +56494,10 @@
       <c r="C611" s="1" t="n">
         <v>0.061566</v>
       </c>
+      <c r="M611" s="13">
+        <f>$Q$5*(B611/100*$Q$7*$Q$6)/($Q$6*$Q$8*A611)</f>
+        <v/>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="1" t="n">
@@ -54037,6 +56509,10 @@
       <c r="C612" s="1" t="n">
         <v>0.061533</v>
       </c>
+      <c r="M612" s="13">
+        <f>$Q$5*(B612/100*$Q$7*$Q$6)/($Q$6*$Q$8*A612)</f>
+        <v/>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="1" t="n">
@@ -54048,6 +56524,10 @@
       <c r="C613" s="1" t="n">
         <v>0.061499</v>
       </c>
+      <c r="M613" s="13">
+        <f>$Q$5*(B613/100*$Q$7*$Q$6)/($Q$6*$Q$8*A613)</f>
+        <v/>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="1" t="n">
@@ -54059,6 +56539,10 @@
       <c r="C614" s="1" t="n">
         <v>0.061466</v>
       </c>
+      <c r="M614" s="13">
+        <f>$Q$5*(B614/100*$Q$7*$Q$6)/($Q$6*$Q$8*A614)</f>
+        <v/>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="1" t="n">
@@ -54070,6 +56554,10 @@
       <c r="C615" s="1" t="n">
         <v>0.061432</v>
       </c>
+      <c r="M615" s="13">
+        <f>$Q$5*(B615/100*$Q$7*$Q$6)/($Q$6*$Q$8*A615)</f>
+        <v/>
+      </c>
     </row>
     <row r="616">
       <c r="A616" s="1" t="n">
@@ -54081,6 +56569,10 @@
       <c r="C616" s="1" t="n">
         <v>0.061399</v>
       </c>
+      <c r="M616" s="13">
+        <f>$Q$5*(B616/100*$Q$7*$Q$6)/($Q$6*$Q$8*A616)</f>
+        <v/>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="1" t="n">
@@ -54092,6 +56584,10 @@
       <c r="C617" s="1" t="n">
         <v>0.061366</v>
       </c>
+      <c r="M617" s="13">
+        <f>$Q$5*(B617/100*$Q$7*$Q$6)/($Q$6*$Q$8*A617)</f>
+        <v/>
+      </c>
     </row>
     <row r="618">
       <c r="A618" s="1" t="n">
@@ -54103,6 +56599,10 @@
       <c r="C618" s="1" t="n">
         <v>0.061333</v>
       </c>
+      <c r="M618" s="13">
+        <f>$Q$5*(B618/100*$Q$7*$Q$6)/($Q$6*$Q$8*A618)</f>
+        <v/>
+      </c>
     </row>
     <row r="619">
       <c r="A619" s="1" t="n">
@@ -54114,6 +56614,10 @@
       <c r="C619" s="1" t="n">
         <v>0.061301</v>
       </c>
+      <c r="M619" s="13">
+        <f>$Q$5*(B619/100*$Q$7*$Q$6)/($Q$6*$Q$8*A619)</f>
+        <v/>
+      </c>
     </row>
     <row r="620">
       <c r="A620" s="1" t="n">
@@ -54125,6 +56629,10 @@
       <c r="C620" s="1" t="n">
         <v>0.061269</v>
       </c>
+      <c r="M620" s="13">
+        <f>$Q$5*(B620/100*$Q$7*$Q$6)/($Q$6*$Q$8*A620)</f>
+        <v/>
+      </c>
     </row>
     <row r="621">
       <c r="A621" s="1" t="n">
@@ -54136,6 +56644,10 @@
       <c r="C621" s="1" t="n">
         <v>0.061235</v>
       </c>
+      <c r="M621" s="13">
+        <f>$Q$5*(B621/100*$Q$7*$Q$6)/($Q$6*$Q$8*A621)</f>
+        <v/>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="1" t="n">
@@ -54147,6 +56659,10 @@
       <c r="C622" s="1" t="n">
         <v>0.061203</v>
       </c>
+      <c r="M622" s="13">
+        <f>$Q$5*(B622/100*$Q$7*$Q$6)/($Q$6*$Q$8*A622)</f>
+        <v/>
+      </c>
     </row>
     <row r="623">
       <c r="A623" s="1" t="n">
@@ -54158,6 +56674,10 @@
       <c r="C623" s="1" t="n">
         <v>0.061171</v>
       </c>
+      <c r="M623" s="13">
+        <f>$Q$5*(B623/100*$Q$7*$Q$6)/($Q$6*$Q$8*A623)</f>
+        <v/>
+      </c>
     </row>
     <row r="624">
       <c r="A624" s="1" t="n">
@@ -54169,6 +56689,10 @@
       <c r="C624" s="1" t="n">
         <v>0.06114</v>
       </c>
+      <c r="M624" s="13">
+        <f>$Q$5*(B624/100*$Q$7*$Q$6)/($Q$6*$Q$8*A624)</f>
+        <v/>
+      </c>
     </row>
     <row r="625">
       <c r="A625" s="1" t="n">
@@ -54180,6 +56704,10 @@
       <c r="C625" s="1" t="n">
         <v>0.061108</v>
       </c>
+      <c r="M625" s="13">
+        <f>$Q$5*(B625/100*$Q$7*$Q$6)/($Q$6*$Q$8*A625)</f>
+        <v/>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="1" t="n">
@@ -54191,6 +56719,10 @@
       <c r="C626" s="1" t="n">
         <v>0.061076</v>
       </c>
+      <c r="M626" s="13">
+        <f>$Q$5*(B626/100*$Q$7*$Q$6)/($Q$6*$Q$8*A626)</f>
+        <v/>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="1" t="n">
@@ -54202,6 +56734,10 @@
       <c r="C627" s="1" t="n">
         <v>0.061044</v>
       </c>
+      <c r="M627" s="13">
+        <f>$Q$5*(B627/100*$Q$7*$Q$6)/($Q$6*$Q$8*A627)</f>
+        <v/>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="1" t="n">
@@ -54213,6 +56749,10 @@
       <c r="C628" s="1" t="n">
         <v>0.061013</v>
       </c>
+      <c r="M628" s="13">
+        <f>$Q$5*(B628/100*$Q$7*$Q$6)/($Q$6*$Q$8*A628)</f>
+        <v/>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="1" t="n">
@@ -54224,6 +56764,10 @@
       <c r="C629" s="1" t="n">
         <v>0.060981</v>
       </c>
+      <c r="M629" s="13">
+        <f>$Q$5*(B629/100*$Q$7*$Q$6)/($Q$6*$Q$8*A629)</f>
+        <v/>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="1" t="n">
@@ -54235,6 +56779,10 @@
       <c r="C630" s="1" t="n">
         <v>0.060949</v>
       </c>
+      <c r="M630" s="13">
+        <f>$Q$5*(B630/100*$Q$7*$Q$6)/($Q$6*$Q$8*A630)</f>
+        <v/>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="1" t="n">
@@ -54246,6 +56794,10 @@
       <c r="C631" s="1" t="n">
         <v>0.060918</v>
       </c>
+      <c r="M631" s="13">
+        <f>$Q$5*(B631/100*$Q$7*$Q$6)/($Q$6*$Q$8*A631)</f>
+        <v/>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="1" t="n">
@@ -54257,6 +56809,10 @@
       <c r="C632" s="1" t="n">
         <v>0.060885</v>
       </c>
+      <c r="M632" s="13">
+        <f>$Q$5*(B632/100*$Q$7*$Q$6)/($Q$6*$Q$8*A632)</f>
+        <v/>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="1" t="n">
@@ -54268,6 +56824,10 @@
       <c r="C633" s="1" t="n">
         <v>0.060854</v>
       </c>
+      <c r="M633" s="13">
+        <f>$Q$5*(B633/100*$Q$7*$Q$6)/($Q$6*$Q$8*A633)</f>
+        <v/>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="1" t="n">
@@ -54279,6 +56839,10 @@
       <c r="C634" s="1" t="n">
         <v>0.060824</v>
       </c>
+      <c r="M634" s="13">
+        <f>$Q$5*(B634/100*$Q$7*$Q$6)/($Q$6*$Q$8*A634)</f>
+        <v/>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="1" t="n">
@@ -54290,6 +56854,10 @@
       <c r="C635" s="1" t="n">
         <v>0.060793</v>
       </c>
+      <c r="M635" s="13">
+        <f>$Q$5*(B635/100*$Q$7*$Q$6)/($Q$6*$Q$8*A635)</f>
+        <v/>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="1" t="n">
@@ -54301,6 +56869,10 @@
       <c r="C636" s="1" t="n">
         <v>0.060763</v>
       </c>
+      <c r="M636" s="13">
+        <f>$Q$5*(B636/100*$Q$7*$Q$6)/($Q$6*$Q$8*A636)</f>
+        <v/>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="1" t="n">
@@ -54312,6 +56884,10 @@
       <c r="C637" s="1" t="n">
         <v>0.060732</v>
       </c>
+      <c r="M637" s="13">
+        <f>$Q$5*(B637/100*$Q$7*$Q$6)/($Q$6*$Q$8*A637)</f>
+        <v/>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="1" t="n">
@@ -54323,6 +56899,10 @@
       <c r="C638" s="1" t="n">
         <v>0.060702</v>
       </c>
+      <c r="M638" s="13">
+        <f>$Q$5*(B638/100*$Q$7*$Q$6)/($Q$6*$Q$8*A638)</f>
+        <v/>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="1" t="n">
@@ -54334,6 +56914,10 @@
       <c r="C639" s="1" t="n">
         <v>0.06067</v>
       </c>
+      <c r="M639" s="13">
+        <f>$Q$5*(B639/100*$Q$7*$Q$6)/($Q$6*$Q$8*A639)</f>
+        <v/>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="1" t="n">
@@ -54345,6 +56929,10 @@
       <c r="C640" s="1" t="n">
         <v>0.060639</v>
       </c>
+      <c r="M640" s="13">
+        <f>$Q$5*(B640/100*$Q$7*$Q$6)/($Q$6*$Q$8*A640)</f>
+        <v/>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="1" t="n">
@@ -54356,6 +56944,10 @@
       <c r="C641" s="1" t="n">
         <v>0.060609</v>
       </c>
+      <c r="M641" s="13">
+        <f>$Q$5*(B641/100*$Q$7*$Q$6)/($Q$6*$Q$8*A641)</f>
+        <v/>
+      </c>
     </row>
     <row r="642">
       <c r="A642" s="1" t="n">
@@ -54367,6 +56959,10 @@
       <c r="C642" s="1" t="n">
         <v>0.060578</v>
       </c>
+      <c r="M642" s="13">
+        <f>$Q$5*(B642/100*$Q$7*$Q$6)/($Q$6*$Q$8*A642)</f>
+        <v/>
+      </c>
     </row>
     <row r="643">
       <c r="A643" s="1" t="n">
@@ -54378,6 +56974,10 @@
       <c r="C643" s="1" t="n">
         <v>0.060549</v>
       </c>
+      <c r="M643" s="13">
+        <f>$Q$5*(B643/100*$Q$7*$Q$6)/($Q$6*$Q$8*A643)</f>
+        <v/>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="1" t="n">
@@ -54389,6 +56989,10 @@
       <c r="C644" s="1" t="n">
         <v>0.060519</v>
       </c>
+      <c r="M644" s="13">
+        <f>$Q$5*(B644/100*$Q$7*$Q$6)/($Q$6*$Q$8*A644)</f>
+        <v/>
+      </c>
     </row>
     <row r="645">
       <c r="A645" s="1" t="n">
@@ -54400,6 +57004,10 @@
       <c r="C645" s="1" t="n">
         <v>0.060487</v>
       </c>
+      <c r="M645" s="13">
+        <f>$Q$5*(B645/100*$Q$7*$Q$6)/($Q$6*$Q$8*A645)</f>
+        <v/>
+      </c>
     </row>
     <row r="646">
       <c r="A646" s="1" t="n">
@@ -54411,6 +57019,10 @@
       <c r="C646" s="1" t="n">
         <v>0.060458</v>
       </c>
+      <c r="M646" s="13">
+        <f>$Q$5*(B646/100*$Q$7*$Q$6)/($Q$6*$Q$8*A646)</f>
+        <v/>
+      </c>
     </row>
     <row r="647">
       <c r="A647" s="1" t="n">
@@ -54422,6 +57034,10 @@
       <c r="C647" s="1" t="n">
         <v>0.060429</v>
       </c>
+      <c r="M647" s="13">
+        <f>$Q$5*(B647/100*$Q$7*$Q$6)/($Q$6*$Q$8*A647)</f>
+        <v/>
+      </c>
     </row>
     <row r="648">
       <c r="A648" s="1" t="n">
@@ -54433,6 +57049,10 @@
       <c r="C648" s="1" t="n">
         <v>0.060399</v>
       </c>
+      <c r="M648" s="13">
+        <f>$Q$5*(B648/100*$Q$7*$Q$6)/($Q$6*$Q$8*A648)</f>
+        <v/>
+      </c>
     </row>
     <row r="649">
       <c r="A649" s="1" t="n">
@@ -54444,6 +57064,10 @@
       <c r="C649" s="1" t="n">
         <v>0.060369</v>
       </c>
+      <c r="M649" s="13">
+        <f>$Q$5*(B649/100*$Q$7*$Q$6)/($Q$6*$Q$8*A649)</f>
+        <v/>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="1" t="n">
@@ -54455,6 +57079,10 @@
       <c r="C650" s="1" t="n">
         <v>0.060339</v>
       </c>
+      <c r="M650" s="13">
+        <f>$Q$5*(B650/100*$Q$7*$Q$6)/($Q$6*$Q$8*A650)</f>
+        <v/>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="1" t="n">
@@ -54466,6 +57094,10 @@
       <c r="C651" s="1" t="n">
         <v>0.06031</v>
       </c>
+      <c r="M651" s="13">
+        <f>$Q$5*(B651/100*$Q$7*$Q$6)/($Q$6*$Q$8*A651)</f>
+        <v/>
+      </c>
     </row>
     <row r="652">
       <c r="A652" s="1" t="n">
@@ -54477,6 +57109,10 @@
       <c r="C652" s="1" t="n">
         <v>0.06028</v>
       </c>
+      <c r="M652" s="13">
+        <f>$Q$5*(B652/100*$Q$7*$Q$6)/($Q$6*$Q$8*A652)</f>
+        <v/>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="1" t="n">
@@ -54488,6 +57124,10 @@
       <c r="C653" s="1" t="n">
         <v>0.06025</v>
       </c>
+      <c r="M653" s="13">
+        <f>$Q$5*(B653/100*$Q$7*$Q$6)/($Q$6*$Q$8*A653)</f>
+        <v/>
+      </c>
     </row>
     <row r="654">
       <c r="A654" s="1" t="n">
@@ -54499,6 +57139,10 @@
       <c r="C654" s="1" t="n">
         <v>0.06022</v>
       </c>
+      <c r="M654" s="13">
+        <f>$Q$5*(B654/100*$Q$7*$Q$6)/($Q$6*$Q$8*A654)</f>
+        <v/>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="1" t="n">
@@ -54510,6 +57154,10 @@
       <c r="C655" s="1" t="n">
         <v>0.060192</v>
       </c>
+      <c r="M655" s="13">
+        <f>$Q$5*(B655/100*$Q$7*$Q$6)/($Q$6*$Q$8*A655)</f>
+        <v/>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="1" t="n">
@@ -54521,6 +57169,10 @@
       <c r="C656" s="1" t="n">
         <v>0.060163</v>
       </c>
+      <c r="M656" s="13">
+        <f>$Q$5*(B656/100*$Q$7*$Q$6)/($Q$6*$Q$8*A656)</f>
+        <v/>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="1" t="n">
@@ -54532,6 +57184,10 @@
       <c r="C657" s="1" t="n">
         <v>0.060133</v>
       </c>
+      <c r="M657" s="13">
+        <f>$Q$5*(B657/100*$Q$7*$Q$6)/($Q$6*$Q$8*A657)</f>
+        <v/>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="1" t="n">
@@ -54543,6 +57199,10 @@
       <c r="C658" s="1" t="n">
         <v>0.060104</v>
       </c>
+      <c r="M658" s="13">
+        <f>$Q$5*(B658/100*$Q$7*$Q$6)/($Q$6*$Q$8*A658)</f>
+        <v/>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="1" t="n">
@@ -54554,6 +57214,10 @@
       <c r="C659" s="1" t="n">
         <v>0.060075</v>
       </c>
+      <c r="M659" s="13">
+        <f>$Q$5*(B659/100*$Q$7*$Q$6)/($Q$6*$Q$8*A659)</f>
+        <v/>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="1" t="n">
@@ -54565,6 +57229,10 @@
       <c r="C660" s="1" t="n">
         <v>0.060046</v>
       </c>
+      <c r="M660" s="13">
+        <f>$Q$5*(B660/100*$Q$7*$Q$6)/($Q$6*$Q$8*A660)</f>
+        <v/>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="1" t="n">
@@ -54576,6 +57244,10 @@
       <c r="C661" s="1" t="n">
         <v>0.060017</v>
       </c>
+      <c r="M661" s="13">
+        <f>$Q$5*(B661/100*$Q$7*$Q$6)/($Q$6*$Q$8*A661)</f>
+        <v/>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="1" t="n">
@@ -54587,6 +57259,10 @@
       <c r="C662" s="1" t="n">
         <v>0.059988</v>
       </c>
+      <c r="M662" s="13">
+        <f>$Q$5*(B662/100*$Q$7*$Q$6)/($Q$6*$Q$8*A662)</f>
+        <v/>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="1" t="n">
@@ -54598,6 +57274,10 @@
       <c r="C663" s="1" t="n">
         <v>0.059959</v>
       </c>
+      <c r="M663" s="13">
+        <f>$Q$5*(B663/100*$Q$7*$Q$6)/($Q$6*$Q$8*A663)</f>
+        <v/>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="1" t="n">
@@ -54609,6 +57289,10 @@
       <c r="C664" s="1" t="n">
         <v>0.059931</v>
       </c>
+      <c r="M664" s="13">
+        <f>$Q$5*(B664/100*$Q$7*$Q$6)/($Q$6*$Q$8*A664)</f>
+        <v/>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="1" t="n">
@@ -54620,6 +57304,10 @@
       <c r="C665" s="1" t="n">
         <v>0.059902</v>
       </c>
+      <c r="M665" s="13">
+        <f>$Q$5*(B665/100*$Q$7*$Q$6)/($Q$6*$Q$8*A665)</f>
+        <v/>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="1" t="n">
@@ -54631,6 +57319,10 @@
       <c r="C666" s="1" t="n">
         <v>0.059875</v>
       </c>
+      <c r="M666" s="13">
+        <f>$Q$5*(B666/100*$Q$7*$Q$6)/($Q$6*$Q$8*A666)</f>
+        <v/>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="1" t="n">
@@ -54642,6 +57334,10 @@
       <c r="C667" s="1" t="n">
         <v>0.059847</v>
       </c>
+      <c r="M667" s="13">
+        <f>$Q$5*(B667/100*$Q$7*$Q$6)/($Q$6*$Q$8*A667)</f>
+        <v/>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="1" t="n">
@@ -54653,6 +57349,10 @@
       <c r="C668" s="1" t="n">
         <v>0.059818</v>
       </c>
+      <c r="M668" s="13">
+        <f>$Q$5*(B668/100*$Q$7*$Q$6)/($Q$6*$Q$8*A668)</f>
+        <v/>
+      </c>
     </row>
     <row r="669">
       <c r="A669" s="1" t="n">
@@ -54664,6 +57364,10 @@
       <c r="C669" s="1" t="n">
         <v>0.059789</v>
       </c>
+      <c r="M669" s="13">
+        <f>$Q$5*(B669/100*$Q$7*$Q$6)/($Q$6*$Q$8*A669)</f>
+        <v/>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="1" t="n">
@@ -54675,6 +57379,10 @@
       <c r="C670" s="1" t="n">
         <v>0.059761</v>
       </c>
+      <c r="M670" s="13">
+        <f>$Q$5*(B670/100*$Q$7*$Q$6)/($Q$6*$Q$8*A670)</f>
+        <v/>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="1" t="n">
@@ -54686,6 +57394,10 @@
       <c r="C671" s="1" t="n">
         <v>0.059732</v>
       </c>
+      <c r="M671" s="13">
+        <f>$Q$5*(B671/100*$Q$7*$Q$6)/($Q$6*$Q$8*A671)</f>
+        <v/>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="1" t="n">
@@ -54697,6 +57409,10 @@
       <c r="C672" s="1" t="n">
         <v>0.059705</v>
       </c>
+      <c r="M672" s="13">
+        <f>$Q$5*(B672/100*$Q$7*$Q$6)/($Q$6*$Q$8*A672)</f>
+        <v/>
+      </c>
     </row>
     <row r="673">
       <c r="A673" s="1" t="n">
@@ -54708,6 +57424,10 @@
       <c r="C673" s="1" t="n">
         <v>0.059677</v>
       </c>
+      <c r="M673" s="13">
+        <f>$Q$5*(B673/100*$Q$7*$Q$6)/($Q$6*$Q$8*A673)</f>
+        <v/>
+      </c>
     </row>
     <row r="674">
       <c r="A674" s="1" t="n">
@@ -54719,6 +57439,10 @@
       <c r="C674" s="1" t="n">
         <v>0.059649</v>
       </c>
+      <c r="M674" s="13">
+        <f>$Q$5*(B674/100*$Q$7*$Q$6)/($Q$6*$Q$8*A674)</f>
+        <v/>
+      </c>
     </row>
     <row r="675">
       <c r="A675" s="1" t="n">
@@ -54730,6 +57454,10 @@
       <c r="C675" s="1" t="n">
         <v>0.059621</v>
       </c>
+      <c r="M675" s="13">
+        <f>$Q$5*(B675/100*$Q$7*$Q$6)/($Q$6*$Q$8*A675)</f>
+        <v/>
+      </c>
     </row>
     <row r="676">
       <c r="A676" s="1" t="n">
@@ -54741,6 +57469,10 @@
       <c r="C676" s="1" t="n">
         <v>0.059593</v>
       </c>
+      <c r="M676" s="13">
+        <f>$Q$5*(B676/100*$Q$7*$Q$6)/($Q$6*$Q$8*A676)</f>
+        <v/>
+      </c>
     </row>
     <row r="677">
       <c r="A677" s="1" t="n">
@@ -54751,6 +57483,10 @@
       </c>
       <c r="C677" s="1" t="n">
         <v>0.059566</v>
+      </c>
+      <c r="M677" s="13">
+        <f>$Q$5*(B677/100*$Q$7*$Q$6)/($Q$6*$Q$8*A677)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
